--- a/research/traditional_assets/database/data/switzerland/switzerland_recreation.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtpa_tvrb" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.09740000000000001</v>
+        <v>-0.0359</v>
+      </c>
+      <c r="E2">
+        <v>0.246</v>
       </c>
       <c r="G2">
-        <v>0.29</v>
+        <v>0.1108930323846909</v>
       </c>
       <c r="H2">
-        <v>0.29</v>
+        <v>0.1108930323846909</v>
       </c>
       <c r="I2">
-        <v>-0.262632911392405</v>
+        <v>0.02011776251226693</v>
       </c>
       <c r="J2">
-        <v>-0.262632911392405</v>
+        <v>0.01815119112839542</v>
       </c>
       <c r="K2">
-        <v>-26.467</v>
+        <v>11.66</v>
       </c>
       <c r="L2">
-        <v>-0.3350253164556962</v>
+        <v>0.1144259077526987</v>
       </c>
       <c r="M2">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.395585738539898e-05</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.0003022631956776363</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>3.395585738539898e-05</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.0003022631956776363</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>33.71</v>
+        <v>39.9</v>
       </c>
       <c r="V2">
-        <v>0.1430814940577249</v>
+        <v>0.1854951185495118</v>
       </c>
       <c r="W2">
-        <v>-0.08304427997402768</v>
+        <v>0.04123791631254318</v>
       </c>
       <c r="X2">
-        <v>0.06515921855771113</v>
+        <v>0.1074940241738651</v>
       </c>
       <c r="Y2">
-        <v>-0.1482034985317388</v>
+        <v>-0.06625610786132194</v>
       </c>
       <c r="Z2">
-        <v>0.2918801887245575</v>
+        <v>0.3419130353086444</v>
       </c>
       <c r="AA2">
-        <v>-0.06887351734936929</v>
+        <v>0.005531179323930605</v>
       </c>
       <c r="AB2">
-        <v>0.05580605118868925</v>
+        <v>0.09557168406635169</v>
       </c>
       <c r="AC2">
-        <v>-0.1246795685380585</v>
+        <v>-0.09004050474242109</v>
       </c>
       <c r="AD2">
-        <v>48.1</v>
+        <v>35.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>48.1</v>
+        <v>35.7</v>
       </c>
       <c r="AG2">
-        <v>14.39</v>
+        <v>-4.199999999999996</v>
       </c>
       <c r="AH2">
-        <v>0.1695452943249912</v>
+        <v>0.1423444976076555</v>
       </c>
       <c r="AI2">
-        <v>0.1445746919146378</v>
+        <v>0.1116322701688555</v>
       </c>
       <c r="AJ2">
-        <v>0.05756230249209968</v>
+        <v>-0.01991465149359884</v>
       </c>
       <c r="AK2">
-        <v>0.04812869995652028</v>
+        <v>-0.01500535905680598</v>
       </c>
       <c r="AL2">
-        <v>0.274</v>
+        <v>0.433</v>
       </c>
       <c r="AM2">
-        <v>0.04600000000000001</v>
+        <v>0.428</v>
       </c>
       <c r="AN2">
-        <v>4.011676396997498</v>
+        <v>1.274544805426633</v>
       </c>
       <c r="AO2">
-        <v>-75.72262773722626</v>
+        <v>4.734411085450346</v>
       </c>
       <c r="AP2">
-        <v>1.200166805671393</v>
+        <v>-0.1499464476972508</v>
       </c>
       <c r="AQ2">
-        <v>-451.0434782608694</v>
+        <v>4.789719626168224</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +721,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0138</v>
+        <v>0.05019999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.746</v>
       </c>
       <c r="G3">
-        <v>0.3372549019607843</v>
+        <v>0.1921331316187595</v>
       </c>
       <c r="H3">
-        <v>0.3372549019607843</v>
+        <v>0.1921331316187595</v>
       </c>
       <c r="I3">
-        <v>-0.006823529411764706</v>
+        <v>0.1340393343419062</v>
       </c>
       <c r="J3">
-        <v>-0.006823529411764706</v>
+        <v>0.1152682657359339</v>
       </c>
       <c r="K3">
-        <v>-0.367</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L3">
-        <v>-0.007196078431372549</v>
+        <v>0.1240544629349471</v>
       </c>
       <c r="M3">
-        <v>0.008</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0001122019635343619</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.0217983651226158</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.008</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0001122019635343619</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.0217983651226158</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>25.3</v>
+        <v>24.4</v>
       </c>
       <c r="V3">
-        <v>0.3548387096774194</v>
+        <v>0.359882005899705</v>
       </c>
       <c r="W3">
-        <v>-0.002759398496240601</v>
+        <v>0.05828002842928216</v>
       </c>
       <c r="X3">
-        <v>0.07015152950555749</v>
+        <v>0.1134616679858441</v>
       </c>
       <c r="Y3">
-        <v>-0.07291092800179809</v>
+        <v>-0.05518163955656194</v>
       </c>
       <c r="Z3">
-        <v>0.4272824001541568</v>
+        <v>0.4585851157563186</v>
       </c>
       <c r="AA3">
-        <v>-0.002915574024581305</v>
+        <v>0.05286031098554332</v>
       </c>
       <c r="AB3">
-        <v>0.05568219330842759</v>
+        <v>0.09466911577748599</v>
       </c>
       <c r="AC3">
-        <v>-0.05859776733300889</v>
+        <v>-0.04180880479194267</v>
       </c>
       <c r="AD3">
-        <v>28.8</v>
+        <v>22.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>28.8</v>
+        <v>22.8</v>
       </c>
       <c r="AG3">
-        <v>3.5</v>
+        <v>-1.599999999999998</v>
       </c>
       <c r="AH3">
-        <v>0.2877122877122877</v>
+        <v>0.2516556291390729</v>
       </c>
       <c r="AI3">
-        <v>0.1693121693121693</v>
+        <v>0.1349112426035503</v>
       </c>
       <c r="AJ3">
-        <v>0.04679144385026738</v>
+        <v>-0.02416918429003018</v>
       </c>
       <c r="AK3">
-        <v>0.02417127071823204</v>
+        <v>-0.01106500691562931</v>
       </c>
       <c r="AL3">
-        <v>0.246</v>
+        <v>0.354</v>
       </c>
       <c r="AM3">
-        <v>0.212</v>
+        <v>0.349</v>
       </c>
       <c r="AN3">
-        <v>2.149253731343284</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AO3">
-        <v>-1.414634146341463</v>
+        <v>25.02824858757062</v>
       </c>
       <c r="AP3">
-        <v>0.2611940298507462</v>
+        <v>-0.07407407407407397</v>
       </c>
       <c r="AQ3">
-        <v>-1.641509433962264</v>
+        <v>25.38681948424069</v>
       </c>
     </row>
     <row r="4">
@@ -850,25 +852,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.181</v>
+        <v>-0.122</v>
+      </c>
+      <c r="E4">
+        <v>-0.254</v>
       </c>
       <c r="G4">
-        <v>0.2039285714285714</v>
+        <v>-0.03910614525139665</v>
       </c>
       <c r="H4">
-        <v>0.2039285714285714</v>
+        <v>-0.03910614525139665</v>
       </c>
       <c r="I4">
-        <v>-0.7285714285714285</v>
+        <v>-0.1902234636871508</v>
       </c>
       <c r="J4">
-        <v>-0.7285714285714285</v>
+        <v>-0.1796728180236285</v>
       </c>
       <c r="K4">
-        <v>-26.1</v>
+        <v>3.46</v>
       </c>
       <c r="L4">
-        <v>-0.9321428571428572</v>
+        <v>0.09664804469273744</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,7 +882,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -886,79 +891,8791 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8.41</v>
+        <v>15.5</v>
       </c>
       <c r="V4">
-        <v>0.05118685331710286</v>
+        <v>0.1052274270196877</v>
       </c>
       <c r="W4">
-        <v>-0.1633291614518148</v>
+        <v>0.0241958041958042</v>
       </c>
       <c r="X4">
-        <v>0.06016690760986477</v>
+        <v>0.1015263803618861</v>
       </c>
       <c r="Y4">
-        <v>-0.2234960690616795</v>
+        <v>-0.07733057616608192</v>
       </c>
       <c r="Z4">
-        <v>0.1850627891606081</v>
+        <v>0.2326336993956722</v>
       </c>
       <c r="AA4">
-        <v>-0.1348314606741573</v>
+        <v>-0.04179795233768211</v>
       </c>
       <c r="AB4">
-        <v>0.05592990906895092</v>
+        <v>0.09647425235521739</v>
       </c>
       <c r="AC4">
-        <v>-0.1907613697431082</v>
+        <v>-0.1382722046928995</v>
       </c>
       <c r="AD4">
-        <v>19.3</v>
+        <v>12.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>19.3</v>
+        <v>12.9</v>
       </c>
       <c r="AG4">
-        <v>10.89</v>
+        <v>-2.6</v>
       </c>
       <c r="AH4">
-        <v>0.105119825708061</v>
+        <v>0.08052434456928838</v>
       </c>
       <c r="AI4">
-        <v>0.1186961869618696</v>
+        <v>0.08554376657824933</v>
       </c>
       <c r="AJ4">
-        <v>0.06216108225355329</v>
+        <v>-0.01796821008984105</v>
       </c>
       <c r="AK4">
-        <v>0.07062714832349699</v>
+        <v>-0.01921655580192165</v>
       </c>
       <c r="AL4">
-        <v>0.028</v>
+        <v>0.079</v>
       </c>
       <c r="AM4">
-        <v>-0.166</v>
+        <v>0.079</v>
       </c>
       <c r="AN4">
-        <v>-13.68794326241135</v>
+        <v>2.012480499219969</v>
       </c>
       <c r="AO4">
-        <v>-728.5714285714286</v>
+        <v>-86.20253164556962</v>
       </c>
       <c r="AP4">
-        <v>-7.72340425531915</v>
+        <v>-0.4056162246489859</v>
       </c>
       <c r="AQ4">
-        <v>122.8915662650602</v>
+        <v>-86.20253164556962</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Téléverbier SA (ENXTPA:TVRB)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTPA:TVRB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.251655629139073</v>
+      </c>
+      <c r="F2">
+        <v>0.18</v>
+      </c>
+      <c r="G2">
+        <v>67.8</v>
+      </c>
+      <c r="H2">
+        <v>73.6127799537657</v>
+      </c>
+      <c r="I2">
+        <v>66.2</v>
+      </c>
+      <c r="J2">
+        <v>65.5207799537657</v>
+      </c>
+      <c r="K2">
+        <v>22.8</v>
+      </c>
+      <c r="L2">
+        <v>16.308</v>
+      </c>
+      <c r="M2">
+        <v>0.094669115777486</v>
+      </c>
+      <c r="N2">
+        <v>0.09542495768847541</v>
+      </c>
+      <c r="O2">
+        <v>0.038786</v>
+      </c>
+      <c r="P2">
+        <v>0.038786</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.113461667985844</v>
+      </c>
+      <c r="T2">
+        <v>0.107857899620092</v>
+      </c>
+      <c r="U2">
+        <v>1.26240504377076</v>
+      </c>
+      <c r="V2">
+        <v>1.16765460971416</v>
+      </c>
+      <c r="W2">
+        <v>10.63045880541645</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>67.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0473</v>
+      </c>
+      <c r="AD2">
+        <v>0.18</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>21.6</v>
+      </c>
+      <c r="AH2">
+        <v>13.4</v>
+      </c>
+      <c r="AI2">
+        <v>15.4</v>
+      </c>
+      <c r="AJ2">
+        <v>22.8</v>
+      </c>
+      <c r="AK2">
+        <v>22.8</v>
+      </c>
+      <c r="AL2">
+        <v>0.354</v>
+      </c>
+      <c r="AM2">
+        <v>22.8</v>
+      </c>
+      <c r="AN2">
+        <v>24.4</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09732364374584063</v>
+      </c>
+      <c r="C2">
+        <v>88.27450546622859</v>
+      </c>
+      <c r="D2">
+        <v>63.8745054662286</v>
+      </c>
+      <c r="E2">
+        <v>-22.8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>24.4</v>
+      </c>
+      <c r="H2">
+        <v>67.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>21.6</v>
+      </c>
+      <c r="K2">
+        <v>13.4</v>
+      </c>
+      <c r="L2">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="O2">
+        <v>1.476000000000001</v>
+      </c>
+      <c r="P2">
+        <v>6.724</v>
+      </c>
+      <c r="Q2">
+        <v>20.124</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09732364374584063</v>
+      </c>
+      <c r="T2">
+        <v>0.9895378048425111</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.18</v>
+      </c>
+      <c r="W2">
+        <v>0.037474</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09720504118709809</v>
+      </c>
+      <c r="C3">
+        <v>87.46891473456711</v>
+      </c>
+      <c r="D3">
+        <v>63.97491473456711</v>
+      </c>
+      <c r="E3">
+        <v>-21.894</v>
+      </c>
+      <c r="F3">
+        <v>0.9059999999999999</v>
+      </c>
+      <c r="G3">
+        <v>24.4</v>
+      </c>
+      <c r="H3">
+        <v>67.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>21.6</v>
+      </c>
+      <c r="K3">
+        <v>13.4</v>
+      </c>
+      <c r="L3">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M3">
+        <v>0.0414042</v>
+      </c>
+      <c r="N3">
+        <v>8.158595800000001</v>
+      </c>
+      <c r="O3">
+        <v>1.468547244</v>
+      </c>
+      <c r="P3">
+        <v>6.690048556</v>
+      </c>
+      <c r="Q3">
+        <v>20.090048556</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09780838503747283</v>
+      </c>
+      <c r="T3">
+        <v>0.9977339765593883</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.18</v>
+      </c>
+      <c r="W3">
+        <v>0.037474</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>198.0475410707126</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09708643862835559</v>
+      </c>
+      <c r="C4">
+        <v>86.66364018209966</v>
+      </c>
+      <c r="D4">
+        <v>64.07564018209966</v>
+      </c>
+      <c r="E4">
+        <v>-20.988</v>
+      </c>
+      <c r="F4">
+        <v>1.812</v>
+      </c>
+      <c r="G4">
+        <v>24.4</v>
+      </c>
+      <c r="H4">
+        <v>67.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>21.6</v>
+      </c>
+      <c r="K4">
+        <v>13.4</v>
+      </c>
+      <c r="L4">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M4">
+        <v>0.0828084</v>
+      </c>
+      <c r="N4">
+        <v>8.117191600000002</v>
+      </c>
+      <c r="O4">
+        <v>1.461094488000001</v>
+      </c>
+      <c r="P4">
+        <v>6.656097112000001</v>
+      </c>
+      <c r="Q4">
+        <v>20.056097112</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09830301900852612</v>
+      </c>
+      <c r="T4">
+        <v>1.006097417086814</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.18</v>
+      </c>
+      <c r="W4">
+        <v>0.037474</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>99.02377053535633</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09696783606961308</v>
+      </c>
+      <c r="C5">
+        <v>85.85868330460839</v>
+      </c>
+      <c r="D5">
+        <v>64.1766833046084</v>
+      </c>
+      <c r="E5">
+        <v>-20.082</v>
+      </c>
+      <c r="F5">
+        <v>2.718</v>
+      </c>
+      <c r="G5">
+        <v>24.4</v>
+      </c>
+      <c r="H5">
+        <v>67.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>21.6</v>
+      </c>
+      <c r="K5">
+        <v>13.4</v>
+      </c>
+      <c r="L5">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M5">
+        <v>0.1242126</v>
+      </c>
+      <c r="N5">
+        <v>8.075787400000001</v>
+      </c>
+      <c r="O5">
+        <v>1.453641732000001</v>
+      </c>
+      <c r="P5">
+        <v>6.622145668000001</v>
+      </c>
+      <c r="Q5">
+        <v>20.022145668</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09880785161815782</v>
+      </c>
+      <c r="T5">
+        <v>1.014633299686971</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.18</v>
+      </c>
+      <c r="W5">
+        <v>0.037474</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>66.01584702357088</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09684923351087056</v>
+      </c>
+      <c r="C6">
+        <v>85.05404560732541</v>
+      </c>
+      <c r="D6">
+        <v>64.27804560732541</v>
+      </c>
+      <c r="E6">
+        <v>-19.176</v>
+      </c>
+      <c r="F6">
+        <v>3.624</v>
+      </c>
+      <c r="G6">
+        <v>24.4</v>
+      </c>
+      <c r="H6">
+        <v>67.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>21.6</v>
+      </c>
+      <c r="K6">
+        <v>13.4</v>
+      </c>
+      <c r="L6">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M6">
+        <v>0.1656168</v>
+      </c>
+      <c r="N6">
+        <v>8.034383200000001</v>
+      </c>
+      <c r="O6">
+        <v>1.446188976</v>
+      </c>
+      <c r="P6">
+        <v>6.588194224</v>
+      </c>
+      <c r="Q6">
+        <v>19.988194224</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09932320157382352</v>
+      </c>
+      <c r="T6">
+        <v>1.02334701317463</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.18</v>
+      </c>
+      <c r="W6">
+        <v>0.037474</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>49.51188526767816</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09673063095212805</v>
+      </c>
+      <c r="C7">
+        <v>84.24972860500736</v>
+      </c>
+      <c r="D7">
+        <v>64.37972860500737</v>
+      </c>
+      <c r="E7">
+        <v>-18.27</v>
+      </c>
+      <c r="F7">
+        <v>4.53</v>
+      </c>
+      <c r="G7">
+        <v>24.4</v>
+      </c>
+      <c r="H7">
+        <v>67.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>21.6</v>
+      </c>
+      <c r="K7">
+        <v>13.4</v>
+      </c>
+      <c r="L7">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M7">
+        <v>0.207021</v>
+      </c>
+      <c r="N7">
+        <v>7.992979000000001</v>
+      </c>
+      <c r="O7">
+        <v>1.43873622</v>
+      </c>
+      <c r="P7">
+        <v>6.554242780000001</v>
+      </c>
+      <c r="Q7">
+        <v>19.95424278</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09984940100224006</v>
+      </c>
+      <c r="T7">
+        <v>1.03224417326203</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.18</v>
+      </c>
+      <c r="W7">
+        <v>0.037474</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>39.60950821414252</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09661202839338555</v>
+      </c>
+      <c r="C8">
+        <v>83.44573382201115</v>
+      </c>
+      <c r="D8">
+        <v>64.48173382201114</v>
+      </c>
+      <c r="E8">
+        <v>-17.364</v>
+      </c>
+      <c r="F8">
+        <v>5.435999999999999</v>
+      </c>
+      <c r="G8">
+        <v>24.4</v>
+      </c>
+      <c r="H8">
+        <v>67.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>21.6</v>
+      </c>
+      <c r="K8">
+        <v>13.4</v>
+      </c>
+      <c r="L8">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M8">
+        <v>0.2484252</v>
+      </c>
+      <c r="N8">
+        <v>7.951574800000001</v>
+      </c>
+      <c r="O8">
+        <v>1.431283464000001</v>
+      </c>
+      <c r="P8">
+        <v>6.520291336000001</v>
+      </c>
+      <c r="Q8">
+        <v>19.920291336</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1003867961631761</v>
+      </c>
+      <c r="T8">
+        <v>1.041330634627885</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.18</v>
+      </c>
+      <c r="W8">
+        <v>0.037474</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>33.00792351178544</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09649342583464302</v>
+      </c>
+      <c r="C9">
+        <v>82.64206279236983</v>
+      </c>
+      <c r="D9">
+        <v>64.58406279236982</v>
+      </c>
+      <c r="E9">
+        <v>-16.458</v>
+      </c>
+      <c r="F9">
+        <v>6.342000000000001</v>
+      </c>
+      <c r="G9">
+        <v>24.4</v>
+      </c>
+      <c r="H9">
+        <v>67.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>21.6</v>
+      </c>
+      <c r="K9">
+        <v>13.4</v>
+      </c>
+      <c r="L9">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M9">
+        <v>0.2898294000000001</v>
+      </c>
+      <c r="N9">
+        <v>7.910170600000001</v>
+      </c>
+      <c r="O9">
+        <v>1.423830708000001</v>
+      </c>
+      <c r="P9">
+        <v>6.486339892</v>
+      </c>
+      <c r="Q9">
+        <v>19.886339892</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1009357482092936</v>
+      </c>
+      <c r="T9">
+        <v>1.050612503765049</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.18</v>
+      </c>
+      <c r="W9">
+        <v>0.037474</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>28.29250586724466</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09637482327590052</v>
+      </c>
+      <c r="C10">
+        <v>81.83871705986964</v>
+      </c>
+      <c r="D10">
+        <v>64.68671705986964</v>
+      </c>
+      <c r="E10">
+        <v>-15.552</v>
+      </c>
+      <c r="F10">
+        <v>7.247999999999999</v>
+      </c>
+      <c r="G10">
+        <v>24.4</v>
+      </c>
+      <c r="H10">
+        <v>67.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>21.6</v>
+      </c>
+      <c r="K10">
+        <v>13.4</v>
+      </c>
+      <c r="L10">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M10">
+        <v>0.3312336</v>
+      </c>
+      <c r="N10">
+        <v>7.868766400000001</v>
+      </c>
+      <c r="O10">
+        <v>1.416377952000001</v>
+      </c>
+      <c r="P10">
+        <v>6.452388448000001</v>
+      </c>
+      <c r="Q10">
+        <v>19.852388448</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.101496633995544</v>
+      </c>
+      <c r="T10">
+        <v>1.060096152666064</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.18</v>
+      </c>
+      <c r="W10">
+        <v>0.037474</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>24.75594263383908</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.096256220717158</v>
+      </c>
+      <c r="C11">
+        <v>81.03569817812777</v>
+      </c>
+      <c r="D11">
+        <v>64.78969817812778</v>
+      </c>
+      <c r="E11">
+        <v>-14.646</v>
+      </c>
+      <c r="F11">
+        <v>8.154</v>
+      </c>
+      <c r="G11">
+        <v>24.4</v>
+      </c>
+      <c r="H11">
+        <v>67.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>21.6</v>
+      </c>
+      <c r="K11">
+        <v>13.4</v>
+      </c>
+      <c r="L11">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M11">
+        <v>0.3726378</v>
+      </c>
+      <c r="N11">
+        <v>7.827362200000001</v>
+      </c>
+      <c r="O11">
+        <v>1.408925196000001</v>
+      </c>
+      <c r="P11">
+        <v>6.418437004000001</v>
+      </c>
+      <c r="Q11">
+        <v>19.818437004</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1020698469419319</v>
+      </c>
+      <c r="T11">
+        <v>1.069788233411058</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.18</v>
+      </c>
+      <c r="W11">
+        <v>0.037474</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>22.00528234119029</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.0961376181584155</v>
+      </c>
+      <c r="C12">
+        <v>80.23300771067051</v>
+      </c>
+      <c r="D12">
+        <v>64.8930077106705</v>
+      </c>
+      <c r="E12">
+        <v>-13.74</v>
+      </c>
+      <c r="F12">
+        <v>9.06</v>
+      </c>
+      <c r="G12">
+        <v>24.4</v>
+      </c>
+      <c r="H12">
+        <v>67.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>21.6</v>
+      </c>
+      <c r="K12">
+        <v>13.4</v>
+      </c>
+      <c r="L12">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M12">
+        <v>0.4140420000000001</v>
+      </c>
+      <c r="N12">
+        <v>7.785958000000001</v>
+      </c>
+      <c r="O12">
+        <v>1.40147244</v>
+      </c>
+      <c r="P12">
+        <v>6.38448556</v>
+      </c>
+      <c r="Q12">
+        <v>19.78448556</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.102655797953795</v>
+      </c>
+      <c r="T12">
+        <v>1.079695693728162</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.18</v>
+      </c>
+      <c r="W12">
+        <v>0.037474</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>19.80475410707126</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09601901559967298</v>
+      </c>
+      <c r="C13">
+        <v>79.43064723101246</v>
+      </c>
+      <c r="D13">
+        <v>64.99664723101245</v>
+      </c>
+      <c r="E13">
+        <v>-12.834</v>
+      </c>
+      <c r="F13">
+        <v>9.965999999999999</v>
+      </c>
+      <c r="G13">
+        <v>24.4</v>
+      </c>
+      <c r="H13">
+        <v>67.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>21.6</v>
+      </c>
+      <c r="K13">
+        <v>13.4</v>
+      </c>
+      <c r="L13">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M13">
+        <v>0.4554462</v>
+      </c>
+      <c r="N13">
+        <v>7.744553800000001</v>
+      </c>
+      <c r="O13">
+        <v>1.394019684000001</v>
+      </c>
+      <c r="P13">
+        <v>6.350534116</v>
+      </c>
+      <c r="Q13">
+        <v>19.750534116</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1032549164041269</v>
+      </c>
+      <c r="T13">
+        <v>1.089825793602954</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.18</v>
+      </c>
+      <c r="W13">
+        <v>0.037474</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>18.00432191551933</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09590041304093046</v>
+      </c>
+      <c r="C14">
+        <v>78.62861832273644</v>
+      </c>
+      <c r="D14">
+        <v>65.10061832273645</v>
+      </c>
+      <c r="E14">
+        <v>-11.928</v>
+      </c>
+      <c r="F14">
+        <v>10.872</v>
+      </c>
+      <c r="G14">
+        <v>24.4</v>
+      </c>
+      <c r="H14">
+        <v>67.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>21.6</v>
+      </c>
+      <c r="K14">
+        <v>13.4</v>
+      </c>
+      <c r="L14">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M14">
+        <v>0.4968504</v>
+      </c>
+      <c r="N14">
+        <v>7.703149600000001</v>
+      </c>
+      <c r="O14">
+        <v>1.386566928000001</v>
+      </c>
+      <c r="P14">
+        <v>6.316582672000001</v>
+      </c>
+      <c r="Q14">
+        <v>19.716582672</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1038676511828755</v>
+      </c>
+      <c r="T14">
+        <v>1.100186123020356</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.18</v>
+      </c>
+      <c r="W14">
+        <v>0.037474</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>16.50396175589272</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09578181048218795</v>
+      </c>
+      <c r="C15">
+        <v>77.8269225795742</v>
+      </c>
+      <c r="D15">
+        <v>65.2049225795742</v>
+      </c>
+      <c r="E15">
+        <v>-11.022</v>
+      </c>
+      <c r="F15">
+        <v>11.778</v>
+      </c>
+      <c r="G15">
+        <v>24.4</v>
+      </c>
+      <c r="H15">
+        <v>67.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>21.6</v>
+      </c>
+      <c r="K15">
+        <v>13.4</v>
+      </c>
+      <c r="L15">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M15">
+        <v>0.5382546</v>
+      </c>
+      <c r="N15">
+        <v>7.661745400000001</v>
+      </c>
+      <c r="O15">
+        <v>1.379114172000001</v>
+      </c>
+      <c r="P15">
+        <v>6.282631228000001</v>
+      </c>
+      <c r="Q15">
+        <v>19.682631228</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1044944718186069</v>
+      </c>
+      <c r="T15">
+        <v>1.110784620930111</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.18</v>
+      </c>
+      <c r="W15">
+        <v>0.037474</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>15.23442623620866</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09566320792344543</v>
+      </c>
+      <c r="C16">
+        <v>77.02556160548775</v>
+      </c>
+      <c r="D16">
+        <v>65.30956160548774</v>
+      </c>
+      <c r="E16">
+        <v>-10.116</v>
+      </c>
+      <c r="F16">
+        <v>12.684</v>
+      </c>
+      <c r="G16">
+        <v>24.4</v>
+      </c>
+      <c r="H16">
+        <v>67.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>21.6</v>
+      </c>
+      <c r="K16">
+        <v>13.4</v>
+      </c>
+      <c r="L16">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M16">
+        <v>0.5796588000000001</v>
+      </c>
+      <c r="N16">
+        <v>7.620341200000001</v>
+      </c>
+      <c r="O16">
+        <v>1.371661416000001</v>
+      </c>
+      <c r="P16">
+        <v>6.248679784</v>
+      </c>
+      <c r="Q16">
+        <v>19.648679784</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1051358696784249</v>
+      </c>
+      <c r="T16">
+        <v>1.121629595535442</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.18</v>
+      </c>
+      <c r="W16">
+        <v>0.037474</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>14.14625293362233</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09554460536470294</v>
+      </c>
+      <c r="C17">
+        <v>76.22453701475158</v>
+      </c>
+      <c r="D17">
+        <v>65.41453701475159</v>
+      </c>
+      <c r="E17">
+        <v>-9.210000000000003</v>
+      </c>
+      <c r="F17">
+        <v>13.59</v>
+      </c>
+      <c r="G17">
+        <v>24.4</v>
+      </c>
+      <c r="H17">
+        <v>67.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>21.6</v>
+      </c>
+      <c r="K17">
+        <v>13.4</v>
+      </c>
+      <c r="L17">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M17">
+        <v>0.6210629999999999</v>
+      </c>
+      <c r="N17">
+        <v>7.578937000000002</v>
+      </c>
+      <c r="O17">
+        <v>1.364208660000001</v>
+      </c>
+      <c r="P17">
+        <v>6.214728340000001</v>
+      </c>
+      <c r="Q17">
+        <v>19.61472834</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1057923592525917</v>
+      </c>
+      <c r="T17">
+        <v>1.132729746013839</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.18</v>
+      </c>
+      <c r="W17">
+        <v>0.037474</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>13.20316940471418</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09563592280596041</v>
+      </c>
+      <c r="C18">
+        <v>75.23768187785491</v>
+      </c>
+      <c r="D18">
+        <v>65.33368187785491</v>
+      </c>
+      <c r="E18">
+        <v>-8.304000000000002</v>
+      </c>
+      <c r="F18">
+        <v>14.496</v>
+      </c>
+      <c r="G18">
+        <v>24.4</v>
+      </c>
+      <c r="H18">
+        <v>67.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>21.6</v>
+      </c>
+      <c r="K18">
+        <v>13.4</v>
+      </c>
+      <c r="L18">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M18">
+        <v>0.6856608</v>
+      </c>
+      <c r="N18">
+        <v>7.514339200000001</v>
+      </c>
+      <c r="O18">
+        <v>1.352581056000001</v>
+      </c>
+      <c r="P18">
+        <v>6.161758144</v>
+      </c>
+      <c r="Q18">
+        <v>19.561758144</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1064644795309053</v>
+      </c>
+      <c r="T18">
+        <v>1.144094185789341</v>
+      </c>
+      <c r="U18">
+        <v>0.0473</v>
+      </c>
+      <c r="V18">
+        <v>0.18</v>
+      </c>
+      <c r="W18">
+        <v>0.038786</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>11.95926615609351</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09553044024721789</v>
+      </c>
+      <c r="C19">
+        <v>74.42509715770412</v>
+      </c>
+      <c r="D19">
+        <v>65.42709715770411</v>
+      </c>
+      <c r="E19">
+        <v>-7.398</v>
+      </c>
+      <c r="F19">
+        <v>15.402</v>
+      </c>
+      <c r="G19">
+        <v>24.4</v>
+      </c>
+      <c r="H19">
+        <v>67.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>21.6</v>
+      </c>
+      <c r="K19">
+        <v>13.4</v>
+      </c>
+      <c r="L19">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M19">
+        <v>0.7285146000000001</v>
+      </c>
+      <c r="N19">
+        <v>7.471485400000001</v>
+      </c>
+      <c r="O19">
+        <v>1.344867372</v>
+      </c>
+      <c r="P19">
+        <v>6.126618028</v>
+      </c>
+      <c r="Q19">
+        <v>19.526618028</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1071527954785758</v>
+      </c>
+      <c r="T19">
+        <v>1.155732467487145</v>
+      </c>
+      <c r="U19">
+        <v>0.0473</v>
+      </c>
+      <c r="V19">
+        <v>0.18</v>
+      </c>
+      <c r="W19">
+        <v>0.038786</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>11.25577991161742</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09542495768847539</v>
+      </c>
+      <c r="C20">
+        <v>73.61277995376574</v>
+      </c>
+      <c r="D20">
+        <v>65.52077995376573</v>
+      </c>
+      <c r="E20">
+        <v>-6.492000000000001</v>
+      </c>
+      <c r="F20">
+        <v>16.308</v>
+      </c>
+      <c r="G20">
+        <v>24.4</v>
+      </c>
+      <c r="H20">
+        <v>67.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>21.6</v>
+      </c>
+      <c r="K20">
+        <v>13.4</v>
+      </c>
+      <c r="L20">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M20">
+        <v>0.7713684000000001</v>
+      </c>
+      <c r="N20">
+        <v>7.428631600000001</v>
+      </c>
+      <c r="O20">
+        <v>1.337153688000001</v>
+      </c>
+      <c r="P20">
+        <v>6.091477912</v>
+      </c>
+      <c r="Q20">
+        <v>19.491477912</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1078578996200919</v>
+      </c>
+      <c r="T20">
+        <v>1.167654609714163</v>
+      </c>
+      <c r="U20">
+        <v>0.0473</v>
+      </c>
+      <c r="V20">
+        <v>0.18</v>
+      </c>
+      <c r="W20">
+        <v>0.038786</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>10.63045880541645</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09591151512973288</v>
+      </c>
+      <c r="C21">
+        <v>72.27687173995847</v>
+      </c>
+      <c r="D21">
+        <v>65.09087173995847</v>
+      </c>
+      <c r="E21">
+        <v>-5.586000000000002</v>
+      </c>
+      <c r="F21">
+        <v>17.214</v>
+      </c>
+      <c r="G21">
+        <v>24.4</v>
+      </c>
+      <c r="H21">
+        <v>67.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>21.6</v>
+      </c>
+      <c r="K21">
+        <v>13.4</v>
+      </c>
+      <c r="L21">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M21">
+        <v>0.8796354</v>
+      </c>
+      <c r="N21">
+        <v>7.320364600000001</v>
+      </c>
+      <c r="O21">
+        <v>1.317665628000001</v>
+      </c>
+      <c r="P21">
+        <v>6.002698972000001</v>
+      </c>
+      <c r="Q21">
+        <v>19.402698972</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.108580413740411</v>
+      </c>
+      <c r="T21">
+        <v>1.17987112582333</v>
+      </c>
+      <c r="U21">
+        <v>0.0511</v>
+      </c>
+      <c r="V21">
+        <v>0.18</v>
+      </c>
+      <c r="W21">
+        <v>0.04190199999999999</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>9.322044110548532</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09583719257099037</v>
+      </c>
+      <c r="C22">
+        <v>71.43617559256555</v>
+      </c>
+      <c r="D22">
+        <v>65.15617559256556</v>
+      </c>
+      <c r="E22">
+        <v>-4.68</v>
+      </c>
+      <c r="F22">
+        <v>18.12</v>
+      </c>
+      <c r="G22">
+        <v>24.4</v>
+      </c>
+      <c r="H22">
+        <v>67.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>21.6</v>
+      </c>
+      <c r="K22">
+        <v>13.4</v>
+      </c>
+      <c r="L22">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M22">
+        <v>0.9259320000000001</v>
+      </c>
+      <c r="N22">
+        <v>7.274068000000001</v>
+      </c>
+      <c r="O22">
+        <v>1.30933224</v>
+      </c>
+      <c r="P22">
+        <v>5.96473576</v>
+      </c>
+      <c r="Q22">
+        <v>19.36473576</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.109320990713738</v>
+      </c>
+      <c r="T22">
+        <v>1.192393054835226</v>
+      </c>
+      <c r="U22">
+        <v>0.0511</v>
+      </c>
+      <c r="V22">
+        <v>0.18</v>
+      </c>
+      <c r="W22">
+        <v>0.04190199999999999</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>8.855941905021103</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09576287001224784</v>
+      </c>
+      <c r="C23">
+        <v>70.5956106118292</v>
+      </c>
+      <c r="D23">
+        <v>65.22161061182921</v>
+      </c>
+      <c r="E23">
+        <v>-3.774000000000001</v>
+      </c>
+      <c r="F23">
+        <v>19.026</v>
+      </c>
+      <c r="G23">
+        <v>24.4</v>
+      </c>
+      <c r="H23">
+        <v>67.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>21.6</v>
+      </c>
+      <c r="K23">
+        <v>13.4</v>
+      </c>
+      <c r="L23">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M23">
+        <v>0.9722286</v>
+      </c>
+      <c r="N23">
+        <v>7.227771400000001</v>
+      </c>
+      <c r="O23">
+        <v>1.300998852</v>
+      </c>
+      <c r="P23">
+        <v>5.926772548000001</v>
+      </c>
+      <c r="Q23">
+        <v>19.326772548</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1100803164711998</v>
+      </c>
+      <c r="T23">
+        <v>1.205231994708182</v>
+      </c>
+      <c r="U23">
+        <v>0.0511</v>
+      </c>
+      <c r="V23">
+        <v>0.18</v>
+      </c>
+      <c r="W23">
+        <v>0.04190199999999999</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>8.434230385734384</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09568854745350533</v>
+      </c>
+      <c r="C24">
+        <v>69.75517719333068</v>
+      </c>
+      <c r="D24">
+        <v>65.28717719333068</v>
+      </c>
+      <c r="E24">
+        <v>-2.868000000000002</v>
+      </c>
+      <c r="F24">
+        <v>19.932</v>
+      </c>
+      <c r="G24">
+        <v>24.4</v>
+      </c>
+      <c r="H24">
+        <v>67.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>21.6</v>
+      </c>
+      <c r="K24">
+        <v>13.4</v>
+      </c>
+      <c r="L24">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M24">
+        <v>1.0185252</v>
+      </c>
+      <c r="N24">
+        <v>7.181474800000001</v>
+      </c>
+      <c r="O24">
+        <v>1.292665464000001</v>
+      </c>
+      <c r="P24">
+        <v>5.888809336</v>
+      </c>
+      <c r="Q24">
+        <v>19.288809336</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1108591121198786</v>
+      </c>
+      <c r="T24">
+        <v>1.218400138167625</v>
+      </c>
+      <c r="U24">
+        <v>0.0511</v>
+      </c>
+      <c r="V24">
+        <v>0.18</v>
+      </c>
+      <c r="W24">
+        <v>0.04190199999999999</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>8.050856277291913</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09597256489476283</v>
+      </c>
+      <c r="C25">
+        <v>68.59932793229251</v>
+      </c>
+      <c r="D25">
+        <v>65.0373279322925</v>
+      </c>
+      <c r="E25">
+        <v>-1.962</v>
+      </c>
+      <c r="F25">
+        <v>20.838</v>
+      </c>
+      <c r="G25">
+        <v>24.4</v>
+      </c>
+      <c r="H25">
+        <v>67.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>21.6</v>
+      </c>
+      <c r="K25">
+        <v>13.4</v>
+      </c>
+      <c r="L25">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M25">
+        <v>1.104414</v>
+      </c>
+      <c r="N25">
+        <v>7.095586000000001</v>
+      </c>
+      <c r="O25">
+        <v>1.277205480000001</v>
+      </c>
+      <c r="P25">
+        <v>5.81838052</v>
+      </c>
+      <c r="Q25">
+        <v>19.21838052</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1116581362269647</v>
+      </c>
+      <c r="T25">
+        <v>1.231910311327313</v>
+      </c>
+      <c r="U25">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.18</v>
+      </c>
+      <c r="W25">
+        <v>0.04346</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>7.424751949902844</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.0959138223360203</v>
+      </c>
+      <c r="C26">
+        <v>67.74484659755339</v>
+      </c>
+      <c r="D26">
+        <v>65.08884659755338</v>
+      </c>
+      <c r="E26">
+        <v>-1.056000000000004</v>
+      </c>
+      <c r="F26">
+        <v>21.744</v>
+      </c>
+      <c r="G26">
+        <v>24.4</v>
+      </c>
+      <c r="H26">
+        <v>67.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>21.6</v>
+      </c>
+      <c r="K26">
+        <v>13.4</v>
+      </c>
+      <c r="L26">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M26">
+        <v>1.152432</v>
+      </c>
+      <c r="N26">
+        <v>7.047568000000001</v>
+      </c>
+      <c r="O26">
+        <v>1.268562240000001</v>
+      </c>
+      <c r="P26">
+        <v>5.77900576</v>
+      </c>
+      <c r="Q26">
+        <v>19.17900576</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1124781872842372</v>
+      </c>
+      <c r="T26">
+        <v>1.245776015359624</v>
+      </c>
+      <c r="U26">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.18</v>
+      </c>
+      <c r="W26">
+        <v>0.04346</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>7.11538728532356</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09585507977727779</v>
+      </c>
+      <c r="C27">
+        <v>66.89044694750513</v>
+      </c>
+      <c r="D27">
+        <v>65.14044694750513</v>
+      </c>
+      <c r="E27">
+        <v>-0.1500000000000021</v>
+      </c>
+      <c r="F27">
+        <v>22.65</v>
+      </c>
+      <c r="G27">
+        <v>24.4</v>
+      </c>
+      <c r="H27">
+        <v>67.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>21.6</v>
+      </c>
+      <c r="K27">
+        <v>13.4</v>
+      </c>
+      <c r="L27">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M27">
+        <v>1.20045</v>
+      </c>
+      <c r="N27">
+        <v>6.999550000000001</v>
+      </c>
+      <c r="O27">
+        <v>1.259919</v>
+      </c>
+      <c r="P27">
+        <v>5.739631000000001</v>
+      </c>
+      <c r="Q27">
+        <v>19.139631</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1133201063697037</v>
+      </c>
+      <c r="T27">
+        <v>1.260011471499464</v>
+      </c>
+      <c r="U27">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.18</v>
+      </c>
+      <c r="W27">
+        <v>0.04346</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>6.830771793910618</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09579633721853528</v>
+      </c>
+      <c r="C28">
+        <v>66.03612917657286</v>
+      </c>
+      <c r="D28">
+        <v>65.19212917657286</v>
+      </c>
+      <c r="E28">
+        <v>0.7560000000000002</v>
+      </c>
+      <c r="F28">
+        <v>23.556</v>
+      </c>
+      <c r="G28">
+        <v>24.4</v>
+      </c>
+      <c r="H28">
+        <v>67.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>21.6</v>
+      </c>
+      <c r="K28">
+        <v>13.4</v>
+      </c>
+      <c r="L28">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M28">
+        <v>1.248468</v>
+      </c>
+      <c r="N28">
+        <v>6.951532000000001</v>
+      </c>
+      <c r="O28">
+        <v>1.251275760000001</v>
+      </c>
+      <c r="P28">
+        <v>5.700256240000001</v>
+      </c>
+      <c r="Q28">
+        <v>19.10025624</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1141847800250477</v>
+      </c>
+      <c r="T28">
+        <v>1.274631669697137</v>
+      </c>
+      <c r="U28">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.18</v>
+      </c>
+      <c r="W28">
+        <v>0.04346</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>6.568049801837132</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09573759465979277</v>
+      </c>
+      <c r="C29">
+        <v>65.18189347979926</v>
+      </c>
+      <c r="D29">
+        <v>65.24389347979927</v>
+      </c>
+      <c r="E29">
+        <v>1.661999999999999</v>
+      </c>
+      <c r="F29">
+        <v>24.462</v>
+      </c>
+      <c r="G29">
+        <v>24.4</v>
+      </c>
+      <c r="H29">
+        <v>67.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>21.6</v>
+      </c>
+      <c r="K29">
+        <v>13.4</v>
+      </c>
+      <c r="L29">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M29">
+        <v>1.296486</v>
+      </c>
+      <c r="N29">
+        <v>6.903514000000001</v>
+      </c>
+      <c r="O29">
+        <v>1.242632520000001</v>
+      </c>
+      <c r="P29">
+        <v>5.66088148</v>
+      </c>
+      <c r="Q29">
+        <v>19.06088148</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1150731433695791</v>
+      </c>
+      <c r="T29">
+        <v>1.289652421270089</v>
+      </c>
+      <c r="U29">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.18</v>
+      </c>
+      <c r="W29">
+        <v>0.04346</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>6.324788698065387</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09613805210105025</v>
+      </c>
+      <c r="C30">
+        <v>63.9246291215997</v>
+      </c>
+      <c r="D30">
+        <v>64.8926291215997</v>
+      </c>
+      <c r="E30">
+        <v>2.568000000000001</v>
+      </c>
+      <c r="F30">
+        <v>25.368</v>
+      </c>
+      <c r="G30">
+        <v>24.4</v>
+      </c>
+      <c r="H30">
+        <v>67.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>21.6</v>
+      </c>
+      <c r="K30">
+        <v>13.4</v>
+      </c>
+      <c r="L30">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M30">
+        <v>1.39524</v>
+      </c>
+      <c r="N30">
+        <v>6.804760000000001</v>
+      </c>
+      <c r="O30">
+        <v>1.2248568</v>
+      </c>
+      <c r="P30">
+        <v>5.5799032</v>
+      </c>
+      <c r="Q30">
+        <v>18.9799032</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1159861834736809</v>
+      </c>
+      <c r="T30">
+        <v>1.30509041594229</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.18</v>
+      </c>
+      <c r="W30">
+        <v>0.04509999999999999</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.877125082423096</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09609570954230773</v>
+      </c>
+      <c r="C31">
+        <v>63.05559130480034</v>
+      </c>
+      <c r="D31">
+        <v>64.92959130480034</v>
+      </c>
+      <c r="E31">
+        <v>3.473999999999997</v>
+      </c>
+      <c r="F31">
+        <v>26.274</v>
+      </c>
+      <c r="G31">
+        <v>24.4</v>
+      </c>
+      <c r="H31">
+        <v>67.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>21.6</v>
+      </c>
+      <c r="K31">
+        <v>13.4</v>
+      </c>
+      <c r="L31">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M31">
+        <v>1.44507</v>
+      </c>
+      <c r="N31">
+        <v>6.754930000000002</v>
+      </c>
+      <c r="O31">
+        <v>1.215887400000001</v>
+      </c>
+      <c r="P31">
+        <v>5.539042600000001</v>
+      </c>
+      <c r="Q31">
+        <v>18.9390426</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1169249430173348</v>
+      </c>
+      <c r="T31">
+        <v>1.320963283703848</v>
+      </c>
+      <c r="U31">
+        <v>0.055</v>
+      </c>
+      <c r="V31">
+        <v>0.18</v>
+      </c>
+      <c r="W31">
+        <v>0.04509999999999999</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.674465596822301</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09605336698356523</v>
+      </c>
+      <c r="C32">
+        <v>62.18659561856724</v>
+      </c>
+      <c r="D32">
+        <v>64.96659561856723</v>
+      </c>
+      <c r="E32">
+        <v>4.379999999999995</v>
+      </c>
+      <c r="F32">
+        <v>27.18</v>
+      </c>
+      <c r="G32">
+        <v>24.4</v>
+      </c>
+      <c r="H32">
+        <v>67.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>21.6</v>
+      </c>
+      <c r="K32">
+        <v>13.4</v>
+      </c>
+      <c r="L32">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M32">
+        <v>1.4949</v>
+      </c>
+      <c r="N32">
+        <v>6.705100000000002</v>
+      </c>
+      <c r="O32">
+        <v>1.206918000000001</v>
+      </c>
+      <c r="P32">
+        <v>5.498182000000001</v>
+      </c>
+      <c r="Q32">
+        <v>18.898182</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.117890524262236</v>
+      </c>
+      <c r="T32">
+        <v>1.337289661972879</v>
+      </c>
+      <c r="U32">
+        <v>0.055</v>
+      </c>
+      <c r="V32">
+        <v>0.18</v>
+      </c>
+      <c r="W32">
+        <v>0.04509999999999999</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.485316743594891</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09601102442482271</v>
+      </c>
+      <c r="C33">
+        <v>61.31764213497395</v>
+      </c>
+      <c r="D33">
+        <v>65.00364213497396</v>
+      </c>
+      <c r="E33">
+        <v>5.285999999999998</v>
+      </c>
+      <c r="F33">
+        <v>28.086</v>
+      </c>
+      <c r="G33">
+        <v>24.4</v>
+      </c>
+      <c r="H33">
+        <v>67.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>21.6</v>
+      </c>
+      <c r="K33">
+        <v>13.4</v>
+      </c>
+      <c r="L33">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M33">
+        <v>1.54473</v>
+      </c>
+      <c r="N33">
+        <v>6.655270000000002</v>
+      </c>
+      <c r="O33">
+        <v>1.197948600000001</v>
+      </c>
+      <c r="P33">
+        <v>5.457321400000001</v>
+      </c>
+      <c r="Q33">
+        <v>18.8573214</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1188840933693083</v>
+      </c>
+      <c r="T33">
+        <v>1.354089268597535</v>
+      </c>
+      <c r="U33">
+        <v>0.055</v>
+      </c>
+      <c r="V33">
+        <v>0.18</v>
+      </c>
+      <c r="W33">
+        <v>0.04509999999999999</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.308371042188604</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09596868186608019</v>
+      </c>
+      <c r="C34">
+        <v>60.44873092625848</v>
+      </c>
+      <c r="D34">
+        <v>65.04073092625848</v>
+      </c>
+      <c r="E34">
+        <v>6.191999999999997</v>
+      </c>
+      <c r="F34">
+        <v>28.992</v>
+      </c>
+      <c r="G34">
+        <v>24.4</v>
+      </c>
+      <c r="H34">
+        <v>67.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>21.6</v>
+      </c>
+      <c r="K34">
+        <v>13.4</v>
+      </c>
+      <c r="L34">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M34">
+        <v>1.59456</v>
+      </c>
+      <c r="N34">
+        <v>6.605440000000002</v>
+      </c>
+      <c r="O34">
+        <v>1.188979200000001</v>
+      </c>
+      <c r="P34">
+        <v>5.416460800000001</v>
+      </c>
+      <c r="Q34">
+        <v>18.8164608</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1199068850971768</v>
+      </c>
+      <c r="T34">
+        <v>1.371382981299386</v>
+      </c>
+      <c r="U34">
+        <v>0.055</v>
+      </c>
+      <c r="V34">
+        <v>0.18</v>
+      </c>
+      <c r="W34">
+        <v>0.04509999999999999</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.142484447120211</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09592633930733768</v>
+      </c>
+      <c r="C35">
+        <v>59.57986206482383</v>
+      </c>
+      <c r="D35">
+        <v>65.07786206482383</v>
+      </c>
+      <c r="E35">
+        <v>7.097999999999999</v>
+      </c>
+      <c r="F35">
+        <v>29.898</v>
+      </c>
+      <c r="G35">
+        <v>24.4</v>
+      </c>
+      <c r="H35">
+        <v>67.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>21.6</v>
+      </c>
+      <c r="K35">
+        <v>13.4</v>
+      </c>
+      <c r="L35">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M35">
+        <v>1.64439</v>
+      </c>
+      <c r="N35">
+        <v>6.555610000000001</v>
+      </c>
+      <c r="O35">
+        <v>1.180009800000001</v>
+      </c>
+      <c r="P35">
+        <v>5.375600200000001</v>
+      </c>
+      <c r="Q35">
+        <v>18.7756002</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1209602079213995</v>
+      </c>
+      <c r="T35">
+        <v>1.389192924231143</v>
+      </c>
+      <c r="U35">
+        <v>0.055</v>
+      </c>
+      <c r="V35">
+        <v>0.18</v>
+      </c>
+      <c r="W35">
+        <v>0.04509999999999999</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.986651585086264</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09588399674859517</v>
+      </c>
+      <c r="C36">
+        <v>58.71103562323842</v>
+      </c>
+      <c r="D36">
+        <v>65.11503562323841</v>
+      </c>
+      <c r="E36">
+        <v>8.004000000000001</v>
+      </c>
+      <c r="F36">
+        <v>30.804</v>
+      </c>
+      <c r="G36">
+        <v>24.4</v>
+      </c>
+      <c r="H36">
+        <v>67.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>21.6</v>
+      </c>
+      <c r="K36">
+        <v>13.4</v>
+      </c>
+      <c r="L36">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M36">
+        <v>1.69422</v>
+      </c>
+      <c r="N36">
+        <v>6.505780000000001</v>
+      </c>
+      <c r="O36">
+        <v>1.171040400000001</v>
+      </c>
+      <c r="P36">
+        <v>5.334739600000001</v>
+      </c>
+      <c r="Q36">
+        <v>18.7347396</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1220454496190836</v>
+      </c>
+      <c r="T36">
+        <v>1.407542562403257</v>
+      </c>
+      <c r="U36">
+        <v>0.055</v>
+      </c>
+      <c r="V36">
+        <v>0.18</v>
+      </c>
+      <c r="W36">
+        <v>0.04509999999999999</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.839985361995492</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09584165418985266</v>
+      </c>
+      <c r="C37">
+        <v>57.84225167423651</v>
+      </c>
+      <c r="D37">
+        <v>65.15225167423652</v>
+      </c>
+      <c r="E37">
+        <v>8.91</v>
+      </c>
+      <c r="F37">
+        <v>31.71</v>
+      </c>
+      <c r="G37">
+        <v>24.4</v>
+      </c>
+      <c r="H37">
+        <v>67.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>21.6</v>
+      </c>
+      <c r="K37">
+        <v>13.4</v>
+      </c>
+      <c r="L37">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M37">
+        <v>1.74405</v>
+      </c>
+      <c r="N37">
+        <v>6.455950000000001</v>
+      </c>
+      <c r="O37">
+        <v>1.162071000000001</v>
+      </c>
+      <c r="P37">
+        <v>5.293879</v>
+      </c>
+      <c r="Q37">
+        <v>18.693879</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1231640833690041</v>
+      </c>
+      <c r="T37">
+        <v>1.42645680482682</v>
+      </c>
+      <c r="U37">
+        <v>0.055</v>
+      </c>
+      <c r="V37">
+        <v>0.18</v>
+      </c>
+      <c r="W37">
+        <v>0.04509999999999999</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>4.701700065938477</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.09579931163111015</v>
+      </c>
+      <c r="C38">
+        <v>56.97351029071889</v>
+      </c>
+      <c r="D38">
+        <v>65.1895102907189</v>
+      </c>
+      <c r="E38">
+        <v>9.815999999999999</v>
+      </c>
+      <c r="F38">
+        <v>32.616</v>
+      </c>
+      <c r="G38">
+        <v>24.4</v>
+      </c>
+      <c r="H38">
+        <v>67.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>21.6</v>
+      </c>
+      <c r="K38">
+        <v>13.4</v>
+      </c>
+      <c r="L38">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M38">
+        <v>1.79388</v>
+      </c>
+      <c r="N38">
+        <v>6.406120000000001</v>
+      </c>
+      <c r="O38">
+        <v>1.153101600000001</v>
+      </c>
+      <c r="P38">
+        <v>5.253018400000001</v>
+      </c>
+      <c r="Q38">
+        <v>18.6530184</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1243176744236096</v>
+      </c>
+      <c r="T38">
+        <v>1.445962117326119</v>
+      </c>
+      <c r="U38">
+        <v>0.055</v>
+      </c>
+      <c r="V38">
+        <v>0.18</v>
+      </c>
+      <c r="W38">
+        <v>0.04509999999999999</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.571097286329076</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09690988907236764</v>
+      </c>
+      <c r="C39">
+        <v>55.10416706404222</v>
+      </c>
+      <c r="D39">
+        <v>64.22616706404222</v>
+      </c>
+      <c r="E39">
+        <v>10.722</v>
+      </c>
+      <c r="F39">
+        <v>33.522</v>
+      </c>
+      <c r="G39">
+        <v>24.4</v>
+      </c>
+      <c r="H39">
+        <v>67.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>21.6</v>
+      </c>
+      <c r="K39">
+        <v>13.4</v>
+      </c>
+      <c r="L39">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M39">
+        <v>1.9710936</v>
+      </c>
+      <c r="N39">
+        <v>6.228906400000001</v>
+      </c>
+      <c r="O39">
+        <v>1.121203152000001</v>
+      </c>
+      <c r="P39">
+        <v>5.107703248000001</v>
+      </c>
+      <c r="Q39">
+        <v>18.507703248</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1255078874164566</v>
+      </c>
+      <c r="T39">
+        <v>1.466086646095238</v>
+      </c>
+      <c r="U39">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.18</v>
+      </c>
+      <c r="W39">
+        <v>0.048216</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.160127149720338</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09689870651362513</v>
+      </c>
+      <c r="C40">
+        <v>54.20772518014547</v>
+      </c>
+      <c r="D40">
+        <v>64.23572518014548</v>
+      </c>
+      <c r="E40">
+        <v>11.628</v>
+      </c>
+      <c r="F40">
+        <v>34.428</v>
+      </c>
+      <c r="G40">
+        <v>24.4</v>
+      </c>
+      <c r="H40">
+        <v>67.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>21.6</v>
+      </c>
+      <c r="K40">
+        <v>13.4</v>
+      </c>
+      <c r="L40">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M40">
+        <v>2.0243664</v>
+      </c>
+      <c r="N40">
+        <v>6.175633600000001</v>
+      </c>
+      <c r="O40">
+        <v>1.111614048000001</v>
+      </c>
+      <c r="P40">
+        <v>5.064019552</v>
+      </c>
+      <c r="Q40">
+        <v>18.464019552</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1267364943768147</v>
+      </c>
+      <c r="T40">
+        <v>1.486860353211747</v>
+      </c>
+      <c r="U40">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.18</v>
+      </c>
+      <c r="W40">
+        <v>0.048216</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>4.050650119464541</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.0982306839548826</v>
+      </c>
+      <c r="C41">
+        <v>52.18290150208799</v>
+      </c>
+      <c r="D41">
+        <v>63.116901502088</v>
+      </c>
+      <c r="E41">
+        <v>12.534</v>
+      </c>
+      <c r="F41">
+        <v>35.334</v>
+      </c>
+      <c r="G41">
+        <v>24.4</v>
+      </c>
+      <c r="H41">
+        <v>67.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>21.6</v>
+      </c>
+      <c r="K41">
+        <v>13.4</v>
+      </c>
+      <c r="L41">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M41">
+        <v>2.226042</v>
+      </c>
+      <c r="N41">
+        <v>5.973958000000001</v>
+      </c>
+      <c r="O41">
+        <v>1.07531244</v>
+      </c>
+      <c r="P41">
+        <v>4.898645560000001</v>
+      </c>
+      <c r="Q41">
+        <v>18.29864556</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1280053835325944</v>
+      </c>
+      <c r="T41">
+        <v>1.508315165479618</v>
+      </c>
+      <c r="U41">
+        <v>0.063</v>
+      </c>
+      <c r="V41">
+        <v>0.18</v>
+      </c>
+      <c r="W41">
+        <v>0.05166</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.683668142829292</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.0982539413961401</v>
+      </c>
+      <c r="C42">
+        <v>51.25771200062005</v>
+      </c>
+      <c r="D42">
+        <v>63.09771200062006</v>
+      </c>
+      <c r="E42">
+        <v>13.44</v>
+      </c>
+      <c r="F42">
+        <v>36.24</v>
+      </c>
+      <c r="G42">
+        <v>24.4</v>
+      </c>
+      <c r="H42">
+        <v>67.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>21.6</v>
+      </c>
+      <c r="K42">
+        <v>13.4</v>
+      </c>
+      <c r="L42">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M42">
+        <v>2.28312</v>
+      </c>
+      <c r="N42">
+        <v>5.916880000000001</v>
+      </c>
+      <c r="O42">
+        <v>1.0650384</v>
+      </c>
+      <c r="P42">
+        <v>4.8518416</v>
+      </c>
+      <c r="Q42">
+        <v>18.2518416</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1293165689935668</v>
+      </c>
+      <c r="T42">
+        <v>1.530485138156417</v>
+      </c>
+      <c r="U42">
+        <v>0.063</v>
+      </c>
+      <c r="V42">
+        <v>0.18</v>
+      </c>
+      <c r="W42">
+        <v>0.05166</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.591576439258559</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09827719883739758</v>
+      </c>
+      <c r="C43">
+        <v>50.33253416401645</v>
+      </c>
+      <c r="D43">
+        <v>63.07853416401645</v>
+      </c>
+      <c r="E43">
+        <v>14.346</v>
+      </c>
+      <c r="F43">
+        <v>37.146</v>
+      </c>
+      <c r="G43">
+        <v>24.4</v>
+      </c>
+      <c r="H43">
+        <v>67.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>21.6</v>
+      </c>
+      <c r="K43">
+        <v>13.4</v>
+      </c>
+      <c r="L43">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M43">
+        <v>2.340198</v>
+      </c>
+      <c r="N43">
+        <v>5.859802000000001</v>
+      </c>
+      <c r="O43">
+        <v>1.054764360000001</v>
+      </c>
+      <c r="P43">
+        <v>4.80503764</v>
+      </c>
+      <c r="Q43">
+        <v>18.20503764</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.130672201419318</v>
+      </c>
+      <c r="T43">
+        <v>1.553406635330735</v>
+      </c>
+      <c r="U43">
+        <v>0.063</v>
+      </c>
+      <c r="V43">
+        <v>0.18</v>
+      </c>
+      <c r="W43">
+        <v>0.05166</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>3.503977013910789</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1007456962786551</v>
+      </c>
+      <c r="C44">
+        <v>47.45524886613813</v>
+      </c>
+      <c r="D44">
+        <v>61.10724886613813</v>
+      </c>
+      <c r="E44">
+        <v>15.252</v>
+      </c>
+      <c r="F44">
+        <v>38.052</v>
+      </c>
+      <c r="G44">
+        <v>24.4</v>
+      </c>
+      <c r="H44">
+        <v>67.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>21.6</v>
+      </c>
+      <c r="K44">
+        <v>13.4</v>
+      </c>
+      <c r="L44">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M44">
+        <v>2.6674452</v>
+      </c>
+      <c r="N44">
+        <v>5.532554800000002</v>
+      </c>
+      <c r="O44">
+        <v>0.9958598640000006</v>
+      </c>
+      <c r="P44">
+        <v>4.536694936000001</v>
+      </c>
+      <c r="Q44">
+        <v>17.936694936</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1320745797907846</v>
+      </c>
+      <c r="T44">
+        <v>1.57711852895934</v>
+      </c>
+      <c r="U44">
+        <v>0.0701</v>
+      </c>
+      <c r="V44">
+        <v>0.18</v>
+      </c>
+      <c r="W44">
+        <v>0.05748199999999999</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>3.074102515770521</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1008271737199126</v>
+      </c>
+      <c r="C45">
+        <v>46.48628120313492</v>
+      </c>
+      <c r="D45">
+        <v>61.04428120313491</v>
+      </c>
+      <c r="E45">
+        <v>16.158</v>
+      </c>
+      <c r="F45">
+        <v>38.958</v>
+      </c>
+      <c r="G45">
+        <v>24.4</v>
+      </c>
+      <c r="H45">
+        <v>67.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>21.6</v>
+      </c>
+      <c r="K45">
+        <v>13.4</v>
+      </c>
+      <c r="L45">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M45">
+        <v>2.7309558</v>
+      </c>
+      <c r="N45">
+        <v>5.469044200000001</v>
+      </c>
+      <c r="O45">
+        <v>0.9844279560000004</v>
+      </c>
+      <c r="P45">
+        <v>4.484616244000001</v>
+      </c>
+      <c r="Q45">
+        <v>17.884616244</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1335261644208992</v>
+      </c>
+      <c r="T45">
+        <v>1.601662418855615</v>
+      </c>
+      <c r="U45">
+        <v>0.0701</v>
+      </c>
+      <c r="V45">
+        <v>0.18</v>
+      </c>
+      <c r="W45">
+        <v>0.05748199999999999</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>3.002611759589811</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.10859369116117</v>
+      </c>
+      <c r="C46">
+        <v>40.12058873903101</v>
+      </c>
+      <c r="D46">
+        <v>55.58458873903101</v>
+      </c>
+      <c r="E46">
+        <v>17.064</v>
+      </c>
+      <c r="F46">
+        <v>39.864</v>
+      </c>
+      <c r="G46">
+        <v>24.4</v>
+      </c>
+      <c r="H46">
+        <v>67.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>21.6</v>
+      </c>
+      <c r="K46">
+        <v>13.4</v>
+      </c>
+      <c r="L46">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M46">
+        <v>3.6435696</v>
+      </c>
+      <c r="N46">
+        <v>4.556430400000001</v>
+      </c>
+      <c r="O46">
+        <v>0.8201574720000003</v>
+      </c>
+      <c r="P46">
+        <v>3.736272928</v>
+      </c>
+      <c r="Q46">
+        <v>17.136272928</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1350295913592322</v>
+      </c>
+      <c r="T46">
+        <v>1.627082876248186</v>
+      </c>
+      <c r="U46">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.18</v>
+      </c>
+      <c r="W46">
+        <v>0.074948</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.250540239439917</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1088498286024276</v>
+      </c>
+      <c r="C47">
+        <v>39.05111604945263</v>
+      </c>
+      <c r="D47">
+        <v>55.42111604945262</v>
+      </c>
+      <c r="E47">
+        <v>17.97</v>
+      </c>
+      <c r="F47">
+        <v>40.77</v>
+      </c>
+      <c r="G47">
+        <v>24.4</v>
+      </c>
+      <c r="H47">
+        <v>67.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>21.6</v>
+      </c>
+      <c r="K47">
+        <v>13.4</v>
+      </c>
+      <c r="L47">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M47">
+        <v>3.726378</v>
+      </c>
+      <c r="N47">
+        <v>4.473622000000001</v>
+      </c>
+      <c r="O47">
+        <v>0.8052519600000003</v>
+      </c>
+      <c r="P47">
+        <v>3.66837004</v>
+      </c>
+      <c r="Q47">
+        <v>17.06837004</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1365876883680501</v>
+      </c>
+      <c r="T47">
+        <v>1.653427713909578</v>
+      </c>
+      <c r="U47">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V47">
+        <v>0.18</v>
+      </c>
+      <c r="W47">
+        <v>0.074948</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.200528234119029</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.109105966043685</v>
+      </c>
+      <c r="C48">
+        <v>37.98260207734545</v>
+      </c>
+      <c r="D48">
+        <v>55.25860207734544</v>
+      </c>
+      <c r="E48">
+        <v>18.876</v>
+      </c>
+      <c r="F48">
+        <v>41.676</v>
+      </c>
+      <c r="G48">
+        <v>24.4</v>
+      </c>
+      <c r="H48">
+        <v>67.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>21.6</v>
+      </c>
+      <c r="K48">
+        <v>13.4</v>
+      </c>
+      <c r="L48">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M48">
+        <v>3.809186400000001</v>
+      </c>
+      <c r="N48">
+        <v>4.3908136</v>
+      </c>
+      <c r="O48">
+        <v>0.7903464480000003</v>
+      </c>
+      <c r="P48">
+        <v>3.600467152</v>
+      </c>
+      <c r="Q48">
+        <v>17.000467152</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1382034926734908</v>
+      </c>
+      <c r="T48">
+        <v>1.680748286299169</v>
+      </c>
+      <c r="U48">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.18</v>
+      </c>
+      <c r="W48">
+        <v>0.074948</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.152690663812094</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1093621034849425</v>
+      </c>
+      <c r="C49">
+        <v>36.9150384134898</v>
+      </c>
+      <c r="D49">
+        <v>55.0970384134898</v>
+      </c>
+      <c r="E49">
+        <v>19.782</v>
+      </c>
+      <c r="F49">
+        <v>42.582</v>
+      </c>
+      <c r="G49">
+        <v>24.4</v>
+      </c>
+      <c r="H49">
+        <v>67.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>21.6</v>
+      </c>
+      <c r="K49">
+        <v>13.4</v>
+      </c>
+      <c r="L49">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M49">
+        <v>3.8919948</v>
+      </c>
+      <c r="N49">
+        <v>4.3080052</v>
+      </c>
+      <c r="O49">
+        <v>0.7754409360000002</v>
+      </c>
+      <c r="P49">
+        <v>3.532564264</v>
+      </c>
+      <c r="Q49">
+        <v>16.932564264</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1398802707263066</v>
+      </c>
+      <c r="T49">
+        <v>1.709099823684594</v>
+      </c>
+      <c r="U49">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V49">
+        <v>0.18</v>
+      </c>
+      <c r="W49">
+        <v>0.074948</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.106888734794815</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1096182409262</v>
+      </c>
+      <c r="C50">
+        <v>35.84841674672598</v>
+      </c>
+      <c r="D50">
+        <v>54.93641674672597</v>
+      </c>
+      <c r="E50">
+        <v>20.68799999999999</v>
+      </c>
+      <c r="F50">
+        <v>43.48799999999999</v>
+      </c>
+      <c r="G50">
+        <v>24.4</v>
+      </c>
+      <c r="H50">
+        <v>67.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>21.6</v>
+      </c>
+      <c r="K50">
+        <v>13.4</v>
+      </c>
+      <c r="L50">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M50">
+        <v>3.9748032</v>
+      </c>
+      <c r="N50">
+        <v>4.225196800000001</v>
+      </c>
+      <c r="O50">
+        <v>0.7605354240000004</v>
+      </c>
+      <c r="P50">
+        <v>3.464661376</v>
+      </c>
+      <c r="Q50">
+        <v>16.864661376</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1416215402426923</v>
+      </c>
+      <c r="T50">
+        <v>1.738541804815612</v>
+      </c>
+      <c r="U50">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V50">
+        <v>0.18</v>
+      </c>
+      <c r="W50">
+        <v>0.074948</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.06299521948659</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1098743783674575</v>
+      </c>
+      <c r="C51">
+        <v>34.78272886252902</v>
+      </c>
+      <c r="D51">
+        <v>54.77672886252901</v>
+      </c>
+      <c r="E51">
+        <v>21.594</v>
+      </c>
+      <c r="F51">
+        <v>44.394</v>
+      </c>
+      <c r="G51">
+        <v>24.4</v>
+      </c>
+      <c r="H51">
+        <v>67.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>21.6</v>
+      </c>
+      <c r="K51">
+        <v>13.4</v>
+      </c>
+      <c r="L51">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M51">
+        <v>4.0576116</v>
+      </c>
+      <c r="N51">
+        <v>4.142388400000001</v>
+      </c>
+      <c r="O51">
+        <v>0.7456299120000003</v>
+      </c>
+      <c r="P51">
+        <v>3.396758488000001</v>
+      </c>
+      <c r="Q51">
+        <v>16.796758488</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1434310948381519</v>
+      </c>
+      <c r="T51">
+        <v>1.769138373441964</v>
+      </c>
+      <c r="U51">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V51">
+        <v>0.18</v>
+      </c>
+      <c r="W51">
+        <v>0.074948</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.020893276231762</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.118781515808715</v>
+      </c>
+      <c r="C52">
+        <v>28.84806172568886</v>
+      </c>
+      <c r="D52">
+        <v>49.74806172568886</v>
+      </c>
+      <c r="E52">
+        <v>22.5</v>
+      </c>
+      <c r="F52">
+        <v>45.3</v>
+      </c>
+      <c r="G52">
+        <v>24.4</v>
+      </c>
+      <c r="H52">
+        <v>67.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>21.6</v>
+      </c>
+      <c r="K52">
+        <v>13.4</v>
+      </c>
+      <c r="L52">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M52">
+        <v>5.09625</v>
+      </c>
+      <c r="N52">
+        <v>3.103750000000002</v>
+      </c>
+      <c r="O52">
+        <v>0.5586750000000005</v>
+      </c>
+      <c r="P52">
+        <v>2.545075000000001</v>
+      </c>
+      <c r="Q52">
+        <v>15.945075</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1453130316174299</v>
+      </c>
+      <c r="T52">
+        <v>1.80095880481337</v>
+      </c>
+      <c r="U52">
+        <v>0.1125</v>
+      </c>
+      <c r="V52">
+        <v>0.18</v>
+      </c>
+      <c r="W52">
+        <v>0.09225</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>1.609026244787835</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1192106732499724</v>
+      </c>
+      <c r="C53">
+        <v>27.72298576546503</v>
+      </c>
+      <c r="D53">
+        <v>49.52898576546503</v>
+      </c>
+      <c r="E53">
+        <v>23.406</v>
+      </c>
+      <c r="F53">
+        <v>46.206</v>
+      </c>
+      <c r="G53">
+        <v>24.4</v>
+      </c>
+      <c r="H53">
+        <v>67.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>21.6</v>
+      </c>
+      <c r="K53">
+        <v>13.4</v>
+      </c>
+      <c r="L53">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M53">
+        <v>5.198175</v>
+      </c>
+      <c r="N53">
+        <v>3.001825000000001</v>
+      </c>
+      <c r="O53">
+        <v>0.5403285000000003</v>
+      </c>
+      <c r="P53">
+        <v>2.461496500000001</v>
+      </c>
+      <c r="Q53">
+        <v>15.8614965</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1472717821428009</v>
+      </c>
+      <c r="T53">
+        <v>1.834078029301977</v>
+      </c>
+      <c r="U53">
+        <v>0.1125</v>
+      </c>
+      <c r="V53">
+        <v>0.18</v>
+      </c>
+      <c r="W53">
+        <v>0.09225</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>1.577476710576308</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1196398306912299</v>
+      </c>
+      <c r="C54">
+        <v>26.59983083888734</v>
+      </c>
+      <c r="D54">
+        <v>49.31183083888734</v>
+      </c>
+      <c r="E54">
+        <v>24.312</v>
+      </c>
+      <c r="F54">
+        <v>47.112</v>
+      </c>
+      <c r="G54">
+        <v>24.4</v>
+      </c>
+      <c r="H54">
+        <v>67.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>21.6</v>
+      </c>
+      <c r="K54">
+        <v>13.4</v>
+      </c>
+      <c r="L54">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M54">
+        <v>5.3001</v>
+      </c>
+      <c r="N54">
+        <v>2.899900000000001</v>
+      </c>
+      <c r="O54">
+        <v>0.5219820000000003</v>
+      </c>
+      <c r="P54">
+        <v>2.377918</v>
+      </c>
+      <c r="Q54">
+        <v>15.777918</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1493121472733957</v>
+      </c>
+      <c r="T54">
+        <v>1.868577221477608</v>
+      </c>
+      <c r="U54">
+        <v>0.1125</v>
+      </c>
+      <c r="V54">
+        <v>0.18</v>
+      </c>
+      <c r="W54">
+        <v>0.09225</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>1.547140619988302</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1200689881324874</v>
+      </c>
+      <c r="C55">
+        <v>25.47857178851152</v>
+      </c>
+      <c r="D55">
+        <v>49.09657178851153</v>
+      </c>
+      <c r="E55">
+        <v>25.218</v>
+      </c>
+      <c r="F55">
+        <v>48.018</v>
+      </c>
+      <c r="G55">
+        <v>24.4</v>
+      </c>
+      <c r="H55">
+        <v>67.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>21.6</v>
+      </c>
+      <c r="K55">
+        <v>13.4</v>
+      </c>
+      <c r="L55">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M55">
+        <v>5.402025</v>
+      </c>
+      <c r="N55">
+        <v>2.797975000000001</v>
+      </c>
+      <c r="O55">
+        <v>0.5036355000000003</v>
+      </c>
+      <c r="P55">
+        <v>2.2943395</v>
+      </c>
+      <c r="Q55">
+        <v>15.6943395</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1514393364521009</v>
+      </c>
+      <c r="T55">
+        <v>1.904544464384118</v>
+      </c>
+      <c r="U55">
+        <v>0.1125</v>
+      </c>
+      <c r="V55">
+        <v>0.18</v>
+      </c>
+      <c r="W55">
+        <v>0.09225</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>1.517949287535693</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1613946520655954</v>
+      </c>
+      <c r="C56">
+        <v>10.04247331578373</v>
+      </c>
+      <c r="D56">
+        <v>34.56647331578373</v>
+      </c>
+      <c r="E56">
+        <v>26.124</v>
+      </c>
+      <c r="F56">
+        <v>48.924</v>
+      </c>
+      <c r="G56">
+        <v>24.4</v>
+      </c>
+      <c r="H56">
+        <v>67.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>21.6</v>
+      </c>
+      <c r="K56">
+        <v>13.4</v>
+      </c>
+      <c r="L56">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M56">
+        <v>9.6184584</v>
+      </c>
+      <c r="N56">
+        <v>-1.418458399999999</v>
+      </c>
+      <c r="O56">
+        <v>-0.2553225119999998</v>
+      </c>
+      <c r="P56">
+        <v>-1.163135887999999</v>
+      </c>
+      <c r="Q56">
+        <v>12.236864112</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.155482701726244</v>
+      </c>
+      <c r="T56">
+        <v>1.972911068741973</v>
+      </c>
+      <c r="U56">
+        <v>0.1966</v>
+      </c>
+      <c r="V56">
+        <v>0.1534549445054522</v>
+      </c>
+      <c r="W56">
+        <v>0.1664307579102281</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.8525274694747342</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1629726520655954</v>
+      </c>
+      <c r="C57">
+        <v>8.750213684025944</v>
+      </c>
+      <c r="D57">
+        <v>34.18021368402594</v>
+      </c>
+      <c r="E57">
+        <v>27.03</v>
+      </c>
+      <c r="F57">
+        <v>49.83</v>
+      </c>
+      <c r="G57">
+        <v>24.4</v>
+      </c>
+      <c r="H57">
+        <v>67.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>21.6</v>
+      </c>
+      <c r="K57">
+        <v>13.4</v>
+      </c>
+      <c r="L57">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M57">
+        <v>9.796578</v>
+      </c>
+      <c r="N57">
+        <v>-1.596577999999999</v>
+      </c>
+      <c r="O57">
+        <v>-0.28738404</v>
+      </c>
+      <c r="P57">
+        <v>-1.309193959999999</v>
+      </c>
+      <c r="Q57">
+        <v>12.09080604</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1580756506534938</v>
+      </c>
+      <c r="T57">
+        <v>2.016753536936239</v>
+      </c>
+      <c r="U57">
+        <v>0.1966</v>
+      </c>
+      <c r="V57">
+        <v>0.1506648546053531</v>
+      </c>
+      <c r="W57">
+        <v>0.1669792895845876</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.837026970029739</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1645506520655954</v>
+      </c>
+      <c r="C58">
+        <v>7.466491095900743</v>
+      </c>
+      <c r="D58">
+        <v>33.80249109590075</v>
+      </c>
+      <c r="E58">
+        <v>27.936</v>
+      </c>
+      <c r="F58">
+        <v>50.736</v>
+      </c>
+      <c r="G58">
+        <v>24.4</v>
+      </c>
+      <c r="H58">
+        <v>67.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>21.6</v>
+      </c>
+      <c r="K58">
+        <v>13.4</v>
+      </c>
+      <c r="L58">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M58">
+        <v>9.974697600000001</v>
+      </c>
+      <c r="N58">
+        <v>-1.7746976</v>
+      </c>
+      <c r="O58">
+        <v>-0.319445568</v>
+      </c>
+      <c r="P58">
+        <v>-1.455252032</v>
+      </c>
+      <c r="Q58">
+        <v>11.944747968</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1607864608956187</v>
+      </c>
+      <c r="T58">
+        <v>2.062588844593881</v>
+      </c>
+      <c r="U58">
+        <v>0.1966</v>
+      </c>
+      <c r="V58">
+        <v>0.1479744107731146</v>
+      </c>
+      <c r="W58">
+        <v>0.1675082308420057</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.8220800598506366</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1661286520655954</v>
+      </c>
+      <c r="C59">
+        <v>6.191025618527561</v>
+      </c>
+      <c r="D59">
+        <v>33.43302561852757</v>
+      </c>
+      <c r="E59">
+        <v>28.842</v>
+      </c>
+      <c r="F59">
+        <v>51.642</v>
+      </c>
+      <c r="G59">
+        <v>24.4</v>
+      </c>
+      <c r="H59">
+        <v>67.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>21.6</v>
+      </c>
+      <c r="K59">
+        <v>13.4</v>
+      </c>
+      <c r="L59">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M59">
+        <v>10.1528172</v>
+      </c>
+      <c r="N59">
+        <v>-1.9528172</v>
+      </c>
+      <c r="O59">
+        <v>-0.3515070960000001</v>
+      </c>
+      <c r="P59">
+        <v>-1.601310104</v>
+      </c>
+      <c r="Q59">
+        <v>11.798689896</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1636233553350517</v>
+      </c>
+      <c r="T59">
+        <v>2.110556027026297</v>
+      </c>
+      <c r="U59">
+        <v>0.1966</v>
+      </c>
+      <c r="V59">
+        <v>0.1453783684788494</v>
+      </c>
+      <c r="W59">
+        <v>0.1680186127570582</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.8076576026602744</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1780727976987591</v>
+      </c>
+      <c r="C60">
+        <v>2.730395793934285</v>
+      </c>
+      <c r="D60">
+        <v>30.87839579393428</v>
+      </c>
+      <c r="E60">
+        <v>29.74799999999999</v>
+      </c>
+      <c r="F60">
+        <v>52.54799999999999</v>
+      </c>
+      <c r="G60">
+        <v>24.4</v>
+      </c>
+      <c r="H60">
+        <v>67.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>21.6</v>
+      </c>
+      <c r="K60">
+        <v>13.4</v>
+      </c>
+      <c r="L60">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M60">
+        <v>11.2347624</v>
+      </c>
+      <c r="N60">
+        <v>-3.034762399999996</v>
+      </c>
+      <c r="O60">
+        <v>-0.5462572319999995</v>
+      </c>
+      <c r="P60">
+        <v>-2.488505167999997</v>
+      </c>
+      <c r="Q60">
+        <v>10.911494832</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1675242581600857</v>
+      </c>
+      <c r="T60">
+        <v>2.176513827520605</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.1313779452959327</v>
+      </c>
+      <c r="W60">
+        <v>0.1857113952957296</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.7298774738662923</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1798227976987591</v>
+      </c>
+      <c r="C61">
+        <v>1.482530551425107</v>
+      </c>
+      <c r="D61">
+        <v>30.5365305514251</v>
+      </c>
+      <c r="E61">
+        <v>30.65399999999999</v>
+      </c>
+      <c r="F61">
+        <v>53.45399999999999</v>
+      </c>
+      <c r="G61">
+        <v>24.4</v>
+      </c>
+      <c r="H61">
+        <v>67.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>21.6</v>
+      </c>
+      <c r="K61">
+        <v>13.4</v>
+      </c>
+      <c r="L61">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M61">
+        <v>11.4284652</v>
+      </c>
+      <c r="N61">
+        <v>-3.228465199999997</v>
+      </c>
+      <c r="O61">
+        <v>-0.5811237359999996</v>
+      </c>
+      <c r="P61">
+        <v>-2.647341463999997</v>
+      </c>
+      <c r="Q61">
+        <v>10.752658536</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1706638742127707</v>
+      </c>
+      <c r="T61">
+        <v>2.229599530630864</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.1291512004604084</v>
+      </c>
+      <c r="W61">
+        <v>0.1861874733415647</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.7175066692244907</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1815727976987591</v>
+      </c>
+      <c r="C62">
+        <v>0.2421522318407199</v>
+      </c>
+      <c r="D62">
+        <v>30.20215223184071</v>
+      </c>
+      <c r="E62">
+        <v>31.55999999999999</v>
+      </c>
+      <c r="F62">
+        <v>54.35999999999999</v>
+      </c>
+      <c r="G62">
+        <v>24.4</v>
+      </c>
+      <c r="H62">
+        <v>67.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>21.6</v>
+      </c>
+      <c r="K62">
+        <v>13.4</v>
+      </c>
+      <c r="L62">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M62">
+        <v>11.622168</v>
+      </c>
+      <c r="N62">
+        <v>-3.422167999999997</v>
+      </c>
+      <c r="O62">
+        <v>-0.6159902399999997</v>
+      </c>
+      <c r="P62">
+        <v>-2.806177759999998</v>
+      </c>
+      <c r="Q62">
+        <v>10.59382224</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.17396047106809</v>
+      </c>
+      <c r="T62">
+        <v>2.285339518896635</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.1269986804527349</v>
+      </c>
+      <c r="W62">
+        <v>0.1866476821192053</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.7055482247374159</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1833227976987591</v>
+      </c>
+      <c r="C63">
+        <v>-0.9909824486868999</v>
+      </c>
+      <c r="D63">
+        <v>29.8750175513131</v>
+      </c>
+      <c r="E63">
+        <v>32.46599999999999</v>
+      </c>
+      <c r="F63">
+        <v>55.266</v>
+      </c>
+      <c r="G63">
+        <v>24.4</v>
+      </c>
+      <c r="H63">
+        <v>67.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>21.6</v>
+      </c>
+      <c r="K63">
+        <v>13.4</v>
+      </c>
+      <c r="L63">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M63">
+        <v>11.8158708</v>
+      </c>
+      <c r="N63">
+        <v>-3.615870799999998</v>
+      </c>
+      <c r="O63">
+        <v>-0.6508567439999998</v>
+      </c>
+      <c r="P63">
+        <v>-2.965014055999998</v>
+      </c>
+      <c r="Q63">
+        <v>10.434985944</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1774261241724</v>
+      </c>
+      <c r="T63">
+        <v>2.343937968099113</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.1249167348715425</v>
+      </c>
+      <c r="W63">
+        <v>0.1870928020844642</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.6939818603974581</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1850727976987592</v>
+      </c>
+      <c r="C64">
+        <v>-2.217106346452972</v>
+      </c>
+      <c r="D64">
+        <v>29.55489365354703</v>
+      </c>
+      <c r="E64">
+        <v>33.372</v>
+      </c>
+      <c r="F64">
+        <v>56.172</v>
+      </c>
+      <c r="G64">
+        <v>24.4</v>
+      </c>
+      <c r="H64">
+        <v>67.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>21.6</v>
+      </c>
+      <c r="K64">
+        <v>13.4</v>
+      </c>
+      <c r="L64">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M64">
+        <v>12.0095736</v>
+      </c>
+      <c r="N64">
+        <v>-3.809573599999998</v>
+      </c>
+      <c r="O64">
+        <v>-0.685723248</v>
+      </c>
+      <c r="P64">
+        <v>-3.123850351999998</v>
+      </c>
+      <c r="Q64">
+        <v>10.276149648</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1810741800716737</v>
+      </c>
+      <c r="T64">
+        <v>2.405620546206985</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.1229019488252273</v>
+      </c>
+      <c r="W64">
+        <v>0.1875235633411664</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.6827886045845959</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1868227976987592</v>
+      </c>
+      <c r="C65">
+        <v>-3.436442442936908</v>
+      </c>
+      <c r="D65">
+        <v>29.24155755706309</v>
+      </c>
+      <c r="E65">
+        <v>34.27799999999999</v>
+      </c>
+      <c r="F65">
+        <v>57.078</v>
+      </c>
+      <c r="G65">
+        <v>24.4</v>
+      </c>
+      <c r="H65">
+        <v>67.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>21.6</v>
+      </c>
+      <c r="K65">
+        <v>13.4</v>
+      </c>
+      <c r="L65">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M65">
+        <v>12.2032764</v>
+      </c>
+      <c r="N65">
+        <v>-4.003276399999997</v>
+      </c>
+      <c r="O65">
+        <v>-0.7205897519999996</v>
+      </c>
+      <c r="P65">
+        <v>-3.282686647999998</v>
+      </c>
+      <c r="Q65">
+        <v>10.117313352</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1849194281817189</v>
+      </c>
+      <c r="T65">
+        <v>2.470637317726093</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.1209511242406999</v>
+      </c>
+      <c r="W65">
+        <v>0.1879406496373384</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.6719506902261103</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1885727976987591</v>
+      </c>
+      <c r="C66">
+        <v>-4.649204362766824</v>
+      </c>
+      <c r="D66">
+        <v>28.93479563723317</v>
+      </c>
+      <c r="E66">
+        <v>35.184</v>
+      </c>
+      <c r="F66">
+        <v>57.98399999999999</v>
+      </c>
+      <c r="G66">
+        <v>24.4</v>
+      </c>
+      <c r="H66">
+        <v>67.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>21.6</v>
+      </c>
+      <c r="K66">
+        <v>13.4</v>
+      </c>
+      <c r="L66">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M66">
+        <v>12.3969792</v>
+      </c>
+      <c r="N66">
+        <v>-4.196979199999998</v>
+      </c>
+      <c r="O66">
+        <v>-0.7554562559999998</v>
+      </c>
+      <c r="P66">
+        <v>-3.441522943999998</v>
+      </c>
+      <c r="Q66">
+        <v>9.958477056000003</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1889783011867666</v>
+      </c>
+      <c r="T66">
+        <v>2.539266132107373</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.1190612629244389</v>
+      </c>
+      <c r="W66">
+        <v>0.1883447019867549</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.6614514606913273</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1903227976987592</v>
+      </c>
+      <c r="C67">
+        <v>-5.855596859419826</v>
+      </c>
+      <c r="D67">
+        <v>28.63440314058018</v>
+      </c>
+      <c r="E67">
+        <v>36.09</v>
+      </c>
+      <c r="F67">
+        <v>58.89</v>
+      </c>
+      <c r="G67">
+        <v>24.4</v>
+      </c>
+      <c r="H67">
+        <v>67.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>21.6</v>
+      </c>
+      <c r="K67">
+        <v>13.4</v>
+      </c>
+      <c r="L67">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M67">
+        <v>12.590682</v>
+      </c>
+      <c r="N67">
+        <v>-4.390681999999998</v>
+      </c>
+      <c r="O67">
+        <v>-0.7903227599999999</v>
+      </c>
+      <c r="P67">
+        <v>-3.600359239999998</v>
+      </c>
+      <c r="Q67">
+        <v>9.799640760000003</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1932691097921029</v>
+      </c>
+      <c r="T67">
+        <v>2.611816593024727</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.1172295511871399</v>
+      </c>
+      <c r="W67">
+        <v>0.1887363219561895</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.6512752843729992</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1920727976987592</v>
+      </c>
+      <c r="C68">
+        <v>-7.055816270978774</v>
+      </c>
+      <c r="D68">
+        <v>28.34018372902123</v>
+      </c>
+      <c r="E68">
+        <v>36.996</v>
+      </c>
+      <c r="F68">
+        <v>59.796</v>
+      </c>
+      <c r="G68">
+        <v>24.4</v>
+      </c>
+      <c r="H68">
+        <v>67.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>21.6</v>
+      </c>
+      <c r="K68">
+        <v>13.4</v>
+      </c>
+      <c r="L68">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M68">
+        <v>12.7843848</v>
+      </c>
+      <c r="N68">
+        <v>-4.584384799999999</v>
+      </c>
+      <c r="O68">
+        <v>-0.825189264</v>
+      </c>
+      <c r="P68">
+        <v>-3.759195535999999</v>
+      </c>
+      <c r="Q68">
+        <v>9.640804464000002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1978123189036353</v>
+      </c>
+      <c r="T68">
+        <v>2.688634728113689</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.1154533458661226</v>
+      </c>
+      <c r="W68">
+        <v>0.189116074653823</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.6414074770340144</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1938227976987592</v>
+      </c>
+      <c r="C69">
+        <v>-8.25005094807743</v>
+      </c>
+      <c r="D69">
+        <v>28.05194905192257</v>
+      </c>
+      <c r="E69">
+        <v>37.902</v>
+      </c>
+      <c r="F69">
+        <v>60.702</v>
+      </c>
+      <c r="G69">
+        <v>24.4</v>
+      </c>
+      <c r="H69">
+        <v>67.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>21.6</v>
+      </c>
+      <c r="K69">
+        <v>13.4</v>
+      </c>
+      <c r="L69">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M69">
+        <v>12.9780876</v>
+      </c>
+      <c r="N69">
+        <v>-4.778087599999997</v>
+      </c>
+      <c r="O69">
+        <v>-0.8600557679999997</v>
+      </c>
+      <c r="P69">
+        <v>-3.918031831999998</v>
+      </c>
+      <c r="Q69">
+        <v>9.481968168000002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2026308740219273</v>
+      </c>
+      <c r="T69">
+        <v>2.770108507753498</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.1137301615994641</v>
+      </c>
+      <c r="W69">
+        <v>0.1894844914500346</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.6318342311081335</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1955727976987592</v>
+      </c>
+      <c r="C70">
+        <v>-9.438481655993904</v>
+      </c>
+      <c r="D70">
+        <v>27.7695183440061</v>
+      </c>
+      <c r="E70">
+        <v>38.80800000000001</v>
+      </c>
+      <c r="F70">
+        <v>61.608</v>
+      </c>
+      <c r="G70">
+        <v>24.4</v>
+      </c>
+      <c r="H70">
+        <v>67.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>21.6</v>
+      </c>
+      <c r="K70">
+        <v>13.4</v>
+      </c>
+      <c r="L70">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M70">
+        <v>13.1717904</v>
+      </c>
+      <c r="N70">
+        <v>-4.9717904</v>
+      </c>
+      <c r="O70">
+        <v>-0.8949222720000002</v>
+      </c>
+      <c r="P70">
+        <v>-4.076868127999999</v>
+      </c>
+      <c r="Q70">
+        <v>9.323131872000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2077505888351125</v>
+      </c>
+      <c r="T70">
+        <v>2.856674398620795</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.1120576592230013</v>
+      </c>
+      <c r="W70">
+        <v>0.1898420724581223</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.6225425512388962</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1973227976987592</v>
+      </c>
+      <c r="C71">
+        <v>-10.62128195269613</v>
+      </c>
+      <c r="D71">
+        <v>27.49271804730387</v>
+      </c>
+      <c r="E71">
+        <v>39.714</v>
+      </c>
+      <c r="F71">
+        <v>62.514</v>
+      </c>
+      <c r="G71">
+        <v>24.4</v>
+      </c>
+      <c r="H71">
+        <v>67.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>21.6</v>
+      </c>
+      <c r="K71">
+        <v>13.4</v>
+      </c>
+      <c r="L71">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M71">
+        <v>13.3654932</v>
+      </c>
+      <c r="N71">
+        <v>-5.165493199999998</v>
+      </c>
+      <c r="O71">
+        <v>-0.929788776</v>
+      </c>
+      <c r="P71">
+        <v>-4.235704423999999</v>
+      </c>
+      <c r="Q71">
+        <v>9.164295576000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2132006078297936</v>
+      </c>
+      <c r="T71">
+        <v>2.948825185673079</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.1104336351762912</v>
+      </c>
+      <c r="W71">
+        <v>0.1901892887993089</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.6135201954238397</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1990727976987592</v>
+      </c>
+      <c r="C72">
+        <v>-11.79861854450104</v>
+      </c>
+      <c r="D72">
+        <v>27.22138145549897</v>
+      </c>
+      <c r="E72">
+        <v>40.62</v>
+      </c>
+      <c r="F72">
+        <v>63.42</v>
+      </c>
+      <c r="G72">
+        <v>24.4</v>
+      </c>
+      <c r="H72">
+        <v>67.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>21.6</v>
+      </c>
+      <c r="K72">
+        <v>13.4</v>
+      </c>
+      <c r="L72">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M72">
+        <v>13.559196</v>
+      </c>
+      <c r="N72">
+        <v>-5.359195999999999</v>
+      </c>
+      <c r="O72">
+        <v>-0.9646552800000001</v>
+      </c>
+      <c r="P72">
+        <v>-4.394540719999998</v>
+      </c>
+      <c r="Q72">
+        <v>9.005459280000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2190139614241201</v>
+      </c>
+      <c r="T72">
+        <v>3.047119358528848</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.1088560118166299</v>
+      </c>
+      <c r="W72">
+        <v>0.1905265846736045</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.6047556212034992</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2008227976987592</v>
+      </c>
+      <c r="C73">
+        <v>-12.97065162087857</v>
+      </c>
+      <c r="D73">
+        <v>26.95534837912142</v>
+      </c>
+      <c r="E73">
+        <v>41.526</v>
+      </c>
+      <c r="F73">
+        <v>64.32599999999999</v>
+      </c>
+      <c r="G73">
+        <v>24.4</v>
+      </c>
+      <c r="H73">
+        <v>67.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>21.6</v>
+      </c>
+      <c r="K73">
+        <v>13.4</v>
+      </c>
+      <c r="L73">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M73">
+        <v>13.7528988</v>
+      </c>
+      <c r="N73">
+        <v>-5.552898799999998</v>
+      </c>
+      <c r="O73">
+        <v>-0.9995217839999998</v>
+      </c>
+      <c r="P73">
+        <v>-4.553377015999998</v>
+      </c>
+      <c r="Q73">
+        <v>8.846622984000003</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2252282359559862</v>
+      </c>
+      <c r="T73">
+        <v>3.152192439857428</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.1073228285516069</v>
+      </c>
+      <c r="W73">
+        <v>0.1908543792556664</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5962379363978161</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2025727976987592</v>
+      </c>
+      <c r="C74">
+        <v>-14.13753516981369</v>
+      </c>
+      <c r="D74">
+        <v>26.69446483018631</v>
+      </c>
+      <c r="E74">
+        <v>42.432</v>
+      </c>
+      <c r="F74">
+        <v>65.232</v>
+      </c>
+      <c r="G74">
+        <v>24.4</v>
+      </c>
+      <c r="H74">
+        <v>67.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>21.6</v>
+      </c>
+      <c r="K74">
+        <v>13.4</v>
+      </c>
+      <c r="L74">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M74">
+        <v>13.9466016</v>
+      </c>
+      <c r="N74">
+        <v>-5.746601599999998</v>
+      </c>
+      <c r="O74">
+        <v>-1.034388288</v>
+      </c>
+      <c r="P74">
+        <v>-4.712213311999998</v>
+      </c>
+      <c r="Q74">
+        <v>8.687786688000003</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2318863872401286</v>
+      </c>
+      <c r="T74">
+        <v>3.264770741280908</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.1058322337106124</v>
+      </c>
+      <c r="W74">
+        <v>0.1911730684326711</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5879568539478464</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2043227976987592</v>
+      </c>
+      <c r="C75">
+        <v>-15.29941727503056</v>
+      </c>
+      <c r="D75">
+        <v>26.43858272496943</v>
+      </c>
+      <c r="E75">
+        <v>43.33799999999999</v>
+      </c>
+      <c r="F75">
+        <v>66.13799999999999</v>
+      </c>
+      <c r="G75">
+        <v>24.4</v>
+      </c>
+      <c r="H75">
+        <v>67.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>21.6</v>
+      </c>
+      <c r="K75">
+        <v>13.4</v>
+      </c>
+      <c r="L75">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M75">
+        <v>14.1403044</v>
+      </c>
+      <c r="N75">
+        <v>-5.940304399999997</v>
+      </c>
+      <c r="O75">
+        <v>-1.069254792</v>
+      </c>
+      <c r="P75">
+        <v>-4.871049607999997</v>
+      </c>
+      <c r="Q75">
+        <v>8.528950392000002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2390377349156889</v>
+      </c>
+      <c r="T75">
+        <v>3.385688176143164</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.1043824770844396</v>
+      </c>
+      <c r="W75">
+        <v>0.1914830263993468</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5799026504691089</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2060727976987592</v>
+      </c>
+      <c r="C76">
+        <v>-16.45644039628505</v>
+      </c>
+      <c r="D76">
+        <v>26.18755960371494</v>
+      </c>
+      <c r="E76">
+        <v>44.244</v>
+      </c>
+      <c r="F76">
+        <v>67.044</v>
+      </c>
+      <c r="G76">
+        <v>24.4</v>
+      </c>
+      <c r="H76">
+        <v>67.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>21.6</v>
+      </c>
+      <c r="K76">
+        <v>13.4</v>
+      </c>
+      <c r="L76">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M76">
+        <v>14.3340072</v>
+      </c>
+      <c r="N76">
+        <v>-6.134007199999997</v>
+      </c>
+      <c r="O76">
+        <v>-1.104121296</v>
+      </c>
+      <c r="P76">
+        <v>-5.029885903999998</v>
+      </c>
+      <c r="Q76">
+        <v>8.370114096000002</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2467391862586</v>
+      </c>
+      <c r="T76">
+        <v>3.51590695214867</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.102971903069785</v>
+      </c>
+      <c r="W76">
+        <v>0.19178460712368</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5720661281654722</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2078227976987592</v>
+      </c>
+      <c r="C77">
+        <v>-17.60874163383937</v>
+      </c>
+      <c r="D77">
+        <v>25.94125836616062</v>
+      </c>
+      <c r="E77">
+        <v>45.14999999999999</v>
+      </c>
+      <c r="F77">
+        <v>67.94999999999999</v>
+      </c>
+      <c r="G77">
+        <v>24.4</v>
+      </c>
+      <c r="H77">
+        <v>67.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>21.6</v>
+      </c>
+      <c r="K77">
+        <v>13.4</v>
+      </c>
+      <c r="L77">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M77">
+        <v>14.52771</v>
+      </c>
+      <c r="N77">
+        <v>-6.327709999999996</v>
+      </c>
+      <c r="O77">
+        <v>-1.1389878</v>
+      </c>
+      <c r="P77">
+        <v>-5.188722199999996</v>
+      </c>
+      <c r="Q77">
+        <v>8.211277800000005</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.255056753708944</v>
+      </c>
+      <c r="T77">
+        <v>3.656543230234617</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.1015989443621879</v>
+      </c>
+      <c r="W77">
+        <v>0.1920781456953642</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5644385797899327</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2095727976987592</v>
+      </c>
+      <c r="C78">
+        <v>-18.75645297815147</v>
+      </c>
+      <c r="D78">
+        <v>25.69954702184852</v>
+      </c>
+      <c r="E78">
+        <v>46.056</v>
+      </c>
+      <c r="F78">
+        <v>68.85599999999999</v>
+      </c>
+      <c r="G78">
+        <v>24.4</v>
+      </c>
+      <c r="H78">
+        <v>67.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>21.6</v>
+      </c>
+      <c r="K78">
+        <v>13.4</v>
+      </c>
+      <c r="L78">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M78">
+        <v>14.7214128</v>
+      </c>
+      <c r="N78">
+        <v>-6.521412799999997</v>
+      </c>
+      <c r="O78">
+        <v>-1.173854304</v>
+      </c>
+      <c r="P78">
+        <v>-5.347558495999997</v>
+      </c>
+      <c r="Q78">
+        <v>8.052441504000004</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.26406745178015</v>
+      </c>
+      <c r="T78">
+        <v>3.808899198161059</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.100262116146896</v>
+      </c>
+      <c r="W78">
+        <v>0.1923639595677936</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5570117563716441</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2113227976987592</v>
+      </c>
+      <c r="C79">
+        <v>-19.89970154573388</v>
+      </c>
+      <c r="D79">
+        <v>25.46229845426613</v>
+      </c>
+      <c r="E79">
+        <v>46.962</v>
+      </c>
+      <c r="F79">
+        <v>69.762</v>
+      </c>
+      <c r="G79">
+        <v>24.4</v>
+      </c>
+      <c r="H79">
+        <v>67.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>21.6</v>
+      </c>
+      <c r="K79">
+        <v>13.4</v>
+      </c>
+      <c r="L79">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M79">
+        <v>14.9151156</v>
+      </c>
+      <c r="N79">
+        <v>-6.715115599999999</v>
+      </c>
+      <c r="O79">
+        <v>-1.208720808</v>
+      </c>
+      <c r="P79">
+        <v>-5.506394791999999</v>
+      </c>
+      <c r="Q79">
+        <v>7.893605208000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2738616888140696</v>
+      </c>
+      <c r="T79">
+        <v>3.974503511124584</v>
+      </c>
+      <c r="U79">
+        <v>0.2138</v>
+      </c>
+      <c r="V79">
+        <v>0.09896001074239079</v>
+      </c>
+      <c r="W79">
+        <v>0.1926423497032768</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5497778374577265</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2130727976987592</v>
+      </c>
+      <c r="C80">
+        <v>-21.03860980206804</v>
+      </c>
+      <c r="D80">
+        <v>25.22939019793196</v>
+      </c>
+      <c r="E80">
+        <v>47.86799999999999</v>
+      </c>
+      <c r="F80">
+        <v>70.66799999999999</v>
+      </c>
+      <c r="G80">
+        <v>24.4</v>
+      </c>
+      <c r="H80">
+        <v>67.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>21.6</v>
+      </c>
+      <c r="K80">
+        <v>13.4</v>
+      </c>
+      <c r="L80">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M80">
+        <v>15.1088184</v>
+      </c>
+      <c r="N80">
+        <v>-6.908818399999996</v>
+      </c>
+      <c r="O80">
+        <v>-1.243587312</v>
+      </c>
+      <c r="P80">
+        <v>-5.665231087999996</v>
+      </c>
+      <c r="Q80">
+        <v>7.734768912000004</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2845463110328909</v>
+      </c>
+      <c r="T80">
+        <v>4.155162761630247</v>
+      </c>
+      <c r="U80">
+        <v>0.2138</v>
+      </c>
+      <c r="V80">
+        <v>0.0976912926559499</v>
+      </c>
+      <c r="W80">
+        <v>0.1929136016301579</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5427294036441661</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2148227976987592</v>
+      </c>
+      <c r="C81">
+        <v>-22.17329577239536</v>
+      </c>
+      <c r="D81">
+        <v>25.00070422760464</v>
+      </c>
+      <c r="E81">
+        <v>48.774</v>
+      </c>
+      <c r="F81">
+        <v>71.574</v>
+      </c>
+      <c r="G81">
+        <v>24.4</v>
+      </c>
+      <c r="H81">
+        <v>67.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>21.6</v>
+      </c>
+      <c r="K81">
+        <v>13.4</v>
+      </c>
+      <c r="L81">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M81">
+        <v>15.3025212</v>
+      </c>
+      <c r="N81">
+        <v>-7.102521199999998</v>
+      </c>
+      <c r="O81">
+        <v>-1.278453816</v>
+      </c>
+      <c r="P81">
+        <v>-5.824067383999998</v>
+      </c>
+      <c r="Q81">
+        <v>7.575932616000002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2962485163201715</v>
+      </c>
+      <c r="T81">
+        <v>4.353027655041211</v>
+      </c>
+      <c r="U81">
+        <v>0.2138</v>
+      </c>
+      <c r="V81">
+        <v>0.09645469401473535</v>
+      </c>
+      <c r="W81">
+        <v>0.1931779864196496</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.535859411192974</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2165727976987592</v>
+      </c>
+      <c r="C82">
+        <v>-23.30387324114709</v>
+      </c>
+      <c r="D82">
+        <v>24.77612675885292</v>
+      </c>
+      <c r="E82">
+        <v>49.68000000000001</v>
+      </c>
+      <c r="F82">
+        <v>72.48</v>
+      </c>
+      <c r="G82">
+        <v>24.4</v>
+      </c>
+      <c r="H82">
+        <v>67.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>21.6</v>
+      </c>
+      <c r="K82">
+        <v>13.4</v>
+      </c>
+      <c r="L82">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M82">
+        <v>15.496224</v>
+      </c>
+      <c r="N82">
+        <v>-7.296223999999999</v>
+      </c>
+      <c r="O82">
+        <v>-1.31332032</v>
+      </c>
+      <c r="P82">
+        <v>-5.982903679999999</v>
+      </c>
+      <c r="Q82">
+        <v>7.417096320000002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.30912094213618</v>
+      </c>
+      <c r="T82">
+        <v>4.570679037793272</v>
+      </c>
+      <c r="U82">
+        <v>0.2138</v>
+      </c>
+      <c r="V82">
+        <v>0.09524901033955113</v>
+      </c>
+      <c r="W82">
+        <v>0.193435761589404</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5291611685530617</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2183227976987592</v>
+      </c>
+      <c r="C83">
+        <v>-24.43045194072126</v>
+      </c>
+      <c r="D83">
+        <v>24.55554805927873</v>
+      </c>
+      <c r="E83">
+        <v>50.586</v>
+      </c>
+      <c r="F83">
+        <v>73.386</v>
+      </c>
+      <c r="G83">
+        <v>24.4</v>
+      </c>
+      <c r="H83">
+        <v>67.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>21.6</v>
+      </c>
+      <c r="K83">
+        <v>13.4</v>
+      </c>
+      <c r="L83">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M83">
+        <v>15.6899268</v>
+      </c>
+      <c r="N83">
+        <v>-7.489926799999997</v>
+      </c>
+      <c r="O83">
+        <v>-1.348186824</v>
+      </c>
+      <c r="P83">
+        <v>-6.141739975999998</v>
+      </c>
+      <c r="Q83">
+        <v>7.258260024000003</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3233483601433474</v>
+      </c>
+      <c r="T83">
+        <v>4.811241092413971</v>
+      </c>
+      <c r="U83">
+        <v>0.2138</v>
+      </c>
+      <c r="V83">
+        <v>0.09407309663165547</v>
+      </c>
+      <c r="W83">
+        <v>0.1936871719401521</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.5226283146203079</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2200727976987591</v>
+      </c>
+      <c r="C84">
+        <v>-25.55313773026484</v>
+      </c>
+      <c r="D84">
+        <v>24.33886226973517</v>
+      </c>
+      <c r="E84">
+        <v>51.492</v>
+      </c>
+      <c r="F84">
+        <v>74.292</v>
+      </c>
+      <c r="G84">
+        <v>24.4</v>
+      </c>
+      <c r="H84">
+        <v>67.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>21.6</v>
+      </c>
+      <c r="K84">
+        <v>13.4</v>
+      </c>
+      <c r="L84">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M84">
+        <v>15.8836296</v>
+      </c>
+      <c r="N84">
+        <v>-7.683629599999998</v>
+      </c>
+      <c r="O84">
+        <v>-1.383053328</v>
+      </c>
+      <c r="P84">
+        <v>-6.300576271999998</v>
+      </c>
+      <c r="Q84">
+        <v>7.099423728000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3391566023735333</v>
+      </c>
+      <c r="T84">
+        <v>5.078532264214746</v>
+      </c>
+      <c r="U84">
+        <v>0.2138</v>
+      </c>
+      <c r="V84">
+        <v>0.09292586374590356</v>
+      </c>
+      <c r="W84">
+        <v>0.1939324503311258</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.516254798588353</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2218227976987592</v>
+      </c>
+      <c r="C85">
+        <v>-26.67203276507255</v>
+      </c>
+      <c r="D85">
+        <v>24.12596723492746</v>
+      </c>
+      <c r="E85">
+        <v>52.39800000000001</v>
+      </c>
+      <c r="F85">
+        <v>75.19800000000001</v>
+      </c>
+      <c r="G85">
+        <v>24.4</v>
+      </c>
+      <c r="H85">
+        <v>67.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>21.6</v>
+      </c>
+      <c r="K85">
+        <v>13.4</v>
+      </c>
+      <c r="L85">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M85">
+        <v>16.0773324</v>
+      </c>
+      <c r="N85">
+        <v>-7.877332399999998</v>
+      </c>
+      <c r="O85">
+        <v>-1.417919832</v>
+      </c>
+      <c r="P85">
+        <v>-6.459412567999999</v>
+      </c>
+      <c r="Q85">
+        <v>6.940587432000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3568246378072706</v>
+      </c>
+      <c r="T85">
+        <v>5.37726945622738</v>
+      </c>
+      <c r="U85">
+        <v>0.2138</v>
+      </c>
+      <c r="V85">
+        <v>0.0918062750260734</v>
+      </c>
+      <c r="W85">
+        <v>0.1941718183994255</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5100348612559631</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2235727976987592</v>
+      </c>
+      <c r="C86">
+        <v>-27.78723565717261</v>
+      </c>
+      <c r="D86">
+        <v>23.91676434282739</v>
+      </c>
+      <c r="E86">
+        <v>53.304</v>
+      </c>
+      <c r="F86">
+        <v>76.104</v>
+      </c>
+      <c r="G86">
+        <v>24.4</v>
+      </c>
+      <c r="H86">
+        <v>67.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>21.6</v>
+      </c>
+      <c r="K86">
+        <v>13.4</v>
+      </c>
+      <c r="L86">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M86">
+        <v>16.2710352</v>
+      </c>
+      <c r="N86">
+        <v>-8.071035199999999</v>
+      </c>
+      <c r="O86">
+        <v>-1.452786336</v>
+      </c>
+      <c r="P86">
+        <v>-6.618248863999999</v>
+      </c>
+      <c r="Q86">
+        <v>6.781751136000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3767011776702249</v>
+      </c>
+      <c r="T86">
+        <v>5.713348797241588</v>
+      </c>
+      <c r="U86">
+        <v>0.2138</v>
+      </c>
+      <c r="V86">
+        <v>0.0907133431805249</v>
+      </c>
+      <c r="W86">
+        <v>0.1944054872280038</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5039630176695826</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2470396585989481</v>
+      </c>
+      <c r="C87">
+        <v>-31.18455680739095</v>
+      </c>
+      <c r="D87">
+        <v>21.42544319260904</v>
+      </c>
+      <c r="E87">
+        <v>54.20999999999999</v>
+      </c>
+      <c r="F87">
+        <v>77.00999999999999</v>
+      </c>
+      <c r="G87">
+        <v>24.4</v>
+      </c>
+      <c r="H87">
+        <v>67.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>21.6</v>
+      </c>
+      <c r="K87">
+        <v>13.4</v>
+      </c>
+      <c r="L87">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M87">
+        <v>18.389988</v>
+      </c>
+      <c r="N87">
+        <v>-10.189988</v>
+      </c>
+      <c r="O87">
+        <v>-1.83419784</v>
+      </c>
+      <c r="P87">
+        <v>-8.355790159999998</v>
+      </c>
+      <c r="Q87">
+        <v>5.044209840000002</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4023403288494995</v>
+      </c>
+      <c r="T87">
+        <v>6.14686434330271</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.08026106379188505</v>
+      </c>
+      <c r="W87">
+        <v>0.2196336579664979</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.4458947988438058</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2490396585989481</v>
+      </c>
+      <c r="C88">
+        <v>-32.27909249223615</v>
+      </c>
+      <c r="D88">
+        <v>21.23690750776385</v>
+      </c>
+      <c r="E88">
+        <v>55.116</v>
+      </c>
+      <c r="F88">
+        <v>77.916</v>
+      </c>
+      <c r="G88">
+        <v>24.4</v>
+      </c>
+      <c r="H88">
+        <v>67.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>21.6</v>
+      </c>
+      <c r="K88">
+        <v>13.4</v>
+      </c>
+      <c r="L88">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M88">
+        <v>18.6063408</v>
+      </c>
+      <c r="N88">
+        <v>-10.4063408</v>
+      </c>
+      <c r="O88">
+        <v>-1.873141344000001</v>
+      </c>
+      <c r="P88">
+        <v>-8.533199456</v>
+      </c>
+      <c r="Q88">
+        <v>4.866800544</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4283074951958923</v>
+      </c>
+      <c r="T88">
+        <v>6.585926082110046</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.07932779560825846</v>
+      </c>
+      <c r="W88">
+        <v>0.2198565224087479</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.4407099756014359</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2510396585989481</v>
+      </c>
+      <c r="C89">
+        <v>-33.3703390367836</v>
+      </c>
+      <c r="D89">
+        <v>21.05166096321639</v>
+      </c>
+      <c r="E89">
+        <v>56.02199999999999</v>
+      </c>
+      <c r="F89">
+        <v>78.82199999999999</v>
+      </c>
+      <c r="G89">
+        <v>24.4</v>
+      </c>
+      <c r="H89">
+        <v>67.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>21.6</v>
+      </c>
+      <c r="K89">
+        <v>13.4</v>
+      </c>
+      <c r="L89">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M89">
+        <v>18.8226936</v>
+      </c>
+      <c r="N89">
+        <v>-10.6226936</v>
+      </c>
+      <c r="O89">
+        <v>-1.912084848</v>
+      </c>
+      <c r="P89">
+        <v>-8.710608751999997</v>
+      </c>
+      <c r="Q89">
+        <v>4.689391248000003</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4582696102109609</v>
+      </c>
+      <c r="T89">
+        <v>7.092535780733894</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.07841598186563484</v>
+      </c>
+      <c r="W89">
+        <v>0.2200742635304864</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.4356443436979711</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2530396585989481</v>
+      </c>
+      <c r="C90">
+        <v>-34.45838176884956</v>
+      </c>
+      <c r="D90">
+        <v>20.86961823115043</v>
+      </c>
+      <c r="E90">
+        <v>56.928</v>
+      </c>
+      <c r="F90">
+        <v>79.72799999999999</v>
+      </c>
+      <c r="G90">
+        <v>24.4</v>
+      </c>
+      <c r="H90">
+        <v>67.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>21.6</v>
+      </c>
+      <c r="K90">
+        <v>13.4</v>
+      </c>
+      <c r="L90">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M90">
+        <v>19.0390464</v>
+      </c>
+      <c r="N90">
+        <v>-10.8390464</v>
+      </c>
+      <c r="O90">
+        <v>-1.951028352</v>
+      </c>
+      <c r="P90">
+        <v>-8.888018047999999</v>
+      </c>
+      <c r="Q90">
+        <v>4.511981952000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4932254110618744</v>
+      </c>
+      <c r="T90">
+        <v>7.683580429128387</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.07752489116261624</v>
+      </c>
+      <c r="W90">
+        <v>0.2202870559903672</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.4306938397923123</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2550396585989481</v>
+      </c>
+      <c r="C91">
+        <v>-35.54330309008925</v>
+      </c>
+      <c r="D91">
+        <v>20.69069690991074</v>
+      </c>
+      <c r="E91">
+        <v>57.834</v>
+      </c>
+      <c r="F91">
+        <v>80.634</v>
+      </c>
+      <c r="G91">
+        <v>24.4</v>
+      </c>
+      <c r="H91">
+        <v>67.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>21.6</v>
+      </c>
+      <c r="K91">
+        <v>13.4</v>
+      </c>
+      <c r="L91">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M91">
+        <v>19.2553992</v>
+      </c>
+      <c r="N91">
+        <v>-11.0553992</v>
+      </c>
+      <c r="O91">
+        <v>-1.989971856</v>
+      </c>
+      <c r="P91">
+        <v>-9.065427343999998</v>
+      </c>
+      <c r="Q91">
+        <v>4.334572656000002</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5345368120674993</v>
+      </c>
+      <c r="T91">
+        <v>8.38208774086733</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.07665382496977786</v>
+      </c>
+      <c r="W91">
+        <v>0.220495066597217</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4258545831654325</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2570396585989481</v>
+      </c>
+      <c r="C92">
+        <v>-36.62518260036487</v>
+      </c>
+      <c r="D92">
+        <v>20.51481739963512</v>
+      </c>
+      <c r="E92">
+        <v>58.73999999999999</v>
+      </c>
+      <c r="F92">
+        <v>81.53999999999999</v>
+      </c>
+      <c r="G92">
+        <v>24.4</v>
+      </c>
+      <c r="H92">
+        <v>67.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>21.6</v>
+      </c>
+      <c r="K92">
+        <v>13.4</v>
+      </c>
+      <c r="L92">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M92">
+        <v>19.471752</v>
+      </c>
+      <c r="N92">
+        <v>-11.271752</v>
+      </c>
+      <c r="O92">
+        <v>-2.02891536</v>
+      </c>
+      <c r="P92">
+        <v>-9.242836639999997</v>
+      </c>
+      <c r="Q92">
+        <v>4.157163360000004</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5841104932742494</v>
+      </c>
+      <c r="T92">
+        <v>9.220296514954066</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.07580211580344699</v>
+      </c>
+      <c r="W92">
+        <v>0.2206984547461369</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.4211228655747055</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2590396585989481</v>
+      </c>
+      <c r="C93">
+        <v>-37.70409721582383</v>
+      </c>
+      <c r="D93">
+        <v>20.34190278417617</v>
+      </c>
+      <c r="E93">
+        <v>59.646</v>
+      </c>
+      <c r="F93">
+        <v>82.446</v>
+      </c>
+      <c r="G93">
+        <v>24.4</v>
+      </c>
+      <c r="H93">
+        <v>67.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>21.6</v>
+      </c>
+      <c r="K93">
+        <v>13.4</v>
+      </c>
+      <c r="L93">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M93">
+        <v>19.6881048</v>
+      </c>
+      <c r="N93">
+        <v>-11.4881048</v>
+      </c>
+      <c r="O93">
+        <v>-2.067858864000001</v>
+      </c>
+      <c r="P93">
+        <v>-9.420245936000001</v>
+      </c>
+      <c r="Q93">
+        <v>3.979754064</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6447005480824992</v>
+      </c>
+      <c r="T93">
+        <v>10.24477390550452</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.07496912551989263</v>
+      </c>
+      <c r="W93">
+        <v>0.2208973728258496</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.4164951417771812</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2610396585989481</v>
+      </c>
+      <c r="C94">
+        <v>-38.7801212810555</v>
+      </c>
+      <c r="D94">
+        <v>20.17187871894451</v>
+      </c>
+      <c r="E94">
+        <v>60.55200000000001</v>
+      </c>
+      <c r="F94">
+        <v>83.352</v>
+      </c>
+      <c r="G94">
+        <v>24.4</v>
+      </c>
+      <c r="H94">
+        <v>67.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>21.6</v>
+      </c>
+      <c r="K94">
+        <v>13.4</v>
+      </c>
+      <c r="L94">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M94">
+        <v>19.9044576</v>
+      </c>
+      <c r="N94">
+        <v>-11.7044576</v>
+      </c>
+      <c r="O94">
+        <v>-2.106802368</v>
+      </c>
+      <c r="P94">
+        <v>-9.597655231999999</v>
+      </c>
+      <c r="Q94">
+        <v>3.802344768000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.720438116592812</v>
+      </c>
+      <c r="T94">
+        <v>11.52537064369259</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.07415424372076336</v>
+      </c>
+      <c r="W94">
+        <v>0.2210919665994817</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.4119680206709074</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2630396585989481</v>
+      </c>
+      <c r="C95">
+        <v>-39.85332667566978</v>
+      </c>
+      <c r="D95">
+        <v>20.00467332433022</v>
+      </c>
+      <c r="E95">
+        <v>61.458</v>
+      </c>
+      <c r="F95">
+        <v>84.258</v>
+      </c>
+      <c r="G95">
+        <v>24.4</v>
+      </c>
+      <c r="H95">
+        <v>67.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>21.6</v>
+      </c>
+      <c r="K95">
+        <v>13.4</v>
+      </c>
+      <c r="L95">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M95">
+        <v>20.1208104</v>
+      </c>
+      <c r="N95">
+        <v>-11.9208104</v>
+      </c>
+      <c r="O95">
+        <v>-2.145745872</v>
+      </c>
+      <c r="P95">
+        <v>-9.775064527999998</v>
+      </c>
+      <c r="Q95">
+        <v>3.624935472000002</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8178149903917851</v>
+      </c>
+      <c r="T95">
+        <v>13.1718521642201</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.07335688626140031</v>
+      </c>
+      <c r="W95">
+        <v>0.2212823755607776</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.4075382570077795</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2650396585989481</v>
+      </c>
+      <c r="C96">
+        <v>-40.92378291561892</v>
+      </c>
+      <c r="D96">
+        <v>19.84021708438109</v>
+      </c>
+      <c r="E96">
+        <v>62.364</v>
+      </c>
+      <c r="F96">
+        <v>85.164</v>
+      </c>
+      <c r="G96">
+        <v>24.4</v>
+      </c>
+      <c r="H96">
+        <v>67.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>21.6</v>
+      </c>
+      <c r="K96">
+        <v>13.4</v>
+      </c>
+      <c r="L96">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M96">
+        <v>20.3371632</v>
+      </c>
+      <c r="N96">
+        <v>-12.1371632</v>
+      </c>
+      <c r="O96">
+        <v>-2.184689376000001</v>
+      </c>
+      <c r="P96">
+        <v>-9.952473824</v>
+      </c>
+      <c r="Q96">
+        <v>3.447526176</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9476508221237496</v>
+      </c>
+      <c r="T96">
+        <v>15.36716085825679</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.07257649385436413</v>
+      </c>
+      <c r="W96">
+        <v>0.2214687332675778</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.4032027436353561</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2670396585989481</v>
+      </c>
+      <c r="C97">
+        <v>-41.99155724956194</v>
+      </c>
+      <c r="D97">
+        <v>19.67844275043808</v>
+      </c>
+      <c r="E97">
+        <v>63.27000000000001</v>
+      </c>
+      <c r="F97">
+        <v>86.07000000000001</v>
+      </c>
+      <c r="G97">
+        <v>24.4</v>
+      </c>
+      <c r="H97">
+        <v>67.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>21.6</v>
+      </c>
+      <c r="K97">
+        <v>13.4</v>
+      </c>
+      <c r="L97">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M97">
+        <v>20.553516</v>
+      </c>
+      <c r="N97">
+        <v>-12.353516</v>
+      </c>
+      <c r="O97">
+        <v>-2.223632880000001</v>
+      </c>
+      <c r="P97">
+        <v>-10.12988312</v>
+      </c>
+      <c r="Q97">
+        <v>3.27011688</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.1294209865485</v>
+      </c>
+      <c r="T97">
+        <v>18.44059302990815</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0718125307611603</v>
+      </c>
+      <c r="W97">
+        <v>0.2216511676542349</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3989585042286682</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2690396585989481</v>
+      </c>
+      <c r="C98">
+        <v>-43.0567147505531</v>
+      </c>
+      <c r="D98">
+        <v>19.51928524944688</v>
+      </c>
+      <c r="E98">
+        <v>64.17599999999999</v>
+      </c>
+      <c r="F98">
+        <v>86.97599999999998</v>
+      </c>
+      <c r="G98">
+        <v>24.4</v>
+      </c>
+      <c r="H98">
+        <v>67.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>21.6</v>
+      </c>
+      <c r="K98">
+        <v>13.4</v>
+      </c>
+      <c r="L98">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M98">
+        <v>20.7698688</v>
+      </c>
+      <c r="N98">
+        <v>-12.5698688</v>
+      </c>
+      <c r="O98">
+        <v>-2.262576384</v>
+      </c>
+      <c r="P98">
+        <v>-10.307292416</v>
+      </c>
+      <c r="Q98">
+        <v>3.092707584000005</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.402076233185622</v>
+      </c>
+      <c r="T98">
+        <v>23.05074128738514</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.07106448356573157</v>
+      </c>
+      <c r="W98">
+        <v>0.2218298013245033</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3948026864762864</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2710396585989481</v>
+      </c>
+      <c r="C99">
+        <v>-44.11931840331663</v>
+      </c>
+      <c r="D99">
+        <v>19.36268159668336</v>
+      </c>
+      <c r="E99">
+        <v>65.08199999999999</v>
+      </c>
+      <c r="F99">
+        <v>87.88199999999999</v>
+      </c>
+      <c r="G99">
+        <v>24.4</v>
+      </c>
+      <c r="H99">
+        <v>67.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>21.6</v>
+      </c>
+      <c r="K99">
+        <v>13.4</v>
+      </c>
+      <c r="L99">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M99">
+        <v>20.9862216</v>
+      </c>
+      <c r="N99">
+        <v>-12.7862216</v>
+      </c>
+      <c r="O99">
+        <v>-2.301519888000001</v>
+      </c>
+      <c r="P99">
+        <v>-10.484701712</v>
+      </c>
+      <c r="Q99">
+        <v>2.915298288000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.856501644247496</v>
+      </c>
+      <c r="T99">
+        <v>30.73432171651352</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.07033186002381679</v>
+      </c>
+      <c r="W99">
+        <v>0.2220047518263126</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.390732555687871</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2730396585989481</v>
+      </c>
+      <c r="C100">
+        <v>-45.17942918735328</v>
+      </c>
+      <c r="D100">
+        <v>19.20857081264672</v>
+      </c>
+      <c r="E100">
+        <v>65.988</v>
+      </c>
+      <c r="F100">
+        <v>88.788</v>
+      </c>
+      <c r="G100">
+        <v>24.4</v>
+      </c>
+      <c r="H100">
+        <v>67.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>21.6</v>
+      </c>
+      <c r="K100">
+        <v>13.4</v>
+      </c>
+      <c r="L100">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M100">
+        <v>21.2025744</v>
+      </c>
+      <c r="N100">
+        <v>-13.0025744</v>
+      </c>
+      <c r="O100">
+        <v>-2.340463392</v>
+      </c>
+      <c r="P100">
+        <v>-10.662111008</v>
+      </c>
+      <c r="Q100">
+        <v>2.737888992000002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.765352466371244</v>
+      </c>
+      <c r="T100">
+        <v>46.10148257477028</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.06961418798275744</v>
+      </c>
+      <c r="W100">
+        <v>0.2221761319097176</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3867454887930968</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2750396585989481</v>
+      </c>
+      <c r="C101">
+        <v>-46.23710615610992</v>
+      </c>
+      <c r="D101">
+        <v>19.05689384389008</v>
+      </c>
+      <c r="E101">
+        <v>66.89399999999999</v>
+      </c>
+      <c r="F101">
+        <v>89.69399999999999</v>
+      </c>
+      <c r="G101">
+        <v>24.4</v>
+      </c>
+      <c r="H101">
+        <v>67.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>21.6</v>
+      </c>
+      <c r="K101">
+        <v>13.4</v>
+      </c>
+      <c r="L101">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="M101">
+        <v>21.4189272</v>
+      </c>
+      <c r="N101">
+        <v>-13.2189272</v>
+      </c>
+      <c r="O101">
+        <v>-2.379406896</v>
+      </c>
+      <c r="P101">
+        <v>-10.839520304</v>
+      </c>
+      <c r="Q101">
+        <v>2.560479696000003</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.491904932742488</v>
+      </c>
+      <c r="T101">
+        <v>92.20296514954057</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06891101436677</v>
+      </c>
+      <c r="W101">
+        <v>0.2223440497692153</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3828389687042777</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_recreation.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_recreation.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08463775155252931</v>
+        <v>0.08455261043526259</v>
       </c>
       <c r="C2">
-        <v>153.8995662142906</v>
+        <v>152.6256506796417</v>
       </c>
       <c r="D2">
-        <v>133.3995662142906</v>
+        <v>133.6926506796417</v>
       </c>
       <c r="E2">
-        <v>-17.3</v>
+        <v>-15.733</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.567</v>
       </c>
       <c r="G2">
         <v>20.5</v>
@@ -1445,28 +1445,28 @@
         <v>19.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0788201</v>
       </c>
       <c r="N2">
-        <v>19.6</v>
+        <v>19.5211799</v>
       </c>
       <c r="O2">
-        <v>2.8616</v>
+        <v>2.8500922654</v>
       </c>
       <c r="P2">
-        <v>16.7384</v>
+        <v>16.6710876346</v>
       </c>
       <c r="Q2">
-        <v>31.3384</v>
+        <v>31.2710876346</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08463775155252931</v>
+        <v>0.08497277619723495</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.9046830530539252</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>248.6675353114244</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08455261043526259</v>
+        <v>0.08446746931799591</v>
       </c>
       <c r="C3">
-        <v>152.6256506796417</v>
+        <v>151.3530258184852</v>
       </c>
       <c r="D3">
-        <v>133.6926506796417</v>
+        <v>133.9870258184851</v>
       </c>
       <c r="E3">
-        <v>-15.733</v>
+        <v>-14.166</v>
       </c>
       <c r="F3">
-        <v>1.567</v>
+        <v>3.134</v>
       </c>
       <c r="G3">
         <v>20.5</v>
@@ -1527,28 +1527,28 @@
         <v>19.6</v>
       </c>
       <c r="M3">
-        <v>0.0788201</v>
+        <v>0.1576402</v>
       </c>
       <c r="N3">
-        <v>19.5211799</v>
+        <v>19.4423598</v>
       </c>
       <c r="O3">
-        <v>2.8500922654</v>
+        <v>2.8385845308</v>
       </c>
       <c r="P3">
-        <v>16.6710876346</v>
+        <v>16.6037752692</v>
       </c>
       <c r="Q3">
-        <v>31.2710876346</v>
+        <v>31.2037752692</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08497277619723495</v>
+        <v>0.08531463807958767</v>
       </c>
       <c r="T3">
-        <v>0.9046830530539252</v>
+        <v>0.9125782466417476</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>248.6675353114244</v>
+        <v>124.3337676557122</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08446746931799591</v>
+        <v>0.08438232820072922</v>
       </c>
       <c r="C4">
-        <v>151.3530258184852</v>
+        <v>150.0817001753585</v>
       </c>
       <c r="D4">
-        <v>133.9870258184851</v>
+        <v>134.2827001753585</v>
       </c>
       <c r="E4">
-        <v>-14.166</v>
+        <v>-12.599</v>
       </c>
       <c r="F4">
-        <v>3.134</v>
+        <v>4.701000000000001</v>
       </c>
       <c r="G4">
         <v>20.5</v>
@@ -1609,28 +1609,28 @@
         <v>19.6</v>
       </c>
       <c r="M4">
-        <v>0.1576402</v>
+        <v>0.2364603</v>
       </c>
       <c r="N4">
-        <v>19.4423598</v>
+        <v>19.3635397</v>
       </c>
       <c r="O4">
-        <v>2.8385845308</v>
+        <v>2.8270767962</v>
       </c>
       <c r="P4">
-        <v>16.6037752692</v>
+        <v>16.5364629038</v>
       </c>
       <c r="Q4">
-        <v>31.2037752692</v>
+        <v>31.1364629038</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08531463807958767</v>
+        <v>0.0856635486605456</v>
       </c>
       <c r="T4">
-        <v>0.9125782466417476</v>
+        <v>0.9206362277262261</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>124.3337676557122</v>
+        <v>82.88917843714145</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08438232820072922</v>
+        <v>0.08429718708346254</v>
       </c>
       <c r="C5">
-        <v>150.0817001753585</v>
+        <v>148.8116823703882</v>
       </c>
       <c r="D5">
-        <v>134.2827001753585</v>
+        <v>134.5796823703882</v>
       </c>
       <c r="E5">
-        <v>-12.599</v>
+        <v>-11.032</v>
       </c>
       <c r="F5">
-        <v>4.701000000000001</v>
+        <v>6.268000000000001</v>
       </c>
       <c r="G5">
         <v>20.5</v>
@@ -1691,28 +1691,28 @@
         <v>19.6</v>
       </c>
       <c r="M5">
-        <v>0.2364603</v>
+        <v>0.3152804</v>
       </c>
       <c r="N5">
-        <v>19.3635397</v>
+        <v>19.2847196</v>
       </c>
       <c r="O5">
-        <v>2.8270767962</v>
+        <v>2.8155690616</v>
       </c>
       <c r="P5">
-        <v>16.5364629038</v>
+        <v>16.4691505384</v>
       </c>
       <c r="Q5">
-        <v>31.1364629038</v>
+        <v>31.0691505384</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0856635486605456</v>
+        <v>0.08601972821194014</v>
       </c>
       <c r="T5">
-        <v>0.9206362277262261</v>
+        <v>0.9288620834166313</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>82.88917843714145</v>
+        <v>62.1668838278561</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08429718708346254</v>
+        <v>0.08421204596619583</v>
       </c>
       <c r="C6">
-        <v>148.8116823703882</v>
+        <v>147.5429811001277</v>
       </c>
       <c r="D6">
-        <v>134.5796823703882</v>
+        <v>134.8779811001278</v>
       </c>
       <c r="E6">
-        <v>-11.032</v>
+        <v>-9.465</v>
       </c>
       <c r="F6">
-        <v>6.268000000000001</v>
+        <v>7.835000000000001</v>
       </c>
       <c r="G6">
         <v>20.5</v>
@@ -1773,28 +1773,28 @@
         <v>19.6</v>
       </c>
       <c r="M6">
-        <v>0.3152804</v>
+        <v>0.3941005</v>
       </c>
       <c r="N6">
-        <v>19.2847196</v>
+        <v>19.2058995</v>
       </c>
       <c r="O6">
-        <v>2.8155690616</v>
+        <v>2.804061327</v>
       </c>
       <c r="P6">
-        <v>16.4691505384</v>
+        <v>16.401838173</v>
       </c>
       <c r="Q6">
-        <v>31.0691505384</v>
+        <v>31.001838173</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08601972821194014</v>
+        <v>0.08638340628020615</v>
       </c>
       <c r="T6">
-        <v>0.9288620834166313</v>
+        <v>0.9372611150163083</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>62.1668838278561</v>
+        <v>49.73350706228487</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08421204596619583</v>
+        <v>0.08412690484892914</v>
       </c>
       <c r="C7">
-        <v>147.5429811001277</v>
+        <v>146.275605138406</v>
       </c>
       <c r="D7">
-        <v>134.8779811001278</v>
+        <v>135.177605138406</v>
       </c>
       <c r="E7">
-        <v>-9.465</v>
+        <v>-7.898</v>
       </c>
       <c r="F7">
-        <v>7.835000000000001</v>
+        <v>9.402000000000001</v>
       </c>
       <c r="G7">
         <v>20.5</v>
@@ -1855,28 +1855,28 @@
         <v>19.6</v>
       </c>
       <c r="M7">
-        <v>0.3941005</v>
+        <v>0.4729206</v>
       </c>
       <c r="N7">
-        <v>19.2058995</v>
+        <v>19.1270794</v>
       </c>
       <c r="O7">
-        <v>2.804061327</v>
+        <v>2.7925535924</v>
       </c>
       <c r="P7">
-        <v>16.401838173</v>
+        <v>16.3345258076</v>
       </c>
       <c r="Q7">
-        <v>31.001838173</v>
+        <v>30.9345258076</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08638340628020615</v>
+        <v>0.08675482217971187</v>
       </c>
       <c r="T7">
-        <v>0.9372611150163083</v>
+        <v>0.9458388494159784</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>49.73350706228487</v>
+        <v>41.44458921857073</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08412690484892914</v>
+        <v>0.08404176373166247</v>
       </c>
       <c r="C8">
-        <v>146.275605138406</v>
+        <v>145.0095633371876</v>
       </c>
       <c r="D8">
-        <v>135.177605138406</v>
+        <v>135.4785633371876</v>
       </c>
       <c r="E8">
-        <v>-7.898</v>
+        <v>-6.331000000000001</v>
       </c>
       <c r="F8">
-        <v>9.402000000000001</v>
+        <v>10.969</v>
       </c>
       <c r="G8">
         <v>20.5</v>
@@ -1937,28 +1937,28 @@
         <v>19.6</v>
       </c>
       <c r="M8">
-        <v>0.4729206</v>
+        <v>0.5517407</v>
       </c>
       <c r="N8">
-        <v>19.1270794</v>
+        <v>19.0482593</v>
       </c>
       <c r="O8">
-        <v>2.7925535924</v>
+        <v>2.7810458578</v>
       </c>
       <c r="P8">
-        <v>16.3345258076</v>
+        <v>16.2672134422</v>
       </c>
       <c r="Q8">
-        <v>30.9345258076</v>
+        <v>30.8672134422</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08675482217971187</v>
+        <v>0.08713422551791662</v>
       </c>
       <c r="T8">
-        <v>0.9458388494159784</v>
+        <v>0.9546010512220929</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.44458921857073</v>
+        <v>35.52393361591777</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08404176373166246</v>
+        <v>0.08395662261439577</v>
       </c>
       <c r="C9">
-        <v>145.0095633371877</v>
+        <v>143.7448646274456</v>
       </c>
       <c r="D9">
-        <v>135.4785633371877</v>
+        <v>135.7808646274456</v>
       </c>
       <c r="E9">
-        <v>-6.330999999999998</v>
+        <v>-4.763999999999999</v>
       </c>
       <c r="F9">
-        <v>10.969</v>
+        <v>12.536</v>
       </c>
       <c r="G9">
         <v>20.5</v>
@@ -2019,28 +2019,28 @@
         <v>19.6</v>
       </c>
       <c r="M9">
-        <v>0.5517407000000001</v>
+        <v>0.6305608</v>
       </c>
       <c r="N9">
-        <v>19.0482593</v>
+        <v>18.9694392</v>
       </c>
       <c r="O9">
-        <v>2.7810458578</v>
+        <v>2.7695381232</v>
       </c>
       <c r="P9">
-        <v>16.2672134422</v>
+        <v>16.1999010768</v>
       </c>
       <c r="Q9">
-        <v>30.8672134422</v>
+        <v>30.7999010768</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08713422551791662</v>
+        <v>0.087521876754778</v>
       </c>
       <c r="T9">
-        <v>0.9546010512220929</v>
+        <v>0.9635537356761663</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.52393361591776</v>
+        <v>31.08344191392804</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08395662261439577</v>
+        <v>0.08387148149712909</v>
       </c>
       <c r="C10">
-        <v>143.7448646274456</v>
+        <v>142.4815180200431</v>
       </c>
       <c r="D10">
-        <v>135.7808646274456</v>
+        <v>136.0845180200431</v>
       </c>
       <c r="E10">
-        <v>-4.763999999999999</v>
+        <v>-3.196999999999999</v>
       </c>
       <c r="F10">
-        <v>12.536</v>
+        <v>14.103</v>
       </c>
       <c r="G10">
         <v>20.5</v>
@@ -2101,28 +2101,28 @@
         <v>19.6</v>
       </c>
       <c r="M10">
-        <v>0.6305608</v>
+        <v>0.7093809000000001</v>
       </c>
       <c r="N10">
-        <v>18.9694392</v>
+        <v>18.8906191</v>
       </c>
       <c r="O10">
-        <v>2.7695381232</v>
+        <v>2.7580303886</v>
       </c>
       <c r="P10">
-        <v>16.1999010768</v>
+        <v>16.1325887114</v>
       </c>
       <c r="Q10">
-        <v>30.7999010768</v>
+        <v>30.73258871140001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.087521876754778</v>
+        <v>0.08791804779904294</v>
       </c>
       <c r="T10">
-        <v>0.9635537356761663</v>
+        <v>0.9727031824259338</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.08344191392804</v>
+        <v>27.62972614571382</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08387148149712909</v>
+        <v>0.08378634037986238</v>
       </c>
       <c r="C11">
-        <v>142.4815180200431</v>
+        <v>141.2195326066304</v>
       </c>
       <c r="D11">
-        <v>136.0845180200431</v>
+        <v>136.3895326066304</v>
       </c>
       <c r="E11">
-        <v>-3.196999999999999</v>
+        <v>-1.630000000000001</v>
       </c>
       <c r="F11">
-        <v>14.103</v>
+        <v>15.67</v>
       </c>
       <c r="G11">
         <v>20.5</v>
@@ -2183,28 +2183,28 @@
         <v>19.6</v>
       </c>
       <c r="M11">
-        <v>0.7093809000000001</v>
+        <v>0.7882009999999999</v>
       </c>
       <c r="N11">
-        <v>18.8906191</v>
+        <v>18.811799</v>
       </c>
       <c r="O11">
-        <v>2.7580303886</v>
+        <v>2.746522654</v>
       </c>
       <c r="P11">
-        <v>16.1325887114</v>
+        <v>16.065276346</v>
       </c>
       <c r="Q11">
-        <v>30.73258871140001</v>
+        <v>30.665276346</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08791804779904294</v>
+        <v>0.08832302264429152</v>
       </c>
       <c r="T11">
-        <v>0.9727031824259338</v>
+        <v>0.9820559502145849</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.62972614571382</v>
+        <v>24.86675353114244</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08378634037986238</v>
+        <v>0.08370119926259567</v>
       </c>
       <c r="C12">
-        <v>141.2195326066304</v>
+        <v>139.9589175605512</v>
       </c>
       <c r="D12">
-        <v>136.3895326066304</v>
+        <v>136.6959175605512</v>
       </c>
       <c r="E12">
-        <v>-1.629999999999999</v>
+        <v>-0.06299999999999883</v>
       </c>
       <c r="F12">
-        <v>15.67</v>
+        <v>17.237</v>
       </c>
       <c r="G12">
         <v>20.5</v>
@@ -2265,28 +2265,28 @@
         <v>19.6</v>
       </c>
       <c r="M12">
-        <v>0.788201</v>
+        <v>0.8670211000000001</v>
       </c>
       <c r="N12">
-        <v>18.811799</v>
+        <v>18.7329789</v>
       </c>
       <c r="O12">
-        <v>2.746522654</v>
+        <v>2.7350149194</v>
       </c>
       <c r="P12">
-        <v>16.065276346</v>
+        <v>15.9979639806</v>
       </c>
       <c r="Q12">
-        <v>30.665276346</v>
+        <v>30.5979639806</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08832302264429152</v>
+        <v>0.08873709804786031</v>
       </c>
       <c r="T12">
-        <v>0.9820559502145849</v>
+        <v>0.9916188925602845</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.86675353114244</v>
+        <v>22.60613957376585</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08370119926259567</v>
+        <v>0.08361605814532899</v>
       </c>
       <c r="C13">
-        <v>139.9589175605512</v>
+        <v>138.6996821377626</v>
       </c>
       <c r="D13">
-        <v>136.6959175605512</v>
+        <v>137.0036821377626</v>
       </c>
       <c r="E13">
-        <v>-0.06299999999999883</v>
+        <v>1.504000000000001</v>
       </c>
       <c r="F13">
-        <v>17.237</v>
+        <v>18.804</v>
       </c>
       <c r="G13">
         <v>20.5</v>
@@ -2347,28 +2347,28 @@
         <v>19.6</v>
       </c>
       <c r="M13">
-        <v>0.8670211000000001</v>
+        <v>0.9458412</v>
       </c>
       <c r="N13">
-        <v>18.7329789</v>
+        <v>18.6541588</v>
       </c>
       <c r="O13">
-        <v>2.7350149194</v>
+        <v>2.7235071848</v>
       </c>
       <c r="P13">
-        <v>15.9979639806</v>
+        <v>15.9306516152</v>
       </c>
       <c r="Q13">
-        <v>30.5979639806</v>
+        <v>30.5306516152</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08873709804786031</v>
+        <v>0.08916058425605566</v>
       </c>
       <c r="T13">
-        <v>0.9916188925602845</v>
+        <v>1.00139917450475</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.60613957376585</v>
+        <v>20.72229460928536</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08361605814532899</v>
+        <v>0.08353091702806228</v>
       </c>
       <c r="C14">
-        <v>138.6996821377626</v>
+        <v>137.4418356777676</v>
       </c>
       <c r="D14">
-        <v>137.0036821377626</v>
+        <v>137.3128356777676</v>
       </c>
       <c r="E14">
-        <v>1.504000000000001</v>
+        <v>3.071000000000002</v>
       </c>
       <c r="F14">
-        <v>18.804</v>
+        <v>20.371</v>
       </c>
       <c r="G14">
         <v>20.5</v>
@@ -2429,28 +2429,28 @@
         <v>19.6</v>
       </c>
       <c r="M14">
-        <v>0.9458412</v>
+        <v>1.0246613</v>
       </c>
       <c r="N14">
-        <v>18.6541588</v>
+        <v>18.5753387</v>
       </c>
       <c r="O14">
-        <v>2.7235071848</v>
+        <v>2.7119994502</v>
       </c>
       <c r="P14">
-        <v>15.9306516152</v>
+        <v>15.8633392498</v>
       </c>
       <c r="Q14">
-        <v>30.5306516152</v>
+        <v>30.4633392498</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08916058425605566</v>
+        <v>0.08959380577938195</v>
       </c>
       <c r="T14">
-        <v>1.00139917450475</v>
+        <v>1.011404290516904</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.72229460928536</v>
+        <v>19.12827194703265</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08353091702806228</v>
+        <v>0.08344577591079561</v>
       </c>
       <c r="C15">
-        <v>137.4418356777676</v>
+        <v>136.1853876045591</v>
       </c>
       <c r="D15">
-        <v>137.3128356777676</v>
+        <v>137.6233876045592</v>
       </c>
       <c r="E15">
-        <v>3.071000000000002</v>
+        <v>4.638000000000005</v>
       </c>
       <c r="F15">
-        <v>20.371</v>
+        <v>21.93800000000001</v>
       </c>
       <c r="G15">
         <v>20.5</v>
@@ -2511,28 +2511,28 @@
         <v>19.6</v>
       </c>
       <c r="M15">
-        <v>1.0246613</v>
+        <v>1.1034814</v>
       </c>
       <c r="N15">
-        <v>18.5753387</v>
+        <v>18.4965186</v>
       </c>
       <c r="O15">
-        <v>2.7119994502</v>
+        <v>2.7004917156</v>
       </c>
       <c r="P15">
-        <v>15.8633392498</v>
+        <v>15.7960268844</v>
       </c>
       <c r="Q15">
-        <v>30.4633392498</v>
+        <v>30.3960268844</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08959380577938195</v>
+        <v>0.09003710222185535</v>
       </c>
       <c r="T15">
-        <v>1.011404290516904</v>
+        <v>1.02164208364562</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.12827194703265</v>
+        <v>17.76196680795888</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08344577591079561</v>
+        <v>0.08336063479352891</v>
       </c>
       <c r="C16">
-        <v>136.1853876045591</v>
+        <v>134.9303474275784</v>
       </c>
       <c r="D16">
-        <v>137.6233876045592</v>
+        <v>137.9353474275784</v>
       </c>
       <c r="E16">
-        <v>4.638000000000005</v>
+        <v>6.205000000000005</v>
       </c>
       <c r="F16">
-        <v>21.93800000000001</v>
+        <v>23.50500000000001</v>
       </c>
       <c r="G16">
         <v>20.5</v>
@@ -2593,28 +2593,28 @@
         <v>19.6</v>
       </c>
       <c r="M16">
-        <v>1.1034814</v>
+        <v>1.1823015</v>
       </c>
       <c r="N16">
-        <v>18.4965186</v>
+        <v>18.4176985</v>
       </c>
       <c r="O16">
-        <v>2.7004917156</v>
+        <v>2.688983981</v>
       </c>
       <c r="P16">
-        <v>15.7960268844</v>
+        <v>15.728714519</v>
       </c>
       <c r="Q16">
-        <v>30.3960268844</v>
+        <v>30.328714519</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09003710222185535</v>
+        <v>0.09049082916885755</v>
       </c>
       <c r="T16">
-        <v>1.02164208364562</v>
+        <v>1.032120766024424</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.76196680795888</v>
+        <v>16.57783568742829</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08336063479352891</v>
+        <v>0.08327549367626222</v>
       </c>
       <c r="C17">
-        <v>134.9303474275784</v>
+        <v>133.6767247426848</v>
       </c>
       <c r="D17">
-        <v>137.9353474275784</v>
+        <v>138.2487247426848</v>
       </c>
       <c r="E17">
-        <v>6.205000000000002</v>
+        <v>7.772000000000002</v>
       </c>
       <c r="F17">
-        <v>23.505</v>
+        <v>25.072</v>
       </c>
       <c r="G17">
         <v>20.5</v>
@@ -2675,28 +2675,28 @@
         <v>19.6</v>
       </c>
       <c r="M17">
-        <v>1.1823015</v>
+        <v>1.2611216</v>
       </c>
       <c r="N17">
-        <v>18.4176985</v>
+        <v>18.3388784</v>
       </c>
       <c r="O17">
-        <v>2.688983981</v>
+        <v>2.6774762464</v>
       </c>
       <c r="P17">
-        <v>15.728714519</v>
+        <v>15.6614021536</v>
       </c>
       <c r="Q17">
-        <v>30.328714519</v>
+        <v>30.2614021536</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09049082916885755</v>
+        <v>0.09095535913840741</v>
       </c>
       <c r="T17">
-        <v>1.032120766024424</v>
+        <v>1.042848940840818</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.57783568742829</v>
+        <v>15.54172095696402</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08327549367626222</v>
+        <v>0.08319035255899551</v>
       </c>
       <c r="C18">
-        <v>133.6767247426848</v>
+        <v>132.4245292331404</v>
       </c>
       <c r="D18">
-        <v>138.2487247426848</v>
+        <v>138.5635292331404</v>
       </c>
       <c r="E18">
-        <v>7.772000000000002</v>
+        <v>9.339000000000006</v>
       </c>
       <c r="F18">
-        <v>25.072</v>
+        <v>26.63900000000001</v>
       </c>
       <c r="G18">
         <v>20.5</v>
@@ -2757,28 +2757,28 @@
         <v>19.6</v>
       </c>
       <c r="M18">
-        <v>1.2611216</v>
+        <v>1.3399417</v>
       </c>
       <c r="N18">
-        <v>18.3388784</v>
+        <v>18.2600583</v>
       </c>
       <c r="O18">
-        <v>2.6774762464</v>
+        <v>2.6659685118</v>
       </c>
       <c r="P18">
-        <v>15.6614021536</v>
+        <v>15.5940897882</v>
       </c>
       <c r="Q18">
-        <v>30.2614021536</v>
+        <v>30.1940897882</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09095535913840741</v>
+        <v>0.09143108260119942</v>
       </c>
       <c r="T18">
-        <v>1.042848940840818</v>
+        <v>1.053835625893751</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.54172095696402</v>
+        <v>14.62750207714261</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08319035255899551</v>
+        <v>0.08310521144172883</v>
       </c>
       <c r="C19">
-        <v>132.4245292331404</v>
+        <v>131.1737706706069</v>
       </c>
       <c r="D19">
-        <v>138.5635292331404</v>
+        <v>138.8797706706069</v>
       </c>
       <c r="E19">
-        <v>9.339000000000006</v>
+        <v>10.90600000000001</v>
       </c>
       <c r="F19">
-        <v>26.63900000000001</v>
+        <v>28.20600000000001</v>
       </c>
       <c r="G19">
         <v>20.5</v>
@@ -2839,28 +2839,28 @@
         <v>19.6</v>
       </c>
       <c r="M19">
-        <v>1.3399417</v>
+        <v>1.4187618</v>
       </c>
       <c r="N19">
-        <v>18.2600583</v>
+        <v>18.1812382</v>
       </c>
       <c r="O19">
-        <v>2.6659685118</v>
+        <v>2.6544607772</v>
       </c>
       <c r="P19">
-        <v>15.5940897882</v>
+        <v>15.5267774228</v>
       </c>
       <c r="Q19">
-        <v>30.1940897882</v>
+        <v>30.1267774228</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09143108260119942</v>
+        <v>0.09191840907527907</v>
       </c>
       <c r="T19">
-        <v>1.053835625893751</v>
+        <v>1.065090278874805</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.62750207714261</v>
+        <v>13.81486307285691</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08310521144172883</v>
+        <v>0.08302007032446215</v>
       </c>
       <c r="C20">
-        <v>131.1737706706069</v>
+        <v>129.9244589161571</v>
       </c>
       <c r="D20">
-        <v>138.8797706706069</v>
+        <v>139.1974589161571</v>
       </c>
       <c r="E20">
-        <v>10.906</v>
+        <v>12.473</v>
       </c>
       <c r="F20">
-        <v>28.206</v>
+        <v>29.773</v>
       </c>
       <c r="G20">
         <v>20.5</v>
@@ -2921,28 +2921,28 @@
         <v>19.6</v>
       </c>
       <c r="M20">
-        <v>1.4187618</v>
+        <v>1.4975819</v>
       </c>
       <c r="N20">
-        <v>18.1812382</v>
+        <v>18.1024181</v>
       </c>
       <c r="O20">
-        <v>2.6544607772</v>
+        <v>2.6429530426</v>
       </c>
       <c r="P20">
-        <v>15.5267774228</v>
+        <v>15.4594650574</v>
       </c>
       <c r="Q20">
-        <v>30.1267774228</v>
+        <v>30.0594650574</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09191840907527907</v>
+        <v>0.09241776830180512</v>
       </c>
       <c r="T20">
-        <v>1.065090278874805</v>
+        <v>1.076622824522058</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.81486307285691</v>
+        <v>13.08776501639076</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08302007032446215</v>
+        <v>0.08319112920719546</v>
       </c>
       <c r="C21">
-        <v>129.9244589161571</v>
+        <v>127.7206511409875</v>
       </c>
       <c r="D21">
-        <v>139.1974589161571</v>
+        <v>138.5606511409875</v>
       </c>
       <c r="E21">
-        <v>12.473</v>
+        <v>14.04</v>
       </c>
       <c r="F21">
-        <v>29.773</v>
+        <v>31.34</v>
       </c>
       <c r="G21">
         <v>20.5</v>
@@ -3003,45 +3003,45 @@
         <v>19.6</v>
       </c>
       <c r="M21">
-        <v>1.4975819</v>
+        <v>1.623412</v>
       </c>
       <c r="N21">
-        <v>18.1024181</v>
+        <v>17.976588</v>
       </c>
       <c r="O21">
-        <v>2.6429530426</v>
+        <v>2.624581848</v>
       </c>
       <c r="P21">
-        <v>15.4594650574</v>
+        <v>15.352006152</v>
       </c>
       <c r="Q21">
-        <v>30.0594650574</v>
+        <v>29.952006152</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09241776830180512</v>
+        <v>0.09292961150899431</v>
       </c>
       <c r="T21">
-        <v>1.076622824522058</v>
+        <v>1.088443683810492</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.08776501639076</v>
+        <v>12.07333689784232</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08319112920719546</v>
+        <v>0.08311879808992875</v>
       </c>
       <c r="C22">
-        <v>127.7206511409875</v>
+        <v>126.4222087371373</v>
       </c>
       <c r="D22">
-        <v>138.5606511409875</v>
+        <v>138.8292087371373</v>
       </c>
       <c r="E22">
-        <v>14.04</v>
+        <v>15.607</v>
       </c>
       <c r="F22">
-        <v>31.34</v>
+        <v>32.907</v>
       </c>
       <c r="G22">
         <v>20.5</v>
@@ -3085,28 +3085,28 @@
         <v>19.6</v>
       </c>
       <c r="M22">
-        <v>1.623412</v>
+        <v>1.7045826</v>
       </c>
       <c r="N22">
-        <v>17.976588</v>
+        <v>17.8954174</v>
       </c>
       <c r="O22">
-        <v>2.624581848</v>
+        <v>2.6127309404</v>
       </c>
       <c r="P22">
-        <v>15.352006152</v>
+        <v>15.2826864596</v>
       </c>
       <c r="Q22">
-        <v>29.952006152</v>
+        <v>29.8826864596</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09292961150899431</v>
+        <v>0.09345441277206171</v>
       </c>
       <c r="T22">
-        <v>1.088443683810492</v>
+        <v>1.100563805359393</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.07333689784232</v>
+        <v>11.49841609318316</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08311879808992875</v>
+        <v>0.08304646697266208</v>
       </c>
       <c r="C23">
-        <v>126.4222087371373</v>
+        <v>125.1248093890481</v>
       </c>
       <c r="D23">
-        <v>138.8292087371373</v>
+        <v>139.0988093890481</v>
       </c>
       <c r="E23">
-        <v>15.607</v>
+        <v>17.174</v>
       </c>
       <c r="F23">
-        <v>32.907</v>
+        <v>34.474</v>
       </c>
       <c r="G23">
         <v>20.5</v>
@@ -3167,28 +3167,28 @@
         <v>19.6</v>
       </c>
       <c r="M23">
-        <v>1.7045826</v>
+        <v>1.7857532</v>
       </c>
       <c r="N23">
-        <v>17.8954174</v>
+        <v>17.8142468</v>
       </c>
       <c r="O23">
-        <v>2.6127309404</v>
+        <v>2.6008800328</v>
       </c>
       <c r="P23">
-        <v>15.2826864596</v>
+        <v>15.2133667672</v>
       </c>
       <c r="Q23">
-        <v>29.8826864596</v>
+        <v>29.8133667672</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09345441277206171</v>
+        <v>0.09399267047777188</v>
       </c>
       <c r="T23">
-        <v>1.100563805359393</v>
+        <v>1.112994699255702</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.49841609318316</v>
+        <v>10.97576081622029</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08304646697266208</v>
+        <v>0.08297413585539537</v>
       </c>
       <c r="C24">
-        <v>125.1248093890481</v>
+        <v>123.828459185259</v>
       </c>
       <c r="D24">
-        <v>139.0988093890481</v>
+        <v>139.369459185259</v>
       </c>
       <c r="E24">
-        <v>17.174</v>
+        <v>18.741</v>
       </c>
       <c r="F24">
-        <v>34.474</v>
+        <v>36.041</v>
       </c>
       <c r="G24">
         <v>20.5</v>
@@ -3249,28 +3249,28 @@
         <v>19.6</v>
       </c>
       <c r="M24">
-        <v>1.7857532</v>
+        <v>1.8669238</v>
       </c>
       <c r="N24">
-        <v>17.8142468</v>
+        <v>17.7330762</v>
       </c>
       <c r="O24">
-        <v>2.6008800328</v>
+        <v>2.5890291252</v>
       </c>
       <c r="P24">
-        <v>15.2133667672</v>
+        <v>15.1440470748</v>
       </c>
       <c r="Q24">
-        <v>29.8133667672</v>
+        <v>29.7440470748</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09399267047777188</v>
+        <v>0.09454490890311087</v>
       </c>
       <c r="T24">
-        <v>1.112994699255702</v>
+        <v>1.125748473512953</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.97576081622029</v>
+        <v>10.49855382421072</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08297413585539537</v>
+        <v>0.08290180473812868</v>
       </c>
       <c r="C25">
-        <v>123.828459185259</v>
+        <v>122.5331642617877</v>
       </c>
       <c r="D25">
-        <v>139.369459185259</v>
+        <v>139.6411642617877</v>
       </c>
       <c r="E25">
-        <v>18.741</v>
+        <v>20.308</v>
       </c>
       <c r="F25">
-        <v>36.041</v>
+        <v>37.608</v>
       </c>
       <c r="G25">
         <v>20.5</v>
@@ -3331,28 +3331,28 @@
         <v>19.6</v>
       </c>
       <c r="M25">
-        <v>1.8669238</v>
+        <v>1.9480944</v>
       </c>
       <c r="N25">
-        <v>17.7330762</v>
+        <v>17.6519056</v>
       </c>
       <c r="O25">
-        <v>2.5890291252</v>
+        <v>2.5771782176</v>
       </c>
       <c r="P25">
-        <v>15.1440470748</v>
+        <v>15.0747273824</v>
       </c>
       <c r="Q25">
-        <v>29.7440470748</v>
+        <v>29.6747273824</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09454490890311087</v>
+        <v>0.09511167991859036</v>
       </c>
       <c r="T25">
-        <v>1.125748473512953</v>
+        <v>1.138837873408553</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.49855382421072</v>
+        <v>10.06111408153527</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08290180473812868</v>
+        <v>0.08319242362086197</v>
       </c>
       <c r="C26">
-        <v>122.5331642617877</v>
+        <v>119.8808545864155</v>
       </c>
       <c r="D26">
-        <v>139.6411642617877</v>
+        <v>138.5558545864155</v>
       </c>
       <c r="E26">
-        <v>20.308</v>
+        <v>21.875</v>
       </c>
       <c r="F26">
-        <v>37.608</v>
+        <v>39.175</v>
       </c>
       <c r="G26">
         <v>20.5</v>
@@ -3413,45 +3413,45 @@
         <v>19.6</v>
       </c>
       <c r="M26">
-        <v>1.9480944</v>
+        <v>2.0958625</v>
       </c>
       <c r="N26">
-        <v>17.6519056</v>
+        <v>17.5041375</v>
       </c>
       <c r="O26">
-        <v>2.5771782176</v>
+        <v>2.555604075</v>
       </c>
       <c r="P26">
-        <v>15.0747273824</v>
+        <v>14.948533425</v>
       </c>
       <c r="Q26">
-        <v>29.6747273824</v>
+        <v>29.548533425</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09511167991859036</v>
+        <v>0.09569356482781598</v>
       </c>
       <c r="T26">
-        <v>1.138837873408553</v>
+        <v>1.152276323968036</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>10.06111408153527</v>
+        <v>9.351758524235249</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08319242362086197</v>
+        <v>0.08313461050359527</v>
       </c>
       <c r="C27">
-        <v>119.8808545864155</v>
+        <v>118.5284100822716</v>
       </c>
       <c r="D27">
-        <v>138.5558545864155</v>
+        <v>138.7704100822716</v>
       </c>
       <c r="E27">
-        <v>21.875</v>
+        <v>23.442</v>
       </c>
       <c r="F27">
-        <v>39.175</v>
+        <v>40.742</v>
       </c>
       <c r="G27">
         <v>20.5</v>
@@ -3495,28 +3495,28 @@
         <v>19.6</v>
       </c>
       <c r="M27">
-        <v>2.0958625</v>
+        <v>2.179697</v>
       </c>
       <c r="N27">
-        <v>17.5041375</v>
+        <v>17.420303</v>
       </c>
       <c r="O27">
-        <v>2.555604075</v>
+        <v>2.543364238</v>
       </c>
       <c r="P27">
-        <v>14.948533425</v>
+        <v>14.876938762</v>
       </c>
       <c r="Q27">
-        <v>29.548533425</v>
+        <v>29.476938762</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09569356482781598</v>
+        <v>0.09629117635620985</v>
       </c>
       <c r="T27">
-        <v>1.152276323968036</v>
+        <v>1.166077975893992</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.351758524235249</v>
+        <v>8.992075504072355</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08313461050359527</v>
+        <v>0.0830767973863286</v>
       </c>
       <c r="C28">
-        <v>118.5284100822716</v>
+        <v>117.176631092491</v>
       </c>
       <c r="D28">
-        <v>138.7704100822716</v>
+        <v>138.985631092491</v>
       </c>
       <c r="E28">
-        <v>23.442</v>
+        <v>25.009</v>
       </c>
       <c r="F28">
-        <v>40.742</v>
+        <v>42.309</v>
       </c>
       <c r="G28">
         <v>20.5</v>
@@ -3577,28 +3577,28 @@
         <v>19.6</v>
       </c>
       <c r="M28">
-        <v>2.179697</v>
+        <v>2.2635315</v>
       </c>
       <c r="N28">
-        <v>17.420303</v>
+        <v>17.3364685</v>
       </c>
       <c r="O28">
-        <v>2.543364238</v>
+        <v>2.531124401</v>
       </c>
       <c r="P28">
-        <v>14.876938762</v>
+        <v>14.805344099</v>
       </c>
       <c r="Q28">
-        <v>29.476938762</v>
+        <v>29.405344099</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09629117635620985</v>
+        <v>0.09690516080318987</v>
       </c>
       <c r="T28">
-        <v>1.166077975893992</v>
+        <v>1.180257755269974</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.992075504072355</v>
+        <v>8.659035670588196</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0830767973863286</v>
+        <v>0.0830189842690619</v>
       </c>
       <c r="C29">
-        <v>117.176631092491</v>
+        <v>115.825520718351</v>
       </c>
       <c r="D29">
-        <v>138.985631092491</v>
+        <v>139.201520718351</v>
       </c>
       <c r="E29">
-        <v>25.009</v>
+        <v>26.57600000000001</v>
       </c>
       <c r="F29">
-        <v>42.309</v>
+        <v>43.87600000000001</v>
       </c>
       <c r="G29">
         <v>20.5</v>
@@ -3659,28 +3659,28 @@
         <v>19.6</v>
       </c>
       <c r="M29">
-        <v>2.2635315</v>
+        <v>2.347366000000001</v>
       </c>
       <c r="N29">
-        <v>17.3364685</v>
+        <v>17.252634</v>
       </c>
       <c r="O29">
-        <v>2.531124401</v>
+        <v>2.518884564</v>
       </c>
       <c r="P29">
-        <v>14.805344099</v>
+        <v>14.733749436</v>
       </c>
       <c r="Q29">
-        <v>29.405344099</v>
+        <v>29.333749436</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09690516080318987</v>
+        <v>0.09753620037369709</v>
       </c>
       <c r="T29">
-        <v>1.180257755269974</v>
+        <v>1.194831417406399</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.659035670588196</v>
+        <v>8.349784396638615</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0830189842690619</v>
+        <v>0.08296117115179522</v>
       </c>
       <c r="C30">
-        <v>115.825520718351</v>
+        <v>114.4750820804275</v>
       </c>
       <c r="D30">
-        <v>139.201520718351</v>
+        <v>139.4180820804275</v>
       </c>
       <c r="E30">
-        <v>26.57600000000001</v>
+        <v>28.14300000000001</v>
       </c>
       <c r="F30">
-        <v>43.87600000000001</v>
+        <v>45.44300000000001</v>
       </c>
       <c r="G30">
         <v>20.5</v>
@@ -3741,28 +3741,28 @@
         <v>19.6</v>
       </c>
       <c r="M30">
-        <v>2.347366000000001</v>
+        <v>2.431200500000001</v>
       </c>
       <c r="N30">
-        <v>17.252634</v>
+        <v>17.1687995</v>
       </c>
       <c r="O30">
-        <v>2.518884564</v>
+        <v>2.506644727</v>
       </c>
       <c r="P30">
-        <v>14.733749436</v>
+        <v>14.662154773</v>
       </c>
       <c r="Q30">
-        <v>29.333749436</v>
+        <v>29.262154773</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09753620037369709</v>
+        <v>0.09818501570675384</v>
       </c>
       <c r="T30">
-        <v>1.194831417406399</v>
+        <v>1.209815605236809</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.349784396638615</v>
+        <v>8.061860796754525</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08296117115179522</v>
+        <v>0.08290335803452852</v>
       </c>
       <c r="C31">
-        <v>114.4750820804275</v>
+        <v>113.1253183187462</v>
       </c>
       <c r="D31">
-        <v>139.4180820804275</v>
+        <v>139.6353183187462</v>
       </c>
       <c r="E31">
-        <v>28.143</v>
+        <v>29.71</v>
       </c>
       <c r="F31">
-        <v>45.443</v>
+        <v>47.01000000000001</v>
       </c>
       <c r="G31">
         <v>20.5</v>
@@ -3823,28 +3823,28 @@
         <v>19.6</v>
       </c>
       <c r="M31">
-        <v>2.4312005</v>
+        <v>2.515035</v>
       </c>
       <c r="N31">
-        <v>17.1687995</v>
+        <v>17.084965</v>
       </c>
       <c r="O31">
-        <v>2.506644727</v>
+        <v>2.49440489</v>
       </c>
       <c r="P31">
-        <v>14.662154773</v>
+        <v>14.59056011</v>
       </c>
       <c r="Q31">
-        <v>29.262154773</v>
+        <v>29.19056011</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09818501570675384</v>
+        <v>0.09885236862075503</v>
       </c>
       <c r="T31">
-        <v>1.209815605236809</v>
+        <v>1.225227912719516</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.061860796754527</v>
+        <v>7.793132103529374</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08290335803452852</v>
+        <v>0.08305733691726183</v>
       </c>
       <c r="C32">
-        <v>113.1253183187462</v>
+        <v>110.9812268762586</v>
       </c>
       <c r="D32">
-        <v>139.6353183187462</v>
+        <v>139.0582268762586</v>
       </c>
       <c r="E32">
-        <v>29.71</v>
+        <v>31.277</v>
       </c>
       <c r="F32">
-        <v>47.01000000000001</v>
+        <v>48.57700000000001</v>
       </c>
       <c r="G32">
         <v>20.5</v>
@@ -3905,45 +3905,45 @@
         <v>19.6</v>
       </c>
       <c r="M32">
-        <v>2.515035</v>
+        <v>2.6377311</v>
       </c>
       <c r="N32">
-        <v>17.084965</v>
+        <v>16.9622689</v>
       </c>
       <c r="O32">
-        <v>2.49440489</v>
+        <v>2.4764912594</v>
       </c>
       <c r="P32">
-        <v>14.59056011</v>
+        <v>14.4857776406</v>
       </c>
       <c r="Q32">
-        <v>29.19056011</v>
+        <v>29.0857776406</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09885236862075503</v>
+        <v>0.09953906509748092</v>
       </c>
       <c r="T32">
-        <v>1.225227912719516</v>
+        <v>1.241086953752446</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.793132103529374</v>
+        <v>7.430628542841232</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08305733691726183</v>
+        <v>0.08300635579999514</v>
       </c>
       <c r="C33">
-        <v>110.9812268762586</v>
+        <v>109.6047680786646</v>
       </c>
       <c r="D33">
-        <v>139.0582268762586</v>
+        <v>139.2487680786646</v>
       </c>
       <c r="E33">
-        <v>31.277</v>
+        <v>32.84400000000001</v>
       </c>
       <c r="F33">
-        <v>48.57700000000001</v>
+        <v>50.14400000000001</v>
       </c>
       <c r="G33">
         <v>20.5</v>
@@ -3987,28 +3987,28 @@
         <v>19.6</v>
       </c>
       <c r="M33">
-        <v>2.6377311</v>
+        <v>2.7228192</v>
       </c>
       <c r="N33">
-        <v>16.9622689</v>
+        <v>16.8771808</v>
       </c>
       <c r="O33">
-        <v>2.4764912594</v>
+        <v>2.4640683968</v>
       </c>
       <c r="P33">
-        <v>14.4857776406</v>
+        <v>14.4131124032</v>
       </c>
       <c r="Q33">
-        <v>29.0857776406</v>
+        <v>29.0131124032</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09953906509748092</v>
+        <v>0.1002459585294046</v>
       </c>
       <c r="T33">
-        <v>1.241086953752446</v>
+        <v>1.257412437168698</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.430628542841232</v>
+        <v>7.198421400877443</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08300635579999514</v>
+        <v>0.08295537468272844</v>
       </c>
       <c r="C34">
-        <v>109.6047680786646</v>
+        <v>108.2288321665733</v>
       </c>
       <c r="D34">
-        <v>139.2487680786646</v>
+        <v>139.4398321665733</v>
       </c>
       <c r="E34">
-        <v>32.84400000000001</v>
+        <v>34.411</v>
       </c>
       <c r="F34">
-        <v>50.14400000000001</v>
+        <v>51.71100000000001</v>
       </c>
       <c r="G34">
         <v>20.5</v>
@@ -4069,28 +4069,28 @@
         <v>19.6</v>
       </c>
       <c r="M34">
-        <v>2.7228192</v>
+        <v>2.807907300000001</v>
       </c>
       <c r="N34">
-        <v>16.8771808</v>
+        <v>16.7920927</v>
       </c>
       <c r="O34">
-        <v>2.4640683968</v>
+        <v>2.4516455342</v>
       </c>
       <c r="P34">
-        <v>14.4131124032</v>
+        <v>14.3404471658</v>
       </c>
       <c r="Q34">
-        <v>29.0131124032</v>
+        <v>28.9404471658</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1002459585294046</v>
+        <v>0.1009739532578036</v>
       </c>
       <c r="T34">
-        <v>1.257412437168698</v>
+        <v>1.274225248448121</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.198421400877443</v>
+        <v>6.980287419032671</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08295537468272844</v>
+        <v>0.08290439356546175</v>
       </c>
       <c r="C35">
-        <v>108.2288321665733</v>
+        <v>106.8534212953051</v>
       </c>
       <c r="D35">
-        <v>139.4398321665733</v>
+        <v>139.6314212953052</v>
       </c>
       <c r="E35">
-        <v>34.411</v>
+        <v>35.97800000000001</v>
       </c>
       <c r="F35">
-        <v>51.71100000000001</v>
+        <v>53.27800000000001</v>
       </c>
       <c r="G35">
         <v>20.5</v>
@@ -4151,28 +4151,28 @@
         <v>19.6</v>
       </c>
       <c r="M35">
-        <v>2.807907300000001</v>
+        <v>2.892995400000001</v>
       </c>
       <c r="N35">
-        <v>16.7920927</v>
+        <v>16.7070046</v>
       </c>
       <c r="O35">
-        <v>2.4516455342</v>
+        <v>2.4392226716</v>
       </c>
       <c r="P35">
-        <v>14.3404471658</v>
+        <v>14.2677819284</v>
       </c>
       <c r="Q35">
-        <v>28.9404471658</v>
+        <v>28.8677819284</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1009739532578036</v>
+        <v>0.1017240084325178</v>
       </c>
       <c r="T35">
-        <v>1.274225248448121</v>
+        <v>1.291547538857224</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.980287419032671</v>
+        <v>6.774984847884652</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08290439356546175</v>
+        <v>0.08285341244819505</v>
       </c>
       <c r="C36">
-        <v>106.8534212953051</v>
+        <v>105.4785376320427</v>
       </c>
       <c r="D36">
-        <v>139.6314212953052</v>
+        <v>139.8235376320427</v>
       </c>
       <c r="E36">
-        <v>35.97800000000001</v>
+        <v>37.54500000000002</v>
       </c>
       <c r="F36">
-        <v>53.27800000000001</v>
+        <v>54.84500000000001</v>
       </c>
       <c r="G36">
         <v>20.5</v>
@@ -4233,28 +4233,28 @@
         <v>19.6</v>
       </c>
       <c r="M36">
-        <v>2.892995400000001</v>
+        <v>2.978083500000001</v>
       </c>
       <c r="N36">
-        <v>16.7070046</v>
+        <v>16.6219165</v>
       </c>
       <c r="O36">
-        <v>2.4392226716</v>
+        <v>2.426799809</v>
       </c>
       <c r="P36">
-        <v>14.2677819284</v>
+        <v>14.195116691</v>
       </c>
       <c r="Q36">
-        <v>28.8677819284</v>
+        <v>28.795116691</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1017240084325178</v>
+        <v>0.1024971422279924</v>
       </c>
       <c r="T36">
-        <v>1.291547538857224</v>
+        <v>1.309402822817376</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.774984847884652</v>
+        <v>6.581413852230805</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08285341244819505</v>
+        <v>0.08280243133092835</v>
       </c>
       <c r="C37">
-        <v>105.4785376320427</v>
+        <v>104.1041833559118</v>
       </c>
       <c r="D37">
-        <v>139.8235376320427</v>
+        <v>140.0161833559118</v>
       </c>
       <c r="E37">
-        <v>37.54500000000002</v>
+        <v>39.11200000000001</v>
       </c>
       <c r="F37">
-        <v>54.84500000000001</v>
+        <v>56.41200000000001</v>
       </c>
       <c r="G37">
         <v>20.5</v>
@@ -4315,28 +4315,28 @@
         <v>19.6</v>
       </c>
       <c r="M37">
-        <v>2.978083500000001</v>
+        <v>3.063171600000001</v>
       </c>
       <c r="N37">
-        <v>16.6219165</v>
+        <v>16.5368284</v>
       </c>
       <c r="O37">
-        <v>2.426799809</v>
+        <v>2.4143769464</v>
       </c>
       <c r="P37">
-        <v>14.195116691</v>
+        <v>14.1224514536</v>
       </c>
       <c r="Q37">
-        <v>28.795116691</v>
+        <v>28.7224514536</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1024971422279924</v>
+        <v>0.1032944364545756</v>
       </c>
       <c r="T37">
-        <v>1.309402822817376</v>
+        <v>1.327816084401283</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.581413852230805</v>
+        <v>6.398596800779949</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08280243133092836</v>
+        <v>0.08275145021366168</v>
       </c>
       <c r="C38">
-        <v>104.1041833559117</v>
+        <v>102.7303606580644</v>
       </c>
       <c r="D38">
-        <v>140.0161833559117</v>
+        <v>140.2093606580644</v>
       </c>
       <c r="E38">
-        <v>39.11200000000001</v>
+        <v>40.679</v>
       </c>
       <c r="F38">
-        <v>56.41200000000001</v>
+        <v>57.97900000000001</v>
       </c>
       <c r="G38">
         <v>20.5</v>
@@ -4397,28 +4397,28 @@
         <v>19.6</v>
       </c>
       <c r="M38">
-        <v>3.0631716</v>
+        <v>3.148259700000001</v>
       </c>
       <c r="N38">
-        <v>16.5368284</v>
+        <v>16.4517403</v>
       </c>
       <c r="O38">
-        <v>2.4143769464</v>
+        <v>2.4019540838</v>
       </c>
       <c r="P38">
-        <v>14.1224514536</v>
+        <v>14.0497862162</v>
       </c>
       <c r="Q38">
-        <v>28.7224514536</v>
+        <v>28.6497862162</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1032944364545756</v>
+        <v>0.1041170416089868</v>
       </c>
       <c r="T38">
-        <v>1.327816084401283</v>
+        <v>1.346813893971981</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.398596800779949</v>
+        <v>6.225661752110221</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08275145021366168</v>
+        <v>0.08302498909639497</v>
       </c>
       <c r="C39">
-        <v>102.7303606580644</v>
+        <v>100.1330658804396</v>
       </c>
       <c r="D39">
-        <v>140.2093606580644</v>
+        <v>139.1790658804396</v>
       </c>
       <c r="E39">
-        <v>40.679</v>
+        <v>42.24600000000001</v>
       </c>
       <c r="F39">
-        <v>57.97900000000001</v>
+        <v>59.54600000000001</v>
       </c>
       <c r="G39">
         <v>20.5</v>
@@ -4479,45 +4479,45 @@
         <v>19.6</v>
       </c>
       <c r="M39">
-        <v>3.148259700000001</v>
+        <v>3.2928938</v>
       </c>
       <c r="N39">
-        <v>16.4517403</v>
+        <v>16.3071062</v>
       </c>
       <c r="O39">
-        <v>2.4019540838</v>
+        <v>2.3808375052</v>
       </c>
       <c r="P39">
-        <v>14.0497862162</v>
+        <v>13.9262686948</v>
       </c>
       <c r="Q39">
-        <v>28.6497862162</v>
+        <v>28.5262686948</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1041170416089868</v>
+        <v>0.1049661824135403</v>
       </c>
       <c r="T39">
-        <v>1.346813893971981</v>
+        <v>1.366424536109475</v>
       </c>
       <c r="U39">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.146</v>
       </c>
       <c r="W39">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>6.225661752110221</v>
+        <v>5.952211395338653</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08302498909639497</v>
+        <v>0.0829825479791283</v>
       </c>
       <c r="C40">
-        <v>100.1330658804396</v>
+        <v>98.72492844842211</v>
       </c>
       <c r="D40">
-        <v>139.1790658804396</v>
+        <v>139.3379284484221</v>
       </c>
       <c r="E40">
-        <v>42.24600000000001</v>
+        <v>43.813</v>
       </c>
       <c r="F40">
-        <v>59.54600000000001</v>
+        <v>61.11300000000001</v>
       </c>
       <c r="G40">
         <v>20.5</v>
@@ -4561,28 +4561,28 @@
         <v>19.6</v>
       </c>
       <c r="M40">
-        <v>3.2928938</v>
+        <v>3.379548900000001</v>
       </c>
       <c r="N40">
-        <v>16.3071062</v>
+        <v>16.2204511</v>
       </c>
       <c r="O40">
-        <v>2.3808375052</v>
+        <v>2.3681858606</v>
       </c>
       <c r="P40">
-        <v>13.9262686948</v>
+        <v>13.8522652394</v>
       </c>
       <c r="Q40">
-        <v>28.5262686948</v>
+        <v>28.4522652394</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1049661824135403</v>
+        <v>0.1058431639002103</v>
       </c>
       <c r="T40">
-        <v>1.366424536109475</v>
+        <v>1.38667815012033</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.952211395338653</v>
+        <v>5.799590590329969</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0829825479791283</v>
+        <v>0.08294010686186158</v>
       </c>
       <c r="C41">
-        <v>98.72492844842211</v>
+        <v>97.31715409047465</v>
       </c>
       <c r="D41">
-        <v>139.3379284484221</v>
+        <v>139.4971540904747</v>
       </c>
       <c r="E41">
-        <v>43.813</v>
+        <v>45.38000000000001</v>
       </c>
       <c r="F41">
-        <v>61.11300000000001</v>
+        <v>62.68000000000001</v>
       </c>
       <c r="G41">
         <v>20.5</v>
@@ -4643,28 +4643,28 @@
         <v>19.6</v>
       </c>
       <c r="M41">
-        <v>3.379548900000001</v>
+        <v>3.466204</v>
       </c>
       <c r="N41">
-        <v>16.2204511</v>
+        <v>16.133796</v>
       </c>
       <c r="O41">
-        <v>2.3681858606</v>
+        <v>2.355534216</v>
       </c>
       <c r="P41">
-        <v>13.8522652394</v>
+        <v>13.778261784</v>
       </c>
       <c r="Q41">
-        <v>28.4522652394</v>
+        <v>28.378261784</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1058431639002103</v>
+        <v>0.1067493781031026</v>
       </c>
       <c r="T41">
-        <v>1.38667815012033</v>
+        <v>1.407606884598214</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.799590590329969</v>
+        <v>5.654600825571721</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08294010686186158</v>
+        <v>0.0828976657445949</v>
       </c>
       <c r="C42">
-        <v>97.31715409047465</v>
+        <v>95.90974405270791</v>
       </c>
       <c r="D42">
-        <v>139.4971540904747</v>
+        <v>139.6567440527079</v>
       </c>
       <c r="E42">
-        <v>45.38000000000001</v>
+        <v>46.94700000000002</v>
       </c>
       <c r="F42">
-        <v>62.68000000000001</v>
+        <v>64.24700000000001</v>
       </c>
       <c r="G42">
         <v>20.5</v>
@@ -4725,28 +4725,28 @@
         <v>19.6</v>
       </c>
       <c r="M42">
-        <v>3.466204</v>
+        <v>3.552859100000001</v>
       </c>
       <c r="N42">
-        <v>16.133796</v>
+        <v>16.0471409</v>
       </c>
       <c r="O42">
-        <v>2.355534216</v>
+        <v>2.3428825714</v>
       </c>
       <c r="P42">
-        <v>13.778261784</v>
+        <v>13.7042583286</v>
       </c>
       <c r="Q42">
-        <v>28.378261784</v>
+        <v>28.3042583286</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1067493781031026</v>
+        <v>0.1076863114315168</v>
       </c>
       <c r="T42">
-        <v>1.407606884598214</v>
+        <v>1.429245067702466</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.654600825571721</v>
+        <v>5.516683732265093</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0828976657445949</v>
+        <v>0.08285522462732821</v>
       </c>
       <c r="C43">
-        <v>95.90974405270791</v>
+        <v>94.50269958694192</v>
       </c>
       <c r="D43">
-        <v>139.6567440527079</v>
+        <v>139.8166995869419</v>
       </c>
       <c r="E43">
-        <v>46.94700000000002</v>
+        <v>48.51400000000001</v>
       </c>
       <c r="F43">
-        <v>64.24700000000001</v>
+        <v>65.81400000000001</v>
       </c>
       <c r="G43">
         <v>20.5</v>
@@ -4807,28 +4807,28 @@
         <v>19.6</v>
       </c>
       <c r="M43">
-        <v>3.552859100000001</v>
+        <v>3.639514200000001</v>
       </c>
       <c r="N43">
-        <v>16.0471409</v>
+        <v>15.9604858</v>
       </c>
       <c r="O43">
-        <v>2.3428825714</v>
+        <v>2.3302309268</v>
       </c>
       <c r="P43">
-        <v>13.7042583286</v>
+        <v>13.6302548732</v>
       </c>
       <c r="Q43">
-        <v>28.3042583286</v>
+        <v>28.2302548732</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1076863114315168</v>
+        <v>0.1086555528057383</v>
       </c>
       <c r="T43">
-        <v>1.429245067702466</v>
+        <v>1.451629395051693</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.516683732265093</v>
+        <v>5.385334119592114</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08285522462732822</v>
+        <v>0.08281278351006152</v>
       </c>
       <c r="C44">
-        <v>94.50269958694186</v>
+        <v>93.09602195073813</v>
       </c>
       <c r="D44">
-        <v>139.8166995869419</v>
+        <v>139.9770219507381</v>
       </c>
       <c r="E44">
-        <v>48.51400000000001</v>
+        <v>50.081</v>
       </c>
       <c r="F44">
-        <v>65.81400000000001</v>
+        <v>67.381</v>
       </c>
       <c r="G44">
         <v>20.5</v>
@@ -4889,28 +4889,28 @@
         <v>19.6</v>
       </c>
       <c r="M44">
-        <v>3.639514200000001</v>
+        <v>3.7261693</v>
       </c>
       <c r="N44">
-        <v>15.9604858</v>
+        <v>15.8738307</v>
       </c>
       <c r="O44">
-        <v>2.3302309268</v>
+        <v>2.3175792822</v>
       </c>
       <c r="P44">
-        <v>13.6302548732</v>
+        <v>13.5562514178</v>
       </c>
       <c r="Q44">
-        <v>28.2302548732</v>
+        <v>28.1562514178</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1086555528057383</v>
+        <v>0.1096588026492307</v>
       </c>
       <c r="T44">
-        <v>1.451629395051693</v>
+        <v>1.474799137395629</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.385334119592114</v>
+        <v>5.260093791229508</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08281278351006152</v>
+        <v>0.08277034239279482</v>
       </c>
       <c r="C45">
-        <v>93.09602195073813</v>
+        <v>91.68971240743275</v>
       </c>
       <c r="D45">
-        <v>139.9770219507381</v>
+        <v>140.1377124074328</v>
       </c>
       <c r="E45">
-        <v>50.081</v>
+        <v>51.64800000000001</v>
       </c>
       <c r="F45">
-        <v>67.381</v>
+        <v>68.94800000000001</v>
       </c>
       <c r="G45">
         <v>20.5</v>
@@ -4971,28 +4971,28 @@
         <v>19.6</v>
       </c>
       <c r="M45">
-        <v>3.7261693</v>
+        <v>3.812824400000001</v>
       </c>
       <c r="N45">
-        <v>15.8738307</v>
+        <v>15.7871756</v>
       </c>
       <c r="O45">
-        <v>2.3175792822</v>
+        <v>2.3049276376</v>
       </c>
       <c r="P45">
-        <v>13.5562514178</v>
+        <v>13.4822479624</v>
       </c>
       <c r="Q45">
-        <v>28.1562514178</v>
+        <v>28.0822479624</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1096588026492307</v>
+        <v>0.1106978828442765</v>
       </c>
       <c r="T45">
-        <v>1.474799137395629</v>
+        <v>1.498796370537563</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.260093791229508</v>
+        <v>5.1405462050652</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08277034239279482</v>
+        <v>0.08272790127552813</v>
       </c>
       <c r="C46">
-        <v>91.68971240743275</v>
+        <v>90.28377222616962</v>
       </c>
       <c r="D46">
-        <v>140.1377124074328</v>
+        <v>140.2987722261696</v>
       </c>
       <c r="E46">
-        <v>51.64800000000001</v>
+        <v>53.21500000000002</v>
       </c>
       <c r="F46">
-        <v>68.94800000000001</v>
+        <v>70.51500000000001</v>
       </c>
       <c r="G46">
         <v>20.5</v>
@@ -5053,28 +5053,28 @@
         <v>19.6</v>
       </c>
       <c r="M46">
-        <v>3.812824400000001</v>
+        <v>3.899479500000001</v>
       </c>
       <c r="N46">
-        <v>15.7871756</v>
+        <v>15.7005205</v>
       </c>
       <c r="O46">
-        <v>2.3049276376</v>
+        <v>2.292275993</v>
       </c>
       <c r="P46">
-        <v>13.4822479624</v>
+        <v>13.408244507</v>
       </c>
       <c r="Q46">
-        <v>28.0822479624</v>
+        <v>28.008244507</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1106978828442765</v>
+        <v>0.1117747477736875</v>
       </c>
       <c r="T46">
-        <v>1.498796370537563</v>
+        <v>1.523666230339203</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.1405462050652</v>
+        <v>5.026311844952639</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08272790127552813</v>
+        <v>0.08268546015826145</v>
       </c>
       <c r="C47">
-        <v>90.28377222616962</v>
+        <v>88.87820268193387</v>
       </c>
       <c r="D47">
-        <v>140.2987722261696</v>
+        <v>140.4602026819339</v>
       </c>
       <c r="E47">
-        <v>53.21500000000002</v>
+        <v>54.78200000000001</v>
       </c>
       <c r="F47">
-        <v>70.51500000000001</v>
+        <v>72.08200000000001</v>
       </c>
       <c r="G47">
         <v>20.5</v>
@@ -5135,28 +5135,28 @@
         <v>19.6</v>
       </c>
       <c r="M47">
-        <v>3.899479500000001</v>
+        <v>3.986134600000001</v>
       </c>
       <c r="N47">
-        <v>15.7005205</v>
+        <v>15.6138654</v>
       </c>
       <c r="O47">
-        <v>2.292275993</v>
+        <v>2.2796243484</v>
       </c>
       <c r="P47">
-        <v>13.408244507</v>
+        <v>13.3342410516</v>
       </c>
       <c r="Q47">
-        <v>28.008244507</v>
+        <v>27.9342410516</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1117747477736875</v>
+        <v>0.112891496589373</v>
       </c>
       <c r="T47">
-        <v>1.523666230339203</v>
+        <v>1.549457196059423</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.026311844952639</v>
+        <v>4.917044196149321</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08268546015826145</v>
+        <v>0.08264301904099475</v>
       </c>
       <c r="C48">
-        <v>88.87820268193387</v>
+        <v>87.47300505558557</v>
       </c>
       <c r="D48">
-        <v>140.4602026819339</v>
+        <v>140.6220050555856</v>
       </c>
       <c r="E48">
-        <v>54.78200000000001</v>
+        <v>56.34900000000002</v>
       </c>
       <c r="F48">
-        <v>72.08200000000001</v>
+        <v>73.64900000000002</v>
       </c>
       <c r="G48">
         <v>20.5</v>
@@ -5217,28 +5217,28 @@
         <v>19.6</v>
       </c>
       <c r="M48">
-        <v>3.986134600000001</v>
+        <v>4.072789700000001</v>
       </c>
       <c r="N48">
-        <v>15.6138654</v>
+        <v>15.5272103</v>
       </c>
       <c r="O48">
-        <v>2.2796243484</v>
+        <v>2.2669727038</v>
       </c>
       <c r="P48">
-        <v>13.3342410516</v>
+        <v>13.2602375962</v>
       </c>
       <c r="Q48">
-        <v>27.9342410516</v>
+        <v>27.8602375962</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.112891496589373</v>
+        <v>0.1140503868698014</v>
       </c>
       <c r="T48">
-        <v>1.549457196059423</v>
+        <v>1.576221405769086</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.917044196149321</v>
+        <v>4.812426234529123</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08264301904099475</v>
+        <v>0.08260057792372806</v>
       </c>
       <c r="C49">
-        <v>87.47300505558557</v>
+        <v>86.06818063389335</v>
       </c>
       <c r="D49">
-        <v>140.6220050555856</v>
+        <v>140.7841806338934</v>
       </c>
       <c r="E49">
-        <v>56.34900000000002</v>
+        <v>57.91600000000001</v>
       </c>
       <c r="F49">
-        <v>73.64900000000002</v>
+        <v>75.21600000000001</v>
       </c>
       <c r="G49">
         <v>20.5</v>
@@ -5299,28 +5299,28 @@
         <v>19.6</v>
       </c>
       <c r="M49">
-        <v>4.072789700000001</v>
+        <v>4.1594448</v>
       </c>
       <c r="N49">
-        <v>15.5272103</v>
+        <v>15.4405552</v>
       </c>
       <c r="O49">
-        <v>2.2669727038</v>
+        <v>2.2543210592</v>
       </c>
       <c r="P49">
-        <v>13.2602375962</v>
+        <v>13.1862341408</v>
       </c>
       <c r="Q49">
-        <v>27.8602375962</v>
+        <v>27.7862341408</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1140503868698014</v>
+        <v>0.1152538498533232</v>
       </c>
       <c r="T49">
-        <v>1.576221405769086</v>
+        <v>1.604015008159889</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.812426234529123</v>
+        <v>4.712167354643101</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08260057792372806</v>
+        <v>0.08255813680646135</v>
       </c>
       <c r="C50">
-        <v>86.06818063389335</v>
+        <v>84.6637307095689</v>
       </c>
       <c r="D50">
-        <v>140.7841806338934</v>
+        <v>140.9467307095689</v>
       </c>
       <c r="E50">
-        <v>57.91600000000001</v>
+        <v>59.483</v>
       </c>
       <c r="F50">
-        <v>75.21600000000001</v>
+        <v>76.783</v>
       </c>
       <c r="G50">
         <v>20.5</v>
@@ -5381,28 +5381,28 @@
         <v>19.6</v>
       </c>
       <c r="M50">
-        <v>4.1594448</v>
+        <v>4.2460999</v>
       </c>
       <c r="N50">
-        <v>15.4405552</v>
+        <v>15.3539001</v>
       </c>
       <c r="O50">
-        <v>2.2543210592</v>
+        <v>2.2416694146</v>
       </c>
       <c r="P50">
-        <v>13.1862341408</v>
+        <v>13.1122306854</v>
       </c>
       <c r="Q50">
-        <v>27.7862341408</v>
+        <v>27.7122306854</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1152538498533232</v>
+        <v>0.1165045074636497</v>
       </c>
       <c r="T50">
-        <v>1.604015008159889</v>
+        <v>1.632898555742488</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.712167354643101</v>
+        <v>4.616000673936099</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08255813680646135</v>
+        <v>0.08251569568919466</v>
       </c>
       <c r="C51">
-        <v>84.6637307095689</v>
+        <v>83.25965658130066</v>
       </c>
       <c r="D51">
-        <v>140.9467307095689</v>
+        <v>141.1096565813007</v>
       </c>
       <c r="E51">
-        <v>59.483</v>
+        <v>61.05000000000001</v>
       </c>
       <c r="F51">
-        <v>76.783</v>
+        <v>78.35000000000001</v>
       </c>
       <c r="G51">
         <v>20.5</v>
@@ -5463,28 +5463,28 @@
         <v>19.6</v>
       </c>
       <c r="M51">
-        <v>4.2460999</v>
+        <v>4.332755000000001</v>
       </c>
       <c r="N51">
-        <v>15.3539001</v>
+        <v>15.267245</v>
       </c>
       <c r="O51">
-        <v>2.2416694146</v>
+        <v>2.22901777</v>
       </c>
       <c r="P51">
-        <v>13.1122306854</v>
+        <v>13.03822723</v>
       </c>
       <c r="Q51">
-        <v>27.7122306854</v>
+        <v>27.63822723</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1165045074636497</v>
+        <v>0.1178051913783893</v>
       </c>
       <c r="T51">
-        <v>1.632898555742488</v>
+        <v>1.662937445228391</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.616000673936099</v>
+        <v>4.523680660457376</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08251569568919466</v>
+        <v>0.08356210457192798</v>
       </c>
       <c r="C52">
-        <v>83.25965658130066</v>
+        <v>77.78242965512744</v>
       </c>
       <c r="D52">
-        <v>141.1096565813007</v>
+        <v>137.1994296551275</v>
       </c>
       <c r="E52">
-        <v>61.05000000000001</v>
+        <v>62.61700000000002</v>
       </c>
       <c r="F52">
-        <v>78.35000000000001</v>
+        <v>79.91700000000002</v>
       </c>
       <c r="G52">
         <v>20.5</v>
@@ -5545,45 +5545,45 @@
         <v>19.6</v>
       </c>
       <c r="M52">
-        <v>4.332755000000001</v>
+        <v>4.619202600000001</v>
       </c>
       <c r="N52">
-        <v>15.267245</v>
+        <v>14.9807974</v>
       </c>
       <c r="O52">
-        <v>2.22901777</v>
+        <v>2.1871964204</v>
       </c>
       <c r="P52">
-        <v>13.03822723</v>
+        <v>12.7936009796</v>
       </c>
       <c r="Q52">
-        <v>27.63822723</v>
+        <v>27.3936009796</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1178051913783893</v>
+        <v>0.1191589644325061</v>
       </c>
       <c r="T52">
-        <v>1.662937445228391</v>
+        <v>1.694202411836168</v>
       </c>
       <c r="U52">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.146</v>
       </c>
       <c r="W52">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.523680660457376</v>
+        <v>4.243156600232256</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08356210457192798</v>
+        <v>0.08354101345466128</v>
       </c>
       <c r="C53">
-        <v>77.78242965512744</v>
+        <v>76.29210192740908</v>
       </c>
       <c r="D53">
-        <v>137.1994296551275</v>
+        <v>137.2761019274091</v>
       </c>
       <c r="E53">
-        <v>62.61700000000002</v>
+        <v>64.18400000000001</v>
       </c>
       <c r="F53">
-        <v>79.91700000000002</v>
+        <v>81.48400000000001</v>
       </c>
       <c r="G53">
         <v>20.5</v>
@@ -5627,28 +5627,28 @@
         <v>19.6</v>
       </c>
       <c r="M53">
-        <v>4.619202600000001</v>
+        <v>4.709775200000001</v>
       </c>
       <c r="N53">
-        <v>14.9807974</v>
+        <v>14.8902248</v>
       </c>
       <c r="O53">
-        <v>2.1871964204</v>
+        <v>2.1739728208</v>
       </c>
       <c r="P53">
-        <v>12.7936009796</v>
+        <v>12.7162519792</v>
       </c>
       <c r="Q53">
-        <v>27.3936009796</v>
+        <v>27.3162519792</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1191589644325061</v>
+        <v>0.120569144697211</v>
       </c>
       <c r="T53">
-        <v>1.694202411836168</v>
+        <v>1.726770085385935</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.243156600232256</v>
+        <v>4.161557434843174</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08354101345466128</v>
+        <v>0.08351992233739458</v>
       </c>
       <c r="C54">
-        <v>76.29210192740908</v>
+        <v>74.80185994238505</v>
       </c>
       <c r="D54">
-        <v>137.2761019274091</v>
+        <v>137.3528599423851</v>
       </c>
       <c r="E54">
-        <v>64.18400000000001</v>
+        <v>65.75100000000002</v>
       </c>
       <c r="F54">
-        <v>81.48400000000001</v>
+        <v>83.05100000000002</v>
       </c>
       <c r="G54">
         <v>20.5</v>
@@ -5709,28 +5709,28 @@
         <v>19.6</v>
       </c>
       <c r="M54">
-        <v>4.709775200000001</v>
+        <v>4.800347800000002</v>
       </c>
       <c r="N54">
-        <v>14.8902248</v>
+        <v>14.7996522</v>
       </c>
       <c r="O54">
-        <v>2.1739728208</v>
+        <v>2.1607492212</v>
       </c>
       <c r="P54">
-        <v>12.7162519792</v>
+        <v>12.6389029788</v>
       </c>
       <c r="Q54">
-        <v>27.3162519792</v>
+        <v>27.2389029788</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.120569144697211</v>
+        <v>0.1220393326327544</v>
       </c>
       <c r="T54">
-        <v>1.726770085385935</v>
+        <v>1.760723617384629</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.161557434843174</v>
+        <v>4.083037483242359</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08351992233739458</v>
+        <v>0.08349883122012788</v>
       </c>
       <c r="C55">
-        <v>74.80185994238505</v>
+        <v>73.31170384396508</v>
       </c>
       <c r="D55">
-        <v>137.3528599423851</v>
+        <v>137.4297038439651</v>
       </c>
       <c r="E55">
-        <v>65.75100000000002</v>
+        <v>67.31800000000001</v>
       </c>
       <c r="F55">
-        <v>83.05100000000002</v>
+        <v>84.61800000000001</v>
       </c>
       <c r="G55">
         <v>20.5</v>
@@ -5791,28 +5791,28 @@
         <v>19.6</v>
       </c>
       <c r="M55">
-        <v>4.800347800000002</v>
+        <v>4.890920400000001</v>
       </c>
       <c r="N55">
-        <v>14.7996522</v>
+        <v>14.7090796</v>
       </c>
       <c r="O55">
-        <v>2.1607492212</v>
+        <v>2.1475256216</v>
       </c>
       <c r="P55">
-        <v>12.6389029788</v>
+        <v>12.5615539784</v>
       </c>
       <c r="Q55">
-        <v>27.2389029788</v>
+        <v>27.1615539784</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1220393326327544</v>
+        <v>0.1235734417828867</v>
       </c>
       <c r="T55">
-        <v>1.760723617384629</v>
+        <v>1.796153389905005</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.083037483242359</v>
+        <v>4.007425677997131</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08349883122012788</v>
+        <v>0.08512169010286122</v>
       </c>
       <c r="C56">
-        <v>73.31170384396508</v>
+        <v>66.07279566679436</v>
       </c>
       <c r="D56">
-        <v>137.4297038439651</v>
+        <v>131.7577956667944</v>
       </c>
       <c r="E56">
-        <v>67.31800000000001</v>
+        <v>68.88500000000002</v>
       </c>
       <c r="F56">
-        <v>84.61800000000001</v>
+        <v>86.18500000000002</v>
       </c>
       <c r="G56">
         <v>20.5</v>
@@ -5873,45 +5873,45 @@
         <v>19.6</v>
       </c>
       <c r="M56">
-        <v>4.890920400000001</v>
+        <v>5.283140500000001</v>
       </c>
       <c r="N56">
-        <v>14.7090796</v>
+        <v>14.3168595</v>
       </c>
       <c r="O56">
-        <v>2.1475256216</v>
+        <v>2.090261487</v>
       </c>
       <c r="P56">
-        <v>12.5615539784</v>
+        <v>12.226598013</v>
       </c>
       <c r="Q56">
-        <v>27.1615539784</v>
+        <v>26.826598013</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1235734417828867</v>
+        <v>0.1251757335619138</v>
       </c>
       <c r="T56">
-        <v>1.796153389905005</v>
+        <v>1.833157818981843</v>
       </c>
       <c r="U56">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V56">
         <v>0.146</v>
       </c>
       <c r="W56">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.007425677997131</v>
+        <v>3.709914585841508</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08512169010286122</v>
+        <v>0.08513048898559451</v>
       </c>
       <c r="C57">
-        <v>66.07279566679436</v>
+        <v>64.47631926252963</v>
       </c>
       <c r="D57">
-        <v>131.7577956667944</v>
+        <v>131.7283192625297</v>
       </c>
       <c r="E57">
-        <v>68.88500000000002</v>
+        <v>70.45200000000003</v>
       </c>
       <c r="F57">
-        <v>86.18500000000002</v>
+        <v>87.75200000000002</v>
       </c>
       <c r="G57">
         <v>20.5</v>
@@ -5955,28 +5955,28 @@
         <v>19.6</v>
       </c>
       <c r="M57">
-        <v>5.283140500000001</v>
+        <v>5.379197600000001</v>
       </c>
       <c r="N57">
-        <v>14.3168595</v>
+        <v>14.2208024</v>
       </c>
       <c r="O57">
-        <v>2.090261487</v>
+        <v>2.0762371504</v>
       </c>
       <c r="P57">
-        <v>12.226598013</v>
+        <v>12.1445652496</v>
       </c>
       <c r="Q57">
-        <v>26.826598013</v>
+        <v>26.7445652496</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1251757335619138</v>
+        <v>0.1268508567854421</v>
       </c>
       <c r="T57">
-        <v>1.833157818981843</v>
+        <v>1.871844267562173</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.709914585841508</v>
+        <v>3.643666111094338</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08513048898559451</v>
+        <v>0.08513928786832781</v>
       </c>
       <c r="C58">
-        <v>64.47631926252963</v>
+        <v>62.87985604403607</v>
       </c>
       <c r="D58">
-        <v>131.7283192625297</v>
+        <v>131.6988560440361</v>
       </c>
       <c r="E58">
-        <v>70.45200000000003</v>
+        <v>72.01900000000002</v>
       </c>
       <c r="F58">
-        <v>87.75200000000002</v>
+        <v>89.31900000000002</v>
       </c>
       <c r="G58">
         <v>20.5</v>
@@ -6037,28 +6037,28 @@
         <v>19.6</v>
       </c>
       <c r="M58">
-        <v>5.379197600000001</v>
+        <v>5.475254700000001</v>
       </c>
       <c r="N58">
-        <v>14.2208024</v>
+        <v>14.1247453</v>
       </c>
       <c r="O58">
-        <v>2.0762371504</v>
+        <v>2.0622128138</v>
       </c>
       <c r="P58">
-        <v>12.1445652496</v>
+        <v>12.0625324862</v>
       </c>
       <c r="Q58">
-        <v>26.7445652496</v>
+        <v>26.6625324862</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1268508567854421</v>
+        <v>0.1286038927170414</v>
       </c>
       <c r="T58">
-        <v>1.871844267562173</v>
+        <v>1.912330085843913</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.643666111094338</v>
+        <v>3.579742144233034</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08513928786832781</v>
+        <v>0.08514808675106111</v>
       </c>
       <c r="C59">
-        <v>62.87985604403607</v>
+        <v>61.28340600246801</v>
       </c>
       <c r="D59">
-        <v>131.6988560440361</v>
+        <v>131.669406002468</v>
       </c>
       <c r="E59">
-        <v>72.01900000000002</v>
+        <v>73.58600000000003</v>
       </c>
       <c r="F59">
-        <v>89.31900000000002</v>
+        <v>90.88600000000002</v>
       </c>
       <c r="G59">
         <v>20.5</v>
@@ -6119,28 +6119,28 @@
         <v>19.6</v>
       </c>
       <c r="M59">
-        <v>5.475254700000001</v>
+        <v>5.571311800000002</v>
       </c>
       <c r="N59">
-        <v>14.1247453</v>
+        <v>14.0286882</v>
       </c>
       <c r="O59">
-        <v>2.0622128138</v>
+        <v>2.0481884772</v>
       </c>
       <c r="P59">
-        <v>12.0625324862</v>
+        <v>11.9804997228</v>
       </c>
       <c r="Q59">
-        <v>26.6625324862</v>
+        <v>26.5804997228</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1286038927170414</v>
+        <v>0.1304404065501455</v>
       </c>
       <c r="T59">
-        <v>1.912330085843913</v>
+        <v>1.954743800234308</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.579742144233034</v>
+        <v>3.518022452091085</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08514808675106113</v>
+        <v>0.08656769363379443</v>
       </c>
       <c r="C60">
-        <v>61.283406002468</v>
+        <v>55.13143250150048</v>
       </c>
       <c r="D60">
-        <v>131.669406002468</v>
+        <v>127.0844325015005</v>
       </c>
       <c r="E60">
-        <v>73.58600000000001</v>
+        <v>75.15300000000001</v>
       </c>
       <c r="F60">
-        <v>90.88600000000001</v>
+        <v>92.453</v>
       </c>
       <c r="G60">
         <v>20.5</v>
@@ -6201,45 +6201,45 @@
         <v>19.6</v>
       </c>
       <c r="M60">
-        <v>5.571311800000001</v>
+        <v>5.9262373</v>
       </c>
       <c r="N60">
-        <v>14.0286882</v>
+        <v>13.6737627</v>
       </c>
       <c r="O60">
-        <v>2.0481884772</v>
+        <v>1.9963693542</v>
       </c>
       <c r="P60">
-        <v>11.9804997228</v>
+        <v>11.6773933458</v>
       </c>
       <c r="Q60">
-        <v>26.5804997228</v>
+        <v>26.2773933458</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1304404065501455</v>
+        <v>0.1323665064238889</v>
       </c>
       <c r="T60">
-        <v>1.954743800234308</v>
+        <v>1.999226476302283</v>
       </c>
       <c r="U60">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.146</v>
       </c>
       <c r="W60">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.518022452091085</v>
+        <v>3.307326218610922</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08656769363379443</v>
+        <v>0.08660040451652773</v>
       </c>
       <c r="C61">
-        <v>55.13143250150048</v>
+        <v>53.4625451791064</v>
       </c>
       <c r="D61">
-        <v>127.0844325015005</v>
+        <v>126.9825451791064</v>
       </c>
       <c r="E61">
-        <v>75.15300000000001</v>
+        <v>76.72000000000001</v>
       </c>
       <c r="F61">
-        <v>92.453</v>
+        <v>94.02000000000001</v>
       </c>
       <c r="G61">
         <v>20.5</v>
@@ -6283,28 +6283,28 @@
         <v>19.6</v>
       </c>
       <c r="M61">
-        <v>5.9262373</v>
+        <v>6.026682000000001</v>
       </c>
       <c r="N61">
-        <v>13.6737627</v>
+        <v>13.573318</v>
       </c>
       <c r="O61">
-        <v>1.9963693542</v>
+        <v>1.981704428</v>
       </c>
       <c r="P61">
-        <v>11.6773933458</v>
+        <v>11.591613572</v>
       </c>
       <c r="Q61">
-        <v>26.2773933458</v>
+        <v>26.191613572</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1323665064238889</v>
+        <v>0.1343889112913193</v>
       </c>
       <c r="T61">
-        <v>1.999226476302283</v>
+        <v>2.045933286173657</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.307326218610922</v>
+        <v>3.252204114967406</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08660040451652773</v>
+        <v>0.08663311539926105</v>
       </c>
       <c r="C62">
-        <v>53.4625451791064</v>
+        <v>51.79382109795516</v>
       </c>
       <c r="D62">
-        <v>126.9825451791064</v>
+        <v>126.8808210979552</v>
       </c>
       <c r="E62">
-        <v>76.72000000000001</v>
+        <v>78.28700000000001</v>
       </c>
       <c r="F62">
-        <v>94.02000000000001</v>
+        <v>95.587</v>
       </c>
       <c r="G62">
         <v>20.5</v>
@@ -6365,28 +6365,28 @@
         <v>19.6</v>
       </c>
       <c r="M62">
-        <v>6.026682000000001</v>
+        <v>6.127126700000001</v>
       </c>
       <c r="N62">
-        <v>13.573318</v>
+        <v>13.4728733</v>
       </c>
       <c r="O62">
-        <v>1.981704428</v>
+        <v>1.9670395018</v>
       </c>
       <c r="P62">
-        <v>11.591613572</v>
+        <v>11.5058337982</v>
       </c>
       <c r="Q62">
-        <v>26.191613572</v>
+        <v>26.1058337982</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1343889112913193</v>
+        <v>0.1365150292288745</v>
       </c>
       <c r="T62">
-        <v>2.045933286173657</v>
+        <v>2.095035317064076</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.252204114967406</v>
+        <v>3.198889293410564</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08663311539926105</v>
+        <v>0.08666582628199435</v>
       </c>
       <c r="C63">
-        <v>51.79382109795516</v>
+        <v>50.12525986604957</v>
       </c>
       <c r="D63">
-        <v>126.8808210979552</v>
+        <v>126.7792598660496</v>
       </c>
       <c r="E63">
-        <v>78.28700000000001</v>
+        <v>79.85400000000001</v>
       </c>
       <c r="F63">
-        <v>95.587</v>
+        <v>97.15400000000001</v>
       </c>
       <c r="G63">
         <v>20.5</v>
@@ -6447,28 +6447,28 @@
         <v>19.6</v>
       </c>
       <c r="M63">
-        <v>6.127126700000001</v>
+        <v>6.227571400000001</v>
       </c>
       <c r="N63">
-        <v>13.4728733</v>
+        <v>13.3724286</v>
       </c>
       <c r="O63">
-        <v>1.9670395018</v>
+        <v>1.9523745756</v>
       </c>
       <c r="P63">
-        <v>11.5058337982</v>
+        <v>11.4200540244</v>
       </c>
       <c r="Q63">
-        <v>26.1058337982</v>
+        <v>26.0200540244</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1365150292288745</v>
+        <v>0.1387530481105115</v>
       </c>
       <c r="T63">
-        <v>2.095035317064076</v>
+        <v>2.14672166536978</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.198889293410564</v>
+        <v>3.147294304807167</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08666582628199435</v>
+        <v>0.08669853716472765</v>
       </c>
       <c r="C64">
-        <v>50.12525986604957</v>
+        <v>48.45686109264624</v>
       </c>
       <c r="D64">
-        <v>126.7792598660496</v>
+        <v>126.6778610926463</v>
       </c>
       <c r="E64">
-        <v>79.85400000000001</v>
+        <v>81.42100000000002</v>
       </c>
       <c r="F64">
-        <v>97.15400000000001</v>
+        <v>98.72100000000002</v>
       </c>
       <c r="G64">
         <v>20.5</v>
@@ -6529,28 +6529,28 @@
         <v>19.6</v>
       </c>
       <c r="M64">
-        <v>6.227571400000001</v>
+        <v>6.328016100000002</v>
       </c>
       <c r="N64">
-        <v>13.3724286</v>
+        <v>13.2719839</v>
       </c>
       <c r="O64">
-        <v>1.9523745756</v>
+        <v>1.9377096494</v>
       </c>
       <c r="P64">
-        <v>11.4200540244</v>
+        <v>11.3342742506</v>
       </c>
       <c r="Q64">
-        <v>26.0200540244</v>
+        <v>25.9342742506</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1387530481105115</v>
+        <v>0.1411120409857504</v>
       </c>
       <c r="T64">
-        <v>2.14672166536978</v>
+        <v>2.201201870340657</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.147294304807167</v>
+        <v>3.09733725234991</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08669853716472765</v>
+        <v>0.08673124804746096</v>
       </c>
       <c r="C65">
-        <v>48.45686109264624</v>
+        <v>46.78862438825104</v>
       </c>
       <c r="D65">
-        <v>126.6778610926463</v>
+        <v>126.576624388251</v>
       </c>
       <c r="E65">
-        <v>81.42100000000002</v>
+        <v>82.98800000000001</v>
       </c>
       <c r="F65">
-        <v>98.72100000000002</v>
+        <v>100.288</v>
       </c>
       <c r="G65">
         <v>20.5</v>
@@ -6611,28 +6611,28 @@
         <v>19.6</v>
       </c>
       <c r="M65">
-        <v>6.328016100000002</v>
+        <v>6.428460800000001</v>
       </c>
       <c r="N65">
-        <v>13.2719839</v>
+        <v>13.1715392</v>
       </c>
       <c r="O65">
-        <v>1.9377096494</v>
+        <v>1.9230447232</v>
       </c>
       <c r="P65">
-        <v>11.3342742506</v>
+        <v>11.2484944768</v>
       </c>
       <c r="Q65">
-        <v>25.9342742506</v>
+        <v>25.8484944768</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1411120409857504</v>
+        <v>0.1436020890207249</v>
       </c>
       <c r="T65">
-        <v>2.201201870340657</v>
+        <v>2.258708753365472</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.09733725234991</v>
+        <v>3.048941357781944</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08673124804746096</v>
+        <v>0.08676395893019428</v>
       </c>
       <c r="C66">
-        <v>46.78862438825104</v>
+        <v>45.12054936461379</v>
       </c>
       <c r="D66">
-        <v>126.576624388251</v>
+        <v>126.4755493646138</v>
       </c>
       <c r="E66">
-        <v>82.98800000000001</v>
+        <v>84.55500000000002</v>
       </c>
       <c r="F66">
-        <v>100.288</v>
+        <v>101.855</v>
       </c>
       <c r="G66">
         <v>20.5</v>
@@ -6693,28 +6693,28 @@
         <v>19.6</v>
       </c>
       <c r="M66">
-        <v>6.428460800000001</v>
+        <v>6.528905500000001</v>
       </c>
       <c r="N66">
-        <v>13.1715392</v>
+        <v>13.0710945</v>
       </c>
       <c r="O66">
-        <v>1.9230447232</v>
+        <v>1.908379797</v>
       </c>
       <c r="P66">
-        <v>11.2484944768</v>
+        <v>11.162714703</v>
       </c>
       <c r="Q66">
-        <v>25.8484944768</v>
+        <v>25.762714703</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1436020890207249</v>
+        <v>0.1462344255148408</v>
       </c>
       <c r="T66">
-        <v>2.258708753365472</v>
+        <v>2.319501743991705</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.048941357781944</v>
+        <v>3.002034567662221</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08676395893019428</v>
+        <v>0.09119306181292758</v>
       </c>
       <c r="C67">
-        <v>45.12054936461379</v>
+        <v>31.21304625877231</v>
       </c>
       <c r="D67">
-        <v>126.4755493646138</v>
+        <v>114.1350462587723</v>
       </c>
       <c r="E67">
-        <v>84.55500000000002</v>
+        <v>86.12200000000001</v>
       </c>
       <c r="F67">
-        <v>101.855</v>
+        <v>103.422</v>
       </c>
       <c r="G67">
         <v>20.5</v>
@@ -6775,45 +6775,45 @@
         <v>19.6</v>
       </c>
       <c r="M67">
-        <v>6.528905500000001</v>
+        <v>7.436041800000002</v>
       </c>
       <c r="N67">
-        <v>13.0710945</v>
+        <v>12.1639582</v>
       </c>
       <c r="O67">
-        <v>1.908379797</v>
+        <v>1.7759378972</v>
       </c>
       <c r="P67">
-        <v>11.162714703</v>
+        <v>10.3880203028</v>
       </c>
       <c r="Q67">
-        <v>25.762714703</v>
+        <v>24.9880203028</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1462344255148408</v>
+        <v>0.1490216053321399</v>
       </c>
       <c r="T67">
-        <v>2.319501743991705</v>
+        <v>2.383870792890068</v>
       </c>
       <c r="U67">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V67">
         <v>0.146</v>
       </c>
       <c r="W67">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.002034567662221</v>
+        <v>2.63581089606032</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09119306181292758</v>
+        <v>0.09129238469566089</v>
       </c>
       <c r="C68">
-        <v>31.21304625877231</v>
+        <v>29.39685681989896</v>
       </c>
       <c r="D68">
-        <v>114.1350462587723</v>
+        <v>113.885856819899</v>
       </c>
       <c r="E68">
-        <v>86.12200000000001</v>
+        <v>87.68900000000002</v>
       </c>
       <c r="F68">
-        <v>103.422</v>
+        <v>104.989</v>
       </c>
       <c r="G68">
         <v>20.5</v>
@@ -6857,28 +6857,28 @@
         <v>19.6</v>
       </c>
       <c r="M68">
-        <v>7.436041800000002</v>
+        <v>7.548709100000002</v>
       </c>
       <c r="N68">
-        <v>12.1639582</v>
+        <v>12.0512909</v>
       </c>
       <c r="O68">
-        <v>1.7759378972</v>
+        <v>1.7594884714</v>
       </c>
       <c r="P68">
-        <v>10.3880203028</v>
+        <v>10.2918024286</v>
       </c>
       <c r="Q68">
-        <v>24.9880203028</v>
+        <v>24.8918024286</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1490216053321399</v>
+        <v>0.1519777051383663</v>
       </c>
       <c r="T68">
-        <v>2.383870792890068</v>
+        <v>2.452140996267121</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.63581089606032</v>
+        <v>2.596470434925092</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09129238469566089</v>
+        <v>0.09139170757839418</v>
       </c>
       <c r="C69">
-        <v>29.39685681989896</v>
+        <v>27.58175311414384</v>
       </c>
       <c r="D69">
-        <v>113.885856819899</v>
+        <v>113.6377531141439</v>
       </c>
       <c r="E69">
-        <v>87.68900000000002</v>
+        <v>89.25600000000003</v>
       </c>
       <c r="F69">
-        <v>104.989</v>
+        <v>106.556</v>
       </c>
       <c r="G69">
         <v>20.5</v>
@@ -6939,28 +6939,28 @@
         <v>19.6</v>
       </c>
       <c r="M69">
-        <v>7.548709100000002</v>
+        <v>7.661376400000003</v>
       </c>
       <c r="N69">
-        <v>12.0512909</v>
+        <v>11.9386236</v>
       </c>
       <c r="O69">
-        <v>1.7594884714</v>
+        <v>1.7430390456</v>
       </c>
       <c r="P69">
-        <v>10.2918024286</v>
+        <v>10.1955845544</v>
       </c>
       <c r="Q69">
-        <v>24.8918024286</v>
+        <v>24.7955845544</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1519777051383663</v>
+        <v>0.1551185611824819</v>
       </c>
       <c r="T69">
-        <v>2.452140996267121</v>
+        <v>2.524678087355239</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.596470434925092</v>
+        <v>2.558287046176193</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09139170757839418</v>
+        <v>0.09149103046112751</v>
       </c>
       <c r="C70">
-        <v>27.58175311414384</v>
+        <v>25.76772806102676</v>
       </c>
       <c r="D70">
-        <v>113.6377531141439</v>
+        <v>113.3907280610268</v>
       </c>
       <c r="E70">
-        <v>89.25600000000003</v>
+        <v>90.82300000000002</v>
       </c>
       <c r="F70">
-        <v>106.556</v>
+        <v>108.123</v>
       </c>
       <c r="G70">
         <v>20.5</v>
@@ -7021,28 +7021,28 @@
         <v>19.6</v>
       </c>
       <c r="M70">
-        <v>7.661376400000003</v>
+        <v>7.774043700000002</v>
       </c>
       <c r="N70">
-        <v>11.9386236</v>
+        <v>11.8259563</v>
       </c>
       <c r="O70">
-        <v>1.7430390456</v>
+        <v>1.7265896198</v>
       </c>
       <c r="P70">
-        <v>10.1955845544</v>
+        <v>10.0993666802</v>
       </c>
       <c r="Q70">
-        <v>24.7955845544</v>
+        <v>24.6993666802</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1551185611824819</v>
+        <v>0.1584620531004113</v>
       </c>
       <c r="T70">
-        <v>2.524678087355239</v>
+        <v>2.601894990771624</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.558287046176193</v>
+        <v>2.521210422318567</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09149103046112751</v>
+        <v>0.09392177334386081</v>
       </c>
       <c r="C71">
-        <v>25.76772806102676</v>
+        <v>18.47309821595056</v>
       </c>
       <c r="D71">
-        <v>113.3907280610268</v>
+        <v>107.6630982159506</v>
       </c>
       <c r="E71">
-        <v>90.82300000000002</v>
+        <v>92.39000000000003</v>
       </c>
       <c r="F71">
-        <v>108.123</v>
+        <v>109.69</v>
       </c>
       <c r="G71">
         <v>20.5</v>
@@ -7103,45 +7103,45 @@
         <v>19.6</v>
       </c>
       <c r="M71">
-        <v>7.774043700000002</v>
+        <v>8.314502000000003</v>
       </c>
       <c r="N71">
-        <v>11.8259563</v>
+        <v>11.285498</v>
       </c>
       <c r="O71">
-        <v>1.7265896198</v>
+        <v>1.647682708</v>
       </c>
       <c r="P71">
-        <v>10.0993666802</v>
+        <v>9.637815291999999</v>
       </c>
       <c r="Q71">
-        <v>24.6993666802</v>
+        <v>24.237815292</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1584620531004113</v>
+        <v>0.162028444479536</v>
       </c>
       <c r="T71">
-        <v>2.601894990771624</v>
+        <v>2.6842596877491</v>
       </c>
       <c r="U71">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V71">
         <v>0.146</v>
       </c>
       <c r="W71">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.521210422318567</v>
+        <v>2.357326993246257</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09392177334386081</v>
+        <v>0.09405440222659413</v>
       </c>
       <c r="C72">
-        <v>18.47309821595056</v>
+        <v>16.61018249077102</v>
       </c>
       <c r="D72">
-        <v>107.6630982159506</v>
+        <v>107.367182490771</v>
       </c>
       <c r="E72">
-        <v>92.39000000000003</v>
+        <v>93.95700000000002</v>
       </c>
       <c r="F72">
-        <v>109.69</v>
+        <v>111.257</v>
       </c>
       <c r="G72">
         <v>20.5</v>
@@ -7185,28 +7185,28 @@
         <v>19.6</v>
       </c>
       <c r="M72">
-        <v>8.314502000000003</v>
+        <v>8.433280600000002</v>
       </c>
       <c r="N72">
-        <v>11.285498</v>
+        <v>11.1667194</v>
       </c>
       <c r="O72">
-        <v>1.647682708</v>
+        <v>1.6303410324</v>
       </c>
       <c r="P72">
-        <v>9.637815291999999</v>
+        <v>9.536378367599999</v>
       </c>
       <c r="Q72">
-        <v>24.237815292</v>
+        <v>24.1363783676</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.162028444479536</v>
+        <v>0.1658407938848074</v>
       </c>
       <c r="T72">
-        <v>2.6842596877491</v>
+        <v>2.772304708656059</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.357326993246257</v>
+        <v>2.324125204608987</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09405440222659411</v>
+        <v>0.09418703110932741</v>
       </c>
       <c r="C73">
-        <v>16.61018249077107</v>
+        <v>14.74888897596955</v>
       </c>
       <c r="D73">
-        <v>107.3671824907711</v>
+        <v>107.0728889759696</v>
       </c>
       <c r="E73">
-        <v>93.95700000000001</v>
+        <v>95.52400000000002</v>
       </c>
       <c r="F73">
-        <v>111.257</v>
+        <v>112.824</v>
       </c>
       <c r="G73">
         <v>20.5</v>
@@ -7267,28 +7267,28 @@
         <v>19.6</v>
       </c>
       <c r="M73">
-        <v>8.433280600000002</v>
+        <v>8.552059200000002</v>
       </c>
       <c r="N73">
-        <v>11.1667194</v>
+        <v>11.0479408</v>
       </c>
       <c r="O73">
-        <v>1.6303410324</v>
+        <v>1.6129993568</v>
       </c>
       <c r="P73">
-        <v>9.536378367599999</v>
+        <v>9.4349414432</v>
       </c>
       <c r="Q73">
-        <v>24.1363783676</v>
+        <v>24.0349414432</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1658407938848073</v>
+        <v>0.1699254539618836</v>
       </c>
       <c r="T73">
-        <v>2.772304708656057</v>
+        <v>2.866638659627798</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.324125204608987</v>
+        <v>2.291845687878306</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09418703110932741</v>
+        <v>0.09431965999206073</v>
       </c>
       <c r="C74">
-        <v>14.74888897596955</v>
+        <v>12.88920436857055</v>
       </c>
       <c r="D74">
-        <v>107.0728889759696</v>
+        <v>106.7802043685706</v>
       </c>
       <c r="E74">
-        <v>95.52400000000002</v>
+        <v>97.09100000000001</v>
       </c>
       <c r="F74">
-        <v>112.824</v>
+        <v>114.391</v>
       </c>
       <c r="G74">
         <v>20.5</v>
@@ -7349,28 +7349,28 @@
         <v>19.6</v>
       </c>
       <c r="M74">
-        <v>8.552059200000002</v>
+        <v>8.670837800000001</v>
       </c>
       <c r="N74">
-        <v>11.0479408</v>
+        <v>10.9291622</v>
       </c>
       <c r="O74">
-        <v>1.6129993568</v>
+        <v>1.5956576812</v>
       </c>
       <c r="P74">
-        <v>9.4349414432</v>
+        <v>9.3335045188</v>
       </c>
       <c r="Q74">
-        <v>24.0349414432</v>
+        <v>23.9335045188</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1699254539618836</v>
+        <v>0.1743126814520768</v>
       </c>
       <c r="T74">
-        <v>2.866638659627798</v>
+        <v>2.967960310671519</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.291845687878306</v>
+        <v>2.260450541469015</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09431965999206073</v>
+        <v>0.09445228887479404</v>
       </c>
       <c r="C75">
-        <v>12.88920436857055</v>
+        <v>11.03111551065709</v>
       </c>
       <c r="D75">
-        <v>106.7802043685706</v>
+        <v>106.4891155106571</v>
       </c>
       <c r="E75">
-        <v>97.09100000000001</v>
+        <v>98.65800000000002</v>
       </c>
       <c r="F75">
-        <v>114.391</v>
+        <v>115.958</v>
       </c>
       <c r="G75">
         <v>20.5</v>
@@ -7431,28 +7431,28 @@
         <v>19.6</v>
       </c>
       <c r="M75">
-        <v>8.670837800000001</v>
+        <v>8.789616400000002</v>
       </c>
       <c r="N75">
-        <v>10.9291622</v>
+        <v>10.8103836</v>
       </c>
       <c r="O75">
-        <v>1.5956576812</v>
+        <v>1.5783160056</v>
       </c>
       <c r="P75">
-        <v>9.3335045188</v>
+        <v>9.2320675944</v>
       </c>
       <c r="Q75">
-        <v>23.9335045188</v>
+        <v>23.8320675944</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1743126814520768</v>
+        <v>0.1790373879799771</v>
       </c>
       <c r="T75">
-        <v>2.967960310671519</v>
+        <v>3.077075934872449</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.260450541469015</v>
+        <v>2.229903912530244</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09445228887479404</v>
+        <v>0.09458491775752735</v>
       </c>
       <c r="C76">
-        <v>11.03111551065709</v>
+        <v>9.174609387399201</v>
       </c>
       <c r="D76">
-        <v>106.4891155106571</v>
+        <v>106.1996093873992</v>
       </c>
       <c r="E76">
-        <v>98.65800000000002</v>
+        <v>100.225</v>
       </c>
       <c r="F76">
-        <v>115.958</v>
+        <v>117.525</v>
       </c>
       <c r="G76">
         <v>20.5</v>
@@ -7513,28 +7513,28 @@
         <v>19.6</v>
       </c>
       <c r="M76">
-        <v>8.789616400000002</v>
+        <v>8.908395000000001</v>
       </c>
       <c r="N76">
-        <v>10.8103836</v>
+        <v>10.691605</v>
       </c>
       <c r="O76">
-        <v>1.5783160056</v>
+        <v>1.56097433</v>
       </c>
       <c r="P76">
-        <v>9.2320675944</v>
+        <v>9.13063067</v>
       </c>
       <c r="Q76">
-        <v>23.8320675944</v>
+        <v>23.73063067</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1790373879799771</v>
+        <v>0.1841400710301094</v>
       </c>
       <c r="T76">
-        <v>3.077075934872449</v>
+        <v>3.194920809009454</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.229903912530244</v>
+        <v>2.200171860363175</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09458491775752735</v>
+        <v>0.09471754664026066</v>
       </c>
       <c r="C77">
-        <v>9.174609387399201</v>
+        <v>7.319673125113866</v>
       </c>
       <c r="D77">
-        <v>106.1996093873992</v>
+        <v>105.9116731251139</v>
       </c>
       <c r="E77">
-        <v>100.225</v>
+        <v>101.792</v>
       </c>
       <c r="F77">
-        <v>117.525</v>
+        <v>119.092</v>
       </c>
       <c r="G77">
         <v>20.5</v>
@@ -7595,28 +7595,28 @@
         <v>19.6</v>
       </c>
       <c r="M77">
-        <v>8.908395000000001</v>
+        <v>9.027173600000001</v>
       </c>
       <c r="N77">
-        <v>10.691605</v>
+        <v>10.5728264</v>
       </c>
       <c r="O77">
-        <v>1.56097433</v>
+        <v>1.5436326544</v>
       </c>
       <c r="P77">
-        <v>9.13063067</v>
+        <v>9.029193745600001</v>
       </c>
       <c r="Q77">
-        <v>23.73063067</v>
+        <v>23.6291937456</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1841400710301094</v>
+        <v>0.1896679776677527</v>
       </c>
       <c r="T77">
-        <v>3.194920809009454</v>
+        <v>3.322586089324544</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.200171860363175</v>
+        <v>2.171222230621553</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09471754664026066</v>
+        <v>0.09485017552299396</v>
       </c>
       <c r="C78">
-        <v>7.319673125113866</v>
+        <v>5.466293989356984</v>
       </c>
       <c r="D78">
-        <v>105.9116731251139</v>
+        <v>105.625293989357</v>
       </c>
       <c r="E78">
-        <v>101.792</v>
+        <v>103.359</v>
       </c>
       <c r="F78">
-        <v>119.092</v>
+        <v>120.659</v>
       </c>
       <c r="G78">
         <v>20.5</v>
@@ -7677,28 +7677,28 @@
         <v>19.6</v>
       </c>
       <c r="M78">
-        <v>9.027173600000001</v>
+        <v>9.145952200000002</v>
       </c>
       <c r="N78">
-        <v>10.5728264</v>
+        <v>10.4540478</v>
       </c>
       <c r="O78">
-        <v>1.5436326544</v>
+        <v>1.5262909788</v>
       </c>
       <c r="P78">
-        <v>9.029193745600001</v>
+        <v>8.927756821199999</v>
       </c>
       <c r="Q78">
-        <v>23.6291937456</v>
+        <v>23.5277568212</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1896679776677527</v>
+        <v>0.1956765718391042</v>
       </c>
       <c r="T78">
-        <v>3.322586089324544</v>
+        <v>3.461352698362683</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.171222230621553</v>
+        <v>2.14302453931478</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09485017552299396</v>
+        <v>0.09498280440572726</v>
       </c>
       <c r="C79">
-        <v>5.466293989356984</v>
+        <v>3.614459383045812</v>
       </c>
       <c r="D79">
-        <v>105.625293989357</v>
+        <v>105.3404593830458</v>
       </c>
       <c r="E79">
-        <v>103.359</v>
+        <v>104.926</v>
       </c>
       <c r="F79">
-        <v>120.659</v>
+        <v>122.226</v>
       </c>
       <c r="G79">
         <v>20.5</v>
@@ -7759,28 +7759,28 @@
         <v>19.6</v>
       </c>
       <c r="M79">
-        <v>9.145952200000002</v>
+        <v>9.264730800000002</v>
       </c>
       <c r="N79">
-        <v>10.4540478</v>
+        <v>10.3352692</v>
       </c>
       <c r="O79">
-        <v>1.5262909788</v>
+        <v>1.5089493032</v>
       </c>
       <c r="P79">
-        <v>8.927756821199999</v>
+        <v>8.826319896799999</v>
       </c>
       <c r="Q79">
-        <v>23.5277568212</v>
+        <v>23.4263198968</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1956765718391042</v>
+        <v>0.2022314018442148</v>
       </c>
       <c r="T79">
-        <v>3.461352698362683</v>
+        <v>3.612734453677017</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.14302453931478</v>
+        <v>2.115549865733821</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09498280440572726</v>
+        <v>0.09511543328846059</v>
       </c>
       <c r="C80">
-        <v>3.614459383045812</v>
+        <v>1.764156844611904</v>
       </c>
       <c r="D80">
-        <v>105.3404593830458</v>
+        <v>105.0571568446119</v>
       </c>
       <c r="E80">
-        <v>104.926</v>
+        <v>106.493</v>
       </c>
       <c r="F80">
-        <v>122.226</v>
+        <v>123.793</v>
       </c>
       <c r="G80">
         <v>20.5</v>
@@ -7841,28 +7841,28 @@
         <v>19.6</v>
       </c>
       <c r="M80">
-        <v>9.264730800000002</v>
+        <v>9.383509400000003</v>
       </c>
       <c r="N80">
-        <v>10.3352692</v>
+        <v>10.2164906</v>
       </c>
       <c r="O80">
-        <v>1.5089493032</v>
+        <v>1.4916076276</v>
       </c>
       <c r="P80">
-        <v>8.826319896799999</v>
+        <v>8.7248829724</v>
       </c>
       <c r="Q80">
-        <v>23.4263198968</v>
+        <v>23.3248829724</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2022314018442148</v>
+        <v>0.2094105013736218</v>
       </c>
       <c r="T80">
-        <v>3.612734453677017</v>
+        <v>3.778533519021289</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.115549865733821</v>
+        <v>2.088770753509342</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09511543328846059</v>
+        <v>0.09524806217119389</v>
       </c>
       <c r="C81">
-        <v>1.764156844611904</v>
+        <v>-0.08462595381602966</v>
       </c>
       <c r="D81">
-        <v>105.0571568446119</v>
+        <v>104.775374046184</v>
       </c>
       <c r="E81">
-        <v>106.493</v>
+        <v>108.06</v>
       </c>
       <c r="F81">
-        <v>123.793</v>
+        <v>125.36</v>
       </c>
       <c r="G81">
         <v>20.5</v>
@@ -7923,28 +7923,28 @@
         <v>19.6</v>
       </c>
       <c r="M81">
-        <v>9.383509400000003</v>
+        <v>9.502288000000002</v>
       </c>
       <c r="N81">
-        <v>10.2164906</v>
+        <v>10.097712</v>
       </c>
       <c r="O81">
-        <v>1.4916076276</v>
+        <v>1.474265952</v>
       </c>
       <c r="P81">
-        <v>8.7248829724</v>
+        <v>8.623446048</v>
       </c>
       <c r="Q81">
-        <v>23.3248829724</v>
+        <v>23.223446048</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2094105013736218</v>
+        <v>0.2173075108559694</v>
       </c>
       <c r="T81">
-        <v>3.778533519021289</v>
+        <v>3.960912490899987</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.088770753509342</v>
+        <v>2.062661119090476</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09524806217119389</v>
+        <v>0.0953806910539272</v>
       </c>
       <c r="C82">
-        <v>-0.08462595381602966</v>
+        <v>-1.931901208200784</v>
       </c>
       <c r="D82">
-        <v>104.775374046184</v>
+        <v>104.4950987917992</v>
       </c>
       <c r="E82">
-        <v>108.06</v>
+        <v>109.627</v>
       </c>
       <c r="F82">
-        <v>125.36</v>
+        <v>126.927</v>
       </c>
       <c r="G82">
         <v>20.5</v>
@@ -8005,28 +8005,28 @@
         <v>19.6</v>
       </c>
       <c r="M82">
-        <v>9.502288000000002</v>
+        <v>9.621066600000002</v>
       </c>
       <c r="N82">
-        <v>10.097712</v>
+        <v>9.978933399999999</v>
       </c>
       <c r="O82">
-        <v>1.474265952</v>
+        <v>1.4569242764</v>
       </c>
       <c r="P82">
-        <v>8.623446048</v>
+        <v>8.5220091236</v>
       </c>
       <c r="Q82">
-        <v>23.223446048</v>
+        <v>23.1220091236</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2173075108559694</v>
+        <v>0.2260357844943537</v>
       </c>
       <c r="T82">
-        <v>3.960912490899987</v>
+        <v>4.162489249292233</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.062661119090476</v>
+        <v>2.037196167002939</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0953806910539272</v>
+        <v>0.0955133199366605</v>
       </c>
       <c r="C83">
-        <v>-1.931901208200784</v>
+        <v>-3.77768098435574</v>
       </c>
       <c r="D83">
-        <v>104.4950987917992</v>
+        <v>104.2163190156443</v>
       </c>
       <c r="E83">
-        <v>109.627</v>
+        <v>111.194</v>
       </c>
       <c r="F83">
-        <v>126.927</v>
+        <v>128.494</v>
       </c>
       <c r="G83">
         <v>20.5</v>
@@ -8087,28 +8087,28 @@
         <v>19.6</v>
       </c>
       <c r="M83">
-        <v>9.621066600000002</v>
+        <v>9.739845200000003</v>
       </c>
       <c r="N83">
-        <v>9.978933399999999</v>
+        <v>9.860154799999998</v>
       </c>
       <c r="O83">
-        <v>1.4569242764</v>
+        <v>1.4395826008</v>
       </c>
       <c r="P83">
-        <v>8.5220091236</v>
+        <v>8.420572199199999</v>
       </c>
       <c r="Q83">
-        <v>23.1220091236</v>
+        <v>23.0205721992</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2260357844943537</v>
+        <v>0.2357338663147806</v>
       </c>
       <c r="T83">
-        <v>4.162489249292233</v>
+        <v>4.386463425283616</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.037196167002939</v>
+        <v>2.012352311307781</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0955133199366605</v>
+        <v>0.1057111928193938</v>
       </c>
       <c r="C84">
-        <v>-3.77768098435574</v>
+        <v>-23.08401688494038</v>
       </c>
       <c r="D84">
-        <v>104.2163190156443</v>
+        <v>86.47698311505965</v>
       </c>
       <c r="E84">
-        <v>111.194</v>
+        <v>112.761</v>
       </c>
       <c r="F84">
-        <v>128.494</v>
+        <v>130.061</v>
       </c>
       <c r="G84">
         <v>20.5</v>
@@ -8169,45 +8169,45 @@
         <v>19.6</v>
       </c>
       <c r="M84">
-        <v>9.739845200000003</v>
+        <v>11.70549</v>
       </c>
       <c r="N84">
-        <v>9.860154799999998</v>
+        <v>7.894509999999999</v>
       </c>
       <c r="O84">
-        <v>1.4395826008</v>
+        <v>1.15259846</v>
       </c>
       <c r="P84">
-        <v>8.420572199199999</v>
+        <v>6.741911539999998</v>
       </c>
       <c r="Q84">
-        <v>23.0205721992</v>
+        <v>21.34191154</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2357338663147806</v>
+        <v>0.2465728989376107</v>
       </c>
       <c r="T84">
-        <v>4.386463425283616</v>
+        <v>4.63678750433281</v>
       </c>
       <c r="U84">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V84">
         <v>0.146</v>
       </c>
       <c r="W84">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.012352311307781</v>
+        <v>1.67442798208362</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1057111928193938</v>
+        <v>0.1059650897021271</v>
       </c>
       <c r="C85">
-        <v>-23.08401688494038</v>
+        <v>-25.01595004717447</v>
       </c>
       <c r="D85">
-        <v>86.47698311505965</v>
+        <v>86.11204995282554</v>
       </c>
       <c r="E85">
-        <v>112.761</v>
+        <v>114.328</v>
       </c>
       <c r="F85">
-        <v>130.061</v>
+        <v>131.628</v>
       </c>
       <c r="G85">
         <v>20.5</v>
@@ -8251,28 +8251,28 @@
         <v>19.6</v>
       </c>
       <c r="M85">
-        <v>11.70549</v>
+        <v>11.84652</v>
       </c>
       <c r="N85">
-        <v>7.894509999999999</v>
+        <v>7.75348</v>
       </c>
       <c r="O85">
-        <v>1.15259846</v>
+        <v>1.13200808</v>
       </c>
       <c r="P85">
-        <v>6.741911539999998</v>
+        <v>6.621471919999999</v>
       </c>
       <c r="Q85">
-        <v>21.34191154</v>
+        <v>21.22147192</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2465728989376107</v>
+        <v>0.2587668106382945</v>
       </c>
       <c r="T85">
-        <v>4.63678750433281</v>
+        <v>4.918402093263154</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.67442798208362</v>
+        <v>1.654494315630244</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1059650897021271</v>
+        <v>0.1062189865848604</v>
       </c>
       <c r="C86">
-        <v>-25.01595004717444</v>
+        <v>-26.94481611419445</v>
       </c>
       <c r="D86">
-        <v>86.11204995282557</v>
+        <v>85.75018388580557</v>
       </c>
       <c r="E86">
-        <v>114.328</v>
+        <v>115.895</v>
       </c>
       <c r="F86">
-        <v>131.628</v>
+        <v>133.195</v>
       </c>
       <c r="G86">
         <v>20.5</v>
@@ -8333,28 +8333,28 @@
         <v>19.6</v>
       </c>
       <c r="M86">
-        <v>11.84652</v>
+        <v>11.98755</v>
       </c>
       <c r="N86">
-        <v>7.75348</v>
+        <v>7.612449999999999</v>
       </c>
       <c r="O86">
-        <v>1.13200808</v>
+        <v>1.1114177</v>
       </c>
       <c r="P86">
-        <v>6.621471919999999</v>
+        <v>6.501032299999999</v>
       </c>
       <c r="Q86">
-        <v>21.22147192</v>
+        <v>21.1010323</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2587668106382944</v>
+        <v>0.2725865772324027</v>
       </c>
       <c r="T86">
-        <v>4.91840209326315</v>
+        <v>5.237565294050872</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.654494315630244</v>
+        <v>1.635029676622829</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1062189865848604</v>
+        <v>0.1064728834675937</v>
       </c>
       <c r="C87">
-        <v>-26.94481611419445</v>
+        <v>-28.87065359047892</v>
       </c>
       <c r="D87">
-        <v>85.75018388580557</v>
+        <v>85.39134640952108</v>
       </c>
       <c r="E87">
-        <v>115.895</v>
+        <v>117.462</v>
       </c>
       <c r="F87">
-        <v>133.195</v>
+        <v>134.762</v>
       </c>
       <c r="G87">
         <v>20.5</v>
@@ -8415,28 +8415,28 @@
         <v>19.6</v>
       </c>
       <c r="M87">
-        <v>11.98755</v>
+        <v>12.12858</v>
       </c>
       <c r="N87">
-        <v>7.612449999999999</v>
+        <v>7.471420000000002</v>
       </c>
       <c r="O87">
-        <v>1.1114177</v>
+        <v>1.09082732</v>
       </c>
       <c r="P87">
-        <v>6.501032299999999</v>
+        <v>6.380592680000001</v>
       </c>
       <c r="Q87">
-        <v>21.1010323</v>
+        <v>20.98059268</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2725865772324027</v>
+        <v>0.288380596197098</v>
       </c>
       <c r="T87">
-        <v>5.237565294050872</v>
+        <v>5.602323237808268</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.635029676622829</v>
+        <v>1.616017703638843</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1064728834675937</v>
+        <v>0.106726780350327</v>
       </c>
       <c r="C88">
-        <v>-28.87065359047892</v>
+        <v>-30.79350033867595</v>
       </c>
       <c r="D88">
-        <v>85.39134640952108</v>
+        <v>85.03549966132405</v>
       </c>
       <c r="E88">
-        <v>117.462</v>
+        <v>119.029</v>
       </c>
       <c r="F88">
-        <v>134.762</v>
+        <v>136.329</v>
       </c>
       <c r="G88">
         <v>20.5</v>
@@ -8497,28 +8497,28 @@
         <v>19.6</v>
       </c>
       <c r="M88">
-        <v>12.12858</v>
+        <v>12.26961</v>
       </c>
       <c r="N88">
-        <v>7.471420000000002</v>
+        <v>7.330390000000001</v>
       </c>
       <c r="O88">
-        <v>1.09082732</v>
+        <v>1.07023694</v>
       </c>
       <c r="P88">
-        <v>6.380592680000001</v>
+        <v>6.260153060000001</v>
       </c>
       <c r="Q88">
-        <v>20.98059268</v>
+        <v>20.86015306</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.288380596197098</v>
+        <v>0.3066044642332849</v>
       </c>
       <c r="T88">
-        <v>5.602323237808268</v>
+        <v>6.023197788297572</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.616017703638843</v>
+        <v>1.597442787505063</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.106726780350327</v>
+        <v>0.1069806772330603</v>
       </c>
       <c r="C89">
-        <v>-30.79350033867595</v>
+        <v>-32.71339359292084</v>
       </c>
       <c r="D89">
-        <v>85.03549966132405</v>
+        <v>84.68260640707918</v>
       </c>
       <c r="E89">
-        <v>119.029</v>
+        <v>120.596</v>
       </c>
       <c r="F89">
-        <v>136.329</v>
+        <v>137.896</v>
       </c>
       <c r="G89">
         <v>20.5</v>
@@ -8579,28 +8579,28 @@
         <v>19.6</v>
       </c>
       <c r="M89">
-        <v>12.26961</v>
+        <v>12.41064</v>
       </c>
       <c r="N89">
-        <v>7.330390000000001</v>
+        <v>7.189360000000001</v>
       </c>
       <c r="O89">
-        <v>1.07023694</v>
+        <v>1.04964656</v>
       </c>
       <c r="P89">
-        <v>6.260153060000001</v>
+        <v>6.13971344</v>
       </c>
       <c r="Q89">
-        <v>20.86015306</v>
+        <v>20.73971344</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3066044642332849</v>
+        <v>0.3278656436088362</v>
       </c>
       <c r="T89">
-        <v>6.023197788297572</v>
+        <v>6.514218097201759</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.597442787505063</v>
+        <v>1.579290028556142</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1069806772330603</v>
+        <v>0.1072345741157937</v>
       </c>
       <c r="C90">
-        <v>-32.71339359292084</v>
+        <v>-34.63036997182375</v>
       </c>
       <c r="D90">
-        <v>84.68260640707918</v>
+        <v>84.33263002817627</v>
       </c>
       <c r="E90">
-        <v>120.596</v>
+        <v>122.163</v>
       </c>
       <c r="F90">
-        <v>137.896</v>
+        <v>139.463</v>
       </c>
       <c r="G90">
         <v>20.5</v>
@@ -8661,28 +8661,28 @@
         <v>19.6</v>
       </c>
       <c r="M90">
-        <v>12.41064</v>
+        <v>12.55167</v>
       </c>
       <c r="N90">
-        <v>7.189360000000001</v>
+        <v>7.04833</v>
       </c>
       <c r="O90">
-        <v>1.04964656</v>
+        <v>1.02905618</v>
       </c>
       <c r="P90">
-        <v>6.13971344</v>
+        <v>6.01927382</v>
       </c>
       <c r="Q90">
-        <v>20.73971344</v>
+        <v>20.61927382</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3278656436088362</v>
+        <v>0.3529924919617605</v>
       </c>
       <c r="T90">
-        <v>6.514218097201759</v>
+        <v>7.094514825906709</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.579290028556142</v>
+        <v>1.561545196774612</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1072345741157937</v>
+        <v>0.107488470998527</v>
       </c>
       <c r="C91">
-        <v>-34.63036997182375</v>
+        <v>-36.54446549113672</v>
       </c>
       <c r="D91">
-        <v>84.33263002817627</v>
+        <v>83.98553450886331</v>
       </c>
       <c r="E91">
-        <v>122.163</v>
+        <v>123.73</v>
       </c>
       <c r="F91">
-        <v>139.463</v>
+        <v>141.03</v>
       </c>
       <c r="G91">
         <v>20.5</v>
@@ -8743,28 +8743,28 @@
         <v>19.6</v>
       </c>
       <c r="M91">
-        <v>12.55167</v>
+        <v>12.6927</v>
       </c>
       <c r="N91">
-        <v>7.04833</v>
+        <v>6.907299999999999</v>
       </c>
       <c r="O91">
-        <v>1.02905618</v>
+        <v>1.0084658</v>
       </c>
       <c r="P91">
-        <v>6.01927382</v>
+        <v>5.8988342</v>
       </c>
       <c r="Q91">
-        <v>20.61927382</v>
+        <v>20.4988342</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3529924919617605</v>
+        <v>0.3831447099852696</v>
       </c>
       <c r="T91">
-        <v>7.094514825906709</v>
+        <v>7.790870900352647</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.561545196774612</v>
+        <v>1.544194694588228</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.107488470998527</v>
+        <v>0.1077423678812603</v>
       </c>
       <c r="C92">
-        <v>-36.54446549113672</v>
+        <v>-38.45571557610867</v>
       </c>
       <c r="D92">
-        <v>83.98553450886331</v>
+        <v>83.64128442389134</v>
       </c>
       <c r="E92">
-        <v>123.73</v>
+        <v>125.297</v>
       </c>
       <c r="F92">
-        <v>141.03</v>
+        <v>142.597</v>
       </c>
       <c r="G92">
         <v>20.5</v>
@@ -8825,28 +8825,28 @@
         <v>19.6</v>
       </c>
       <c r="M92">
-        <v>12.6927</v>
+        <v>12.83373</v>
       </c>
       <c r="N92">
-        <v>6.907299999999999</v>
+        <v>6.76627</v>
       </c>
       <c r="O92">
-        <v>1.0084658</v>
+        <v>0.9878754200000001</v>
       </c>
       <c r="P92">
-        <v>5.8988342</v>
+        <v>5.778394580000001</v>
       </c>
       <c r="Q92">
-        <v>20.4988342</v>
+        <v>20.37839458</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3831447099852696</v>
+        <v>0.4199974209028919</v>
       </c>
       <c r="T92">
-        <v>7.790870900352647</v>
+        <v>8.641972769119905</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.544194694588228</v>
+        <v>1.527225522120225</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1077423678812603</v>
+        <v>0.1079962647639936</v>
       </c>
       <c r="C93">
-        <v>-38.45571557610867</v>
+        <v>-40.36415507353861</v>
       </c>
       <c r="D93">
-        <v>83.64128442389134</v>
+        <v>83.2998449264614</v>
       </c>
       <c r="E93">
-        <v>125.297</v>
+        <v>126.864</v>
       </c>
       <c r="F93">
-        <v>142.597</v>
+        <v>144.164</v>
       </c>
       <c r="G93">
         <v>20.5</v>
@@ -8907,28 +8907,28 @@
         <v>19.6</v>
       </c>
       <c r="M93">
-        <v>12.83373</v>
+        <v>12.97476</v>
       </c>
       <c r="N93">
-        <v>6.76627</v>
+        <v>6.62524</v>
       </c>
       <c r="O93">
-        <v>0.9878754200000001</v>
+        <v>0.9672850399999999</v>
       </c>
       <c r="P93">
-        <v>5.778394580000001</v>
+        <v>5.65795496</v>
       </c>
       <c r="Q93">
-        <v>20.37839458</v>
+        <v>20.25795496</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4199974209028919</v>
+        <v>0.4660633095499198</v>
       </c>
       <c r="T93">
-        <v>8.641972769119905</v>
+        <v>9.70585010507898</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.527225522120225</v>
+        <v>1.510625244705875</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1079962647639936</v>
+        <v>0.155474761170053</v>
       </c>
       <c r="C94">
-        <v>-40.36415507353861</v>
+        <v>-77.9918799456363</v>
       </c>
       <c r="D94">
-        <v>83.2998449264614</v>
+        <v>47.23912005436372</v>
       </c>
       <c r="E94">
-        <v>126.864</v>
+        <v>128.431</v>
       </c>
       <c r="F94">
-        <v>144.164</v>
+        <v>145.731</v>
       </c>
       <c r="G94">
         <v>20.5</v>
@@ -8989,45 +8989,45 @@
         <v>19.6</v>
       </c>
       <c r="M94">
-        <v>12.97476</v>
+        <v>21.39331080000001</v>
       </c>
       <c r="N94">
-        <v>6.62524</v>
+        <v>-1.793310800000004</v>
       </c>
       <c r="O94">
-        <v>0.9672850399999999</v>
+        <v>-0.2618233768000006</v>
       </c>
       <c r="P94">
-        <v>5.65795496</v>
+        <v>-1.531487423200003</v>
       </c>
       <c r="Q94">
-        <v>20.25795496</v>
+        <v>13.0685125768</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4660633095499198</v>
+        <v>0.5316058232607621</v>
       </c>
       <c r="T94">
-        <v>9.70585010507898</v>
+        <v>11.21953402449797</v>
       </c>
       <c r="U94">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.146</v>
+        <v>0.1337614372432714</v>
       </c>
       <c r="W94">
-        <v>0.07686</v>
+        <v>0.1271638210126878</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.510625244705875</v>
+        <v>0.9161742276936394</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.155474761170053</v>
+        <v>0.156484761170053</v>
       </c>
       <c r="C95">
-        <v>-77.9918799456363</v>
+        <v>-79.9899375795016</v>
       </c>
       <c r="D95">
-        <v>47.23912005436372</v>
+        <v>46.80806242049842</v>
       </c>
       <c r="E95">
-        <v>128.431</v>
+        <v>129.998</v>
       </c>
       <c r="F95">
-        <v>145.731</v>
+        <v>147.298</v>
       </c>
       <c r="G95">
         <v>20.5</v>
@@ -9071,37 +9071,37 @@
         <v>19.6</v>
       </c>
       <c r="M95">
-        <v>21.39331080000001</v>
+        <v>21.62334640000001</v>
       </c>
       <c r="N95">
-        <v>-1.793310800000004</v>
+        <v>-2.023346400000005</v>
       </c>
       <c r="O95">
-        <v>-0.2618233768000006</v>
+        <v>-0.2954085744000007</v>
       </c>
       <c r="P95">
-        <v>-1.531487423200003</v>
+        <v>-1.727937825600004</v>
       </c>
       <c r="Q95">
-        <v>13.0685125768</v>
+        <v>12.8720621744</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5316058232607621</v>
+        <v>0.6125734604708893</v>
       </c>
       <c r="T95">
-        <v>11.21953402449797</v>
+        <v>13.0894563619143</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1337614372432714</v>
+        <v>0.1323384432300451</v>
       </c>
       <c r="W95">
-        <v>0.1271638210126878</v>
+        <v>0.1273727165338294</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9161742276936394</v>
+        <v>0.9064276933564731</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.156484761170053</v>
+        <v>0.157494761170053</v>
       </c>
       <c r="C96">
-        <v>-79.9899375795016</v>
+        <v>-81.98019953511586</v>
       </c>
       <c r="D96">
-        <v>46.80806242049842</v>
+        <v>46.38480046488418</v>
       </c>
       <c r="E96">
-        <v>129.998</v>
+        <v>131.565</v>
       </c>
       <c r="F96">
-        <v>147.298</v>
+        <v>148.865</v>
       </c>
       <c r="G96">
         <v>20.5</v>
@@ -9153,37 +9153,37 @@
         <v>19.6</v>
       </c>
       <c r="M96">
-        <v>21.62334640000001</v>
+        <v>21.85338200000001</v>
       </c>
       <c r="N96">
-        <v>-2.023346400000005</v>
+        <v>-2.253382000000006</v>
       </c>
       <c r="O96">
-        <v>-0.2954085744000007</v>
+        <v>-0.3289937720000008</v>
       </c>
       <c r="P96">
-        <v>-1.727937825600004</v>
+        <v>-1.924388228000005</v>
       </c>
       <c r="Q96">
-        <v>12.8720621744</v>
+        <v>12.67561177199999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6125734604708893</v>
+        <v>0.7259281525650675</v>
       </c>
       <c r="T96">
-        <v>13.0894563619143</v>
+        <v>15.70734763429717</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1323384432300451</v>
+        <v>0.1309454069855183</v>
       </c>
       <c r="W96">
-        <v>0.1273727165338294</v>
+        <v>0.1275772142545259</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9064276933564731</v>
+        <v>0.8968863492158786</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.157494761170053</v>
+        <v>0.158504761170053</v>
       </c>
       <c r="C97">
-        <v>-81.98019953511586</v>
+        <v>-83.96287539461966</v>
       </c>
       <c r="D97">
-        <v>46.38480046488418</v>
+        <v>45.96912460538037</v>
       </c>
       <c r="E97">
-        <v>131.565</v>
+        <v>133.132</v>
       </c>
       <c r="F97">
-        <v>148.865</v>
+        <v>150.432</v>
       </c>
       <c r="G97">
         <v>20.5</v>
@@ -9235,37 +9235,37 @@
         <v>19.6</v>
       </c>
       <c r="M97">
-        <v>21.85338200000001</v>
+        <v>22.0834176</v>
       </c>
       <c r="N97">
-        <v>-2.253382000000006</v>
+        <v>-2.483417600000003</v>
       </c>
       <c r="O97">
-        <v>-0.3289937720000008</v>
+        <v>-0.3625789696000004</v>
       </c>
       <c r="P97">
-        <v>-1.924388228000005</v>
+        <v>-2.120838630400002</v>
       </c>
       <c r="Q97">
-        <v>12.67561177199999</v>
+        <v>12.4791613696</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7259281525650675</v>
+        <v>0.8959601907063347</v>
       </c>
       <c r="T97">
-        <v>15.70734763429717</v>
+        <v>19.63418454287147</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1309454069855183</v>
+        <v>0.1295813923294191</v>
       </c>
       <c r="W97">
-        <v>0.1275772142545259</v>
+        <v>0.1277774516060413</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8968863492158786</v>
+        <v>0.8875437830782134</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.158504761170053</v>
+        <v>0.159514761170053</v>
       </c>
       <c r="C98">
-        <v>-83.96287539461966</v>
+        <v>-85.93816729422629</v>
       </c>
       <c r="D98">
-        <v>45.96912460538037</v>
+        <v>45.56083270577373</v>
       </c>
       <c r="E98">
-        <v>133.132</v>
+        <v>134.699</v>
       </c>
       <c r="F98">
-        <v>150.432</v>
+        <v>151.999</v>
       </c>
       <c r="G98">
         <v>20.5</v>
@@ -9317,37 +9317,37 @@
         <v>19.6</v>
       </c>
       <c r="M98">
-        <v>22.0834176</v>
+        <v>22.3134532</v>
       </c>
       <c r="N98">
-        <v>-2.483417600000003</v>
+        <v>-2.713453200000004</v>
       </c>
       <c r="O98">
-        <v>-0.3625789696000004</v>
+        <v>-0.3961641672000005</v>
       </c>
       <c r="P98">
-        <v>-2.120838630400002</v>
+        <v>-2.317289032800003</v>
       </c>
       <c r="Q98">
-        <v>12.4791613696</v>
+        <v>12.2827109672</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8959601907063326</v>
+        <v>1.179346920941777</v>
       </c>
       <c r="T98">
-        <v>19.63418454287142</v>
+        <v>26.17891272382856</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1295813923294191</v>
+        <v>0.1282455016868478</v>
       </c>
       <c r="W98">
-        <v>0.1277774516060413</v>
+        <v>0.1279735603523708</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8875437830782134</v>
+        <v>0.8783938471701904</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.159514761170053</v>
+        <v>0.160524761170053</v>
       </c>
       <c r="C99">
-        <v>-85.93816729422629</v>
+        <v>-87.90627025197941</v>
       </c>
       <c r="D99">
-        <v>45.56083270577373</v>
+        <v>45.15972974802059</v>
       </c>
       <c r="E99">
-        <v>134.699</v>
+        <v>136.266</v>
       </c>
       <c r="F99">
-        <v>151.999</v>
+        <v>153.566</v>
       </c>
       <c r="G99">
         <v>20.5</v>
@@ -9399,37 +9399,37 @@
         <v>19.6</v>
       </c>
       <c r="M99">
-        <v>22.3134532</v>
+        <v>22.5434888</v>
       </c>
       <c r="N99">
-        <v>-2.713453200000004</v>
+        <v>-2.943488800000001</v>
       </c>
       <c r="O99">
-        <v>-0.3961641672000005</v>
+        <v>-0.4297493648000001</v>
       </c>
       <c r="P99">
-        <v>-2.317289032800003</v>
+        <v>-2.513739435200001</v>
       </c>
       <c r="Q99">
-        <v>12.2827109672</v>
+        <v>12.0862605648</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.179346920941777</v>
+        <v>1.746120381412665</v>
       </c>
       <c r="T99">
-        <v>26.17891272382856</v>
+        <v>39.26836908574285</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1282455016868478</v>
+        <v>0.1269368741186147</v>
       </c>
       <c r="W99">
-        <v>0.1279735603523708</v>
+        <v>0.1281656668793874</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8783938471701904</v>
+        <v>0.8694306446480458</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.160524761170053</v>
+        <v>0.161534761170053</v>
       </c>
       <c r="C100">
-        <v>-87.90627025197941</v>
+        <v>-89.86737247834927</v>
       </c>
       <c r="D100">
-        <v>45.15972974802059</v>
+        <v>44.76562752165074</v>
       </c>
       <c r="E100">
-        <v>136.266</v>
+        <v>137.833</v>
       </c>
       <c r="F100">
-        <v>153.566</v>
+        <v>155.133</v>
       </c>
       <c r="G100">
         <v>20.5</v>
@@ -9481,37 +9481,37 @@
         <v>19.6</v>
       </c>
       <c r="M100">
-        <v>22.5434888</v>
+        <v>22.7735244</v>
       </c>
       <c r="N100">
-        <v>-2.943488800000001</v>
+        <v>-3.173524400000002</v>
       </c>
       <c r="O100">
-        <v>-0.4297493648000001</v>
+        <v>-0.4633345624000002</v>
       </c>
       <c r="P100">
-        <v>-2.513739435200001</v>
+        <v>-2.710189837600002</v>
       </c>
       <c r="Q100">
-        <v>12.0862605648</v>
+        <v>11.8898101624</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.746120381412665</v>
+        <v>3.44644076282533</v>
       </c>
       <c r="T100">
-        <v>39.26836908574285</v>
+        <v>78.53673817148569</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1269368741186147</v>
+        <v>0.1256546834709519</v>
       </c>
       <c r="W100">
-        <v>0.1281656668793874</v>
+        <v>0.1283538924664643</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8694306446480458</v>
+        <v>0.8606485169243281</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.161534761170053</v>
-      </c>
-      <c r="C101">
-        <v>-89.86737247834927</v>
-      </c>
-      <c r="D101">
-        <v>44.76562752165074</v>
-      </c>
-      <c r="E101">
-        <v>137.833</v>
-      </c>
-      <c r="F101">
-        <v>155.133</v>
-      </c>
-      <c r="G101">
-        <v>20.5</v>
-      </c>
-      <c r="H101">
-        <v>139.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>34.2</v>
-      </c>
-      <c r="K101">
-        <v>14.6</v>
-      </c>
-      <c r="L101">
-        <v>19.6</v>
-      </c>
-      <c r="M101">
-        <v>22.7735244</v>
-      </c>
-      <c r="N101">
-        <v>-3.173524400000002</v>
-      </c>
-      <c r="O101">
-        <v>-0.4633345624000002</v>
-      </c>
-      <c r="P101">
-        <v>-2.710189837600002</v>
-      </c>
-      <c r="Q101">
-        <v>11.8898101624</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.44644076282533</v>
-      </c>
-      <c r="T101">
-        <v>78.53673817148569</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1256546834709519</v>
-      </c>
-      <c r="W101">
-        <v>0.1283538924664643</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8606485169243281</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
